--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 46766-2025</t>
+          <t>A 59356-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45926</v>
+        <v>45253</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,11 +1186,16 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -1202,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1211,21 +1216,130 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Bukspolsnäcka
+Aspvedgnagare
+Myskbock
+Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 59356-2023 artfynd.xlsx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 59356-2023 karta.png", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 59356-2023 georefererad karta.tif", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 59356-2023 FSC-klagomål.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 59356-2023 FSC-klagomål mail.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 59356-2023 tillsynsbegäran.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 59356-2023 tillsynsbegäran mail.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46766-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>8</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Bronshjon
@@ -1234,111 +1348,224 @@
 Mattlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 1075-2022</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>17</v>
+      </c>
+      <c r="U9" t="n">
+        <v>17</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Tallticka
+Blåmossa
+Grönpyrola
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 29305-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
         <v>46202</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>7.9</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S10" t="n">
         <v>5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T10" t="n">
         <v>6</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Krusfrö
@@ -1347,270 +1574,43 @@
 Huggorm</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 29305-2026 artfynd.xlsx", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 29305-2026 karta.png", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 29305-2026 georefererad karta.tif", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 29305-2026 karta knärot.png", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 29305-2026 FSC-klagomål.docx", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 29305-2026 FSC-klagomål mail.docx", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 29305-2026 tillsynsbegäran.docx", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 29305-2026 tillsynsbegäran mail.docx", "A 29305-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 29305-2026 prioriterade fågelarter.docx", "A 29305-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 59356-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45253</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Bukspolsnäcka
-Aspvedgnagare
-Myskbock
-Noshornsoxe</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 59356-2023 artfynd.xlsx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 59356-2023 karta.png", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 59356-2023 georefererad karta.tif", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 59356-2023 FSC-klagomål.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 59356-2023 FSC-klagomål mail.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 59356-2023 tillsynsbegäran.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 59356-2023 tillsynsbegäran mail.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 1075-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44571</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>17</v>
-      </c>
-      <c r="U10" t="n">
-        <v>17</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Tallticka
-Blåmossa
-Grönpyrola
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46018</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 4051-2023</t>
+          <t>A 1543-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44952</v>
+        <v>44573</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2179,19 +2179,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2206,7 +2206,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2215,46 +2215,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 4148-2024</t>
+          <t>A 53785-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45323</v>
+        <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2283,14 +2283,19 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>6.9</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -2324,147 +2329,147 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 53785-2021 artfynd.xlsx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 53785-2021 karta.png", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 53785-2021 georefererad karta.tif", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 53785-2021 FSC-klagomål.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 53785-2021 FSC-klagomål mail.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 53785-2021 tillsynsbegäran.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 53785-2021 tillsynsbegäran mail.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 4148-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Gullviva</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 11749-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44994</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53785-2021</t>
+          <t>A 5414-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2478,10 +2483,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44463</v>
+        <v>45331</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2493,37 +2498,32 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2539,35 +2539,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 53785-2021 artfynd.xlsx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 53785-2021 karta.png", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 53785-2021 georefererad karta.tif", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 53785-2021 FSC-klagomål.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 53785-2021 FSC-klagomål mail.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 53785-2021 tillsynsbegäran.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 53785-2021 tillsynsbegäran mail.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
         <v/>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
         <v>45173</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 27253-2026</t>
+          <t>A 11749-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46188</v>
+        <v>44994</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2745,365 +2745,365 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Adam och eva</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18758-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 4051-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 27253-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="Z24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 5414-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 1543-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44573</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Hasselsnok</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 18758-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45043</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>44749</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47632-2022</t>
+          <t>A 51436-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44852</v>
+        <v>44869</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3435,7 +3435,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51436-2022</t>
+          <t>A 47632-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44869</v>
+        <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>44687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44536</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>44613</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 69261-2021</t>
+          <t>A 54231-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44531</v>
+        <v>44881</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3946,7 +3946,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54231-2022</t>
+          <t>A 69261-2021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44881</v>
+        <v>44531</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>44564</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>44636</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>44658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>44656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44463</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>44573</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44593</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44881</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>44480</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44487</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>44728</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 35659-2022</t>
+          <t>A 29424-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44799</v>
+        <v>44753</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5416,7 +5416,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5430,10 +5430,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45344</v>
+        <v>45687</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45271</v>
+        <v>45597</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5520,11 +5520,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>11.1</v>
+        <v>1.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5567,7 +5567,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 7634-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45339</v>
+        <v>44607</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10120-2025</t>
+          <t>A 48243-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45719</v>
+        <v>45590</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5713,7 +5713,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59516-2023</t>
+          <t>A 37421-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5723,14 +5723,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45254</v>
+        <v>45540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 14417-2024</t>
+          <t>A 19937-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45394</v>
+        <v>45433</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>11.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 18961-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5873,10 +5873,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44883</v>
+        <v>44690</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 65113-2023</t>
+          <t>A 7254-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5946,10 +5946,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45287</v>
+        <v>44970</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6005,7 +6005,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 35908-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6019,10 +6019,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45258</v>
+        <v>45148</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6078,7 +6078,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47679-2024</t>
+          <t>A 6548-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45588</v>
+        <v>44601</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.5</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6151,7 +6151,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 4856-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44833</v>
+        <v>44957</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6224,7 +6224,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 252-2023</t>
+          <t>A 59516-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6234,14 +6234,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44922</v>
+        <v>45254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6297,7 +6297,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7582-2023</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6311,10 +6311,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44972</v>
+        <v>45590</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6370,7 +6370,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44592</v>
+        <v>45020</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6443,7 +6443,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57864-2022</t>
+          <t>A 16342-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44899</v>
+        <v>45028</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 48243-2024</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6530,10 +6530,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45590</v>
+        <v>45344</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6589,7 +6589,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62048-2022</t>
+          <t>A 29008-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6603,10 +6603,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44918</v>
+        <v>44749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 38438-2024</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45546</v>
+        <v>45719</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6735,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 9337-2022</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6749,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44616</v>
+        <v>45189</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6808,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 34357-2023</t>
+          <t>A 3280-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6822,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45133</v>
+        <v>44949</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19745-2024</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6895,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45432</v>
+        <v>45176</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14082-2023</t>
+          <t>A 6022-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45009</v>
+        <v>45336</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7027,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46066</v>
+        <v>44573</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7100,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 47205-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7114,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46066</v>
+        <v>45202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7173,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46066</v>
+        <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 8823-2026</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7260,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46066</v>
+        <v>45204</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7319,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7333,10 +7333,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44942</v>
+        <v>45183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7392,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 38431-2024</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45546</v>
+        <v>45183</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7465,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 4856-2023</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44957</v>
+        <v>45271</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,8 +7494,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>11.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7538,7 +7543,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 45783-2023</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7548,14 +7553,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45195</v>
+        <v>45093</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7568,7 +7573,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7611,7 +7616,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7625,10 +7630,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46077</v>
+        <v>44592</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7641,7 +7646,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>11.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7684,7 +7689,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 49931-2024</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7698,10 +7703,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45597</v>
+        <v>45158</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7713,13 +7718,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7762,7 +7762,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7254-2023</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7776,10 +7776,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44970</v>
+        <v>44593</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7835,7 +7835,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 7266-2023</t>
+          <t>A 8143-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7849,10 +7849,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44970</v>
+        <v>44974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7865,7 +7865,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7908,7 +7908,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44897</v>
+        <v>45036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7981,7 +7981,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 31862-2022</t>
+          <t>A 35659-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44777</v>
+        <v>44799</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 58262-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8068,10 +8068,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45601</v>
+        <v>44894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8127,7 +8127,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8141,10 +8141,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44852</v>
+        <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8200,7 +8200,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 59399-2021</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8214,10 +8214,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44491</v>
+        <v>44749</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8273,7 +8273,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59741-2023</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45257</v>
+        <v>45404</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8346,7 +8346,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 56303-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8360,10 +8360,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46105</v>
+        <v>45624</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8419,7 +8419,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46105</v>
+        <v>45601</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8492,7 +8492,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 15096-2026</t>
+          <t>A 3267-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8506,10 +8506,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46105</v>
+        <v>44949</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8565,7 +8565,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 56303-2024</t>
+          <t>A 8890-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8579,10 +8579,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45624</v>
+        <v>45357</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8638,7 +8638,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6580-2025</t>
+          <t>A 17296-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8652,10 +8652,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45699</v>
+        <v>45035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8667,8 +8667,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8711,7 +8716,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4047-2023</t>
+          <t>A 60285-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8725,10 +8730,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44952</v>
+        <v>45258</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8741,7 +8746,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8784,7 +8789,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22974-2025</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8794,14 +8799,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45790</v>
+        <v>44937</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8814,7 +8819,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8857,7 +8862,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8871,10 +8876,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44903</v>
+        <v>44937</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8887,7 +8892,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8930,7 +8935,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4331-2023</t>
+          <t>A 6357-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8944,10 +8949,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44953</v>
+        <v>44965</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8960,7 +8965,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9003,7 +9008,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 66424-2021</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9017,10 +9022,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44518</v>
+        <v>44883</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9033,7 +9038,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9076,7 +9081,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9090,10 +9095,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45020</v>
+        <v>45992</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9106,7 +9111,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9149,7 +9154,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 34572-2024</t>
+          <t>A 20246-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9163,10 +9168,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45526</v>
+        <v>46139</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9178,8 +9183,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9222,7 +9232,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 23827-2022</t>
+          <t>A 20248-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9236,10 +9246,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44722</v>
+        <v>46139</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9251,8 +9261,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9295,7 +9310,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 41889-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9309,10 +9324,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45685</v>
+        <v>45176</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9325,7 +9340,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9368,7 +9383,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 48158-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9382,10 +9397,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45685</v>
+        <v>45205</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9397,8 +9412,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9441,7 +9461,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 17717-2025</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9455,10 +9475,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45758</v>
+        <v>44979</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9471,7 +9491,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9514,7 +9534,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 41843-2025</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9528,10 +9548,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45902</v>
+        <v>45099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9544,7 +9564,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9587,7 +9607,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9601,10 +9621,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45901</v>
+        <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9617,7 +9637,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9660,7 +9680,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 41839-2025</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9674,10 +9694,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45902</v>
+        <v>45354</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9690,7 +9710,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9733,7 +9753,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 46186-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9747,10 +9767,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45158</v>
+        <v>45581</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9763,7 +9783,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9806,7 +9826,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 57513-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9816,14 +9836,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45189</v>
+        <v>44896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9836,7 +9856,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9879,7 +9899,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 26811-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9893,10 +9913,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45782</v>
+        <v>45093</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9909,7 +9929,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9952,7 +9972,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 26821-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9966,10 +9986,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45433</v>
+        <v>45093</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9982,7 +10002,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10025,7 +10045,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10039,10 +10059,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45581</v>
+        <v>45901</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10055,7 +10075,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10098,7 +10118,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 41839-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10112,10 +10132,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45228</v>
+        <v>45902</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10128,7 +10148,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10171,7 +10191,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 20246-2026</t>
+          <t>A 41843-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10185,10 +10205,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46139</v>
+        <v>45902</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10200,13 +10220,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10249,7 +10264,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 20248-2026</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10263,10 +10278,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46139</v>
+        <v>44585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10278,13 +10293,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10327,7 +10337,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21511-2025</t>
+          <t>A 20307-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10337,14 +10347,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45782</v>
+        <v>46139</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10357,7 +10367,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10400,7 +10410,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10414,10 +10424,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45793</v>
+        <v>44903</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10430,7 +10440,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10473,7 +10483,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 9971-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10487,10 +10497,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45687</v>
+        <v>44985</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10503,7 +10513,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10546,7 +10556,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 20307-2026</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10560,10 +10570,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46139</v>
+        <v>45481</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10576,7 +10586,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10619,7 +10629,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10633,10 +10643,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45761</v>
+        <v>45228</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10649,7 +10659,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10692,7 +10702,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10706,10 +10716,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45992</v>
+        <v>45167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10722,7 +10732,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10765,7 +10775,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10782,7 +10792,7 @@
         <v>45926</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10795,7 +10805,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10838,7 +10848,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21483-2023</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10852,10 +10862,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45063</v>
+        <v>45926</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10868,7 +10878,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10911,7 +10921,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10925,10 +10935,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45215</v>
+        <v>45929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10941,7 +10951,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10984,7 +10994,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 54812-2022</t>
+          <t>A 20773-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10994,14 +11004,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44883</v>
+        <v>46141</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11013,8 +11023,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11057,7 +11072,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 47962-2023</t>
+          <t>A 21511-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11067,14 +11082,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45204</v>
+        <v>45782</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11087,7 +11102,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11130,7 +11145,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11144,10 +11159,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45926</v>
+        <v>44897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11160,7 +11175,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11203,7 +11218,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60242-2022</t>
+          <t>A 53786-2021</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11217,10 +11232,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44910</v>
+        <v>44463</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11232,8 +11247,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11276,7 +11296,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 40728-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11286,14 +11306,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45926</v>
+        <v>45170</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11306,7 +11326,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11349,7 +11369,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11363,10 +11383,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11379,7 +11399,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11422,7 +11442,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11436,10 +11456,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44585</v>
+        <v>45926</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11452,7 +11472,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11495,7 +11515,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20773-2026</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11509,10 +11529,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46141</v>
+        <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11524,13 +11544,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11573,7 +11588,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7646-2025</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11587,10 +11602,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45705</v>
+        <v>45761</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11603,7 +11618,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11646,7 +11661,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 7647-2025</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11660,10 +11675,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45705</v>
+        <v>45411</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11676,7 +11691,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11719,7 +11734,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11733,10 +11748,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45929</v>
+        <v>45685</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11749,7 +11764,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11792,7 +11807,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11806,10 +11821,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45929</v>
+        <v>45685</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11822,7 +11837,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11865,7 +11880,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 58247-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11879,10 +11894,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44593</v>
+        <v>45632</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11895,7 +11910,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11938,7 +11953,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11952,10 +11967,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45411</v>
+        <v>44852</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11968,7 +11983,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12011,7 +12026,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12025,10 +12040,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46147</v>
+        <v>45215</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12040,13 +12055,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12089,7 +12099,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 50992-2023</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12103,10 +12113,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45218</v>
+        <v>46147</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12124,7 +12134,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12167,7 +12177,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 8328-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12181,10 +12191,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45093</v>
+        <v>45352</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12197,7 +12207,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12240,7 +12250,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12254,10 +12264,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46154</v>
+        <v>45258</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12313,7 +12323,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 9292-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12327,10 +12337,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46154</v>
+        <v>44980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12343,7 +12353,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12386,7 +12396,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 22297-2026</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12400,10 +12410,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46154</v>
+        <v>44587</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12416,7 +12426,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12459,7 +12469,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 7634-2022</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12473,10 +12483,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44607</v>
+        <v>44725</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12489,7 +12499,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12532,7 +12542,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12546,10 +12556,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12561,13 +12571,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12610,7 +12615,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 56097-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12624,10 +12629,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45354</v>
+        <v>45973</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12640,7 +12645,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12683,7 +12688,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 39583-2022</t>
+          <t>A 42623-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12697,10 +12702,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44818</v>
+        <v>45565</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12713,7 +12718,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12756,7 +12761,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 21233-2023</t>
+          <t>A 17937-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12770,10 +12775,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45062</v>
+        <v>45040</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12785,8 +12790,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12829,7 +12839,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12843,10 +12853,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45481</v>
+        <v>46154</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12859,7 +12869,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12902,7 +12912,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 22297-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12916,10 +12926,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46170</v>
+        <v>46154</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12932,7 +12942,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12975,7 +12985,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12989,10 +12999,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45099</v>
+        <v>46155</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13004,8 +13014,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13048,7 +13063,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13062,10 +13077,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44937</v>
+        <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13078,7 +13093,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>4.7</v>
+        <v>0.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13121,7 +13136,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13135,10 +13150,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44937</v>
+        <v>44728</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13151,7 +13166,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13194,7 +13209,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13208,10 +13223,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45176</v>
+        <v>45339</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13224,7 +13239,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13267,7 +13282,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26049-2026</t>
+          <t>A 58749-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13281,10 +13296,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46177</v>
+        <v>45986</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13296,13 +13311,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13345,7 +13355,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 19937-2024</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13359,10 +13369,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45433</v>
+        <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13374,8 +13384,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>11.9</v>
+        <v>3.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13418,7 +13433,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 15660-2024</t>
+          <t>A 14429-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13432,10 +13447,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45404</v>
+        <v>44652</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13448,7 +13463,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13491,7 +13506,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 43516-2024</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13505,10 +13520,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45569</v>
+        <v>45992</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13520,13 +13535,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13569,7 +13579,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 43518-2024</t>
+          <t>A 17585-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13583,10 +13593,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45569</v>
+        <v>45036</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13598,13 +13608,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13647,7 +13652,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13661,10 +13666,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45590</v>
+        <v>44970</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13677,7 +13682,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13720,7 +13725,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 57144-2024</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13734,10 +13739,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45629</v>
+        <v>44922</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13750,7 +13755,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13793,7 +13798,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13803,14 +13808,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46189</v>
+        <v>45195</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13823,7 +13828,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13866,7 +13871,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13880,10 +13885,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45036</v>
+        <v>44972</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13896,7 +13901,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13939,7 +13944,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13953,10 +13958,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46049</v>
+        <v>45999</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13968,8 +13973,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14012,7 +14022,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14026,10 +14036,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45719</v>
+        <v>45999</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14041,8 +14051,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14085,7 +14100,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 56830-2024</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14095,14 +14110,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45628</v>
+        <v>44883</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14115,7 +14130,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>8.199999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14158,7 +14173,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14172,10 +14187,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45597</v>
+        <v>46006</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14187,13 +14202,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14236,7 +14246,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35908-2023</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14250,10 +14260,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45148</v>
+        <v>46006</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14266,7 +14276,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14309,7 +14319,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14323,10 +14333,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46195</v>
+        <v>46006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14339,7 +14349,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14382,7 +14392,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14396,10 +14406,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46195</v>
+        <v>46006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14412,7 +14422,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14455,7 +14465,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14469,10 +14479,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44587</v>
+        <v>45183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14485,7 +14495,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>6.3</v>
+        <v>0.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14528,7 +14538,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 41314-2023</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14542,10 +14552,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45173</v>
+        <v>44777</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14558,7 +14568,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14601,7 +14611,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 1974-2022</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14615,10 +14625,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44575</v>
+        <v>46020</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14631,7 +14641,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14674,7 +14684,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14688,10 +14698,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44587</v>
+        <v>44899</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14704,7 +14714,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14747,7 +14757,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14761,10 +14771,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45167</v>
+        <v>46020</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14777,7 +14787,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14820,7 +14830,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 15779-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14834,10 +14844,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44573</v>
+        <v>45404</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14850,7 +14860,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14893,7 +14903,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 56097-2025</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14907,10 +14917,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45973</v>
+        <v>45215</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14923,7 +14933,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14966,7 +14976,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 33177-2026</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14980,10 +14990,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46245</v>
+        <v>46019</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14996,7 +15006,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15039,7 +15049,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15053,10 +15063,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45204</v>
+        <v>46020</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15069,7 +15079,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15112,7 +15122,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 33076-2026</t>
+          <t>A 290-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15126,10 +15136,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46245</v>
+        <v>46027</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15142,7 +15152,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15185,7 +15195,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 33090-2026</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15199,10 +15209,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46245</v>
+        <v>46027</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15215,7 +15225,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15258,7 +15268,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 49345-2023</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15272,10 +15282,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45211</v>
+        <v>46027</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15288,7 +15298,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15331,7 +15341,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 49348-2023</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15345,10 +15355,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45211</v>
+        <v>44953</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15361,7 +15371,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15404,7 +15414,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 45873-2023</t>
+          <t>A 560-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15418,10 +15428,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45195</v>
+        <v>46029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15433,8 +15443,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>15.8</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15477,7 +15492,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 58749-2025</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15491,10 +15506,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45986</v>
+        <v>44830</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15507,7 +15522,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15550,7 +15565,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15564,10 +15579,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44728</v>
+        <v>46170</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15580,7 +15595,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15623,7 +15638,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15637,10 +15652,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44725</v>
+        <v>45257</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15653,7 +15668,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15696,7 +15711,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 43151-2023</t>
+          <t>A 260-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15710,10 +15725,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45183</v>
+        <v>46027</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15726,7 +15741,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15769,7 +15784,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 52223-2021</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15783,10 +15798,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45986</v>
+        <v>44463</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15798,8 +15813,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>0.3</v>
+        <v>10.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15842,7 +15862,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 45377-2023</t>
+          <t>A 8685-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15856,10 +15876,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45193</v>
+        <v>44613</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15872,7 +15892,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15915,7 +15935,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15929,10 +15949,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45183</v>
+        <v>45569</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15944,8 +15964,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15988,7 +16013,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16002,10 +16027,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45183</v>
+        <v>45569</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16017,8 +16042,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16061,7 +16091,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 30523-2026</t>
+          <t>A 21399-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16075,10 +16105,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46210</v>
+        <v>45063</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16091,7 +16121,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16134,7 +16164,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16148,10 +16178,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44749</v>
+        <v>45394</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16164,7 +16194,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>6.6</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16207,7 +16237,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 10135-2025</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16221,10 +16251,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45719</v>
+        <v>45758</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16237,7 +16267,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>10.3</v>
+        <v>0.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16280,7 +16310,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 54849-2023</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16294,10 +16324,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45236</v>
+        <v>45133</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16310,7 +16340,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16353,7 +16383,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 26049-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16367,10 +16397,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45992</v>
+        <v>46177</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16382,8 +16412,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16426,7 +16461,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16440,10 +16475,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45989</v>
+        <v>45063</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16455,13 +16490,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16504,7 +16534,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 34488-2026</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16518,10 +16548,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46255</v>
+        <v>45546</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16534,7 +16564,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16577,7 +16607,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34489-2026</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16591,10 +16621,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46255</v>
+        <v>45546</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16607,7 +16637,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16650,7 +16680,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 50041-2023</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16664,10 +16694,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45215</v>
+        <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16680,7 +16710,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>10.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16723,7 +16753,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 34616-2026</t>
+          <t>A 6160-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16737,10 +16767,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46255</v>
+        <v>46055</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16753,7 +16783,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16796,7 +16826,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 6162-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16806,14 +16836,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46213</v>
+        <v>46055</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16826,7 +16856,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16869,7 +16899,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 42401-2022</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16883,10 +16913,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44830</v>
+        <v>44575</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16899,7 +16929,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16942,7 +16972,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 6161-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16956,10 +16986,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44974</v>
+        <v>46055</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16972,7 +17002,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17015,7 +17045,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17029,10 +17059,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45999</v>
+        <v>45173</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17044,13 +17074,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17093,7 +17118,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17107,10 +17132,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45999</v>
+        <v>44722</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17122,13 +17147,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17171,7 +17191,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 8845-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17185,10 +17205,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46265</v>
+        <v>46066</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17201,7 +17221,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17244,7 +17264,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 8818-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17258,10 +17278,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46266</v>
+        <v>46066</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17274,7 +17294,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17317,7 +17337,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 8823-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17331,10 +17351,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46006</v>
+        <v>46066</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17347,7 +17367,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17390,7 +17410,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 8822-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17404,10 +17424,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46006</v>
+        <v>46066</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17420,7 +17440,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17463,7 +17483,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 21487-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17477,10 +17497,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46006</v>
+        <v>45063</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17493,7 +17513,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17536,7 +17556,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 35806-2026</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17550,10 +17570,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46265</v>
+        <v>45705</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17566,7 +17586,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17609,7 +17629,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17623,10 +17643,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46006</v>
+        <v>45705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17639,7 +17659,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17682,7 +17702,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 10575-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17692,14 +17712,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45170</v>
+        <v>46077</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17712,7 +17732,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17755,7 +17775,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 36555-2026</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17769,10 +17789,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46269</v>
+        <v>45195</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17785,7 +17805,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.1</v>
+        <v>15.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17828,7 +17848,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17842,10 +17862,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46020</v>
+        <v>45629</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17858,7 +17878,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17901,7 +17921,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 3276-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17915,10 +17935,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46019</v>
+        <v>44949</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17931,7 +17951,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17974,7 +17994,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17988,10 +18008,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46020</v>
+        <v>45218</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18003,8 +18023,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18047,7 +18072,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18061,10 +18086,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44894</v>
+        <v>44918</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18077,7 +18102,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18120,7 +18145,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18134,10 +18159,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46020</v>
+        <v>45719</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18150,7 +18175,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18193,7 +18218,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 21399-2023</t>
+          <t>A 4965-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18207,10 +18232,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45063</v>
+        <v>46049</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18223,7 +18248,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18266,7 +18291,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 21397-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18280,10 +18305,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46027</v>
+        <v>45063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18296,7 +18321,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18339,7 +18364,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 27525-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18353,10 +18378,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45336</v>
+        <v>46189</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18369,7 +18394,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18412,7 +18437,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18426,10 +18451,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46027</v>
+        <v>45009</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18442,7 +18467,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18485,7 +18510,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 290-2026</t>
+          <t>A 28119-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18499,10 +18524,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46027</v>
+        <v>46195</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18515,7 +18540,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.2</v>
+        <v>7.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18558,7 +18583,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 38060-2026</t>
+          <t>A 28093-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18572,10 +18597,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46280</v>
+        <v>46195</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18588,7 +18613,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18631,7 +18656,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 52223-2021</t>
+          <t>A 15078-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18645,10 +18670,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44463</v>
+        <v>46105</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18660,13 +18685,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18709,7 +18729,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 15138-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18723,10 +18743,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45036</v>
+        <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18739,7 +18759,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18782,7 +18802,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 8685-2022</t>
+          <t>A 15096-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18796,10 +18816,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44613</v>
+        <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18812,7 +18832,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18855,7 +18875,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18869,10 +18889,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45093</v>
+        <v>44952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18885,7 +18905,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18928,7 +18948,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18942,10 +18962,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46029</v>
+        <v>45204</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18957,13 +18977,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19006,7 +19021,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 3267-2023</t>
+          <t>A 33076-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19020,10 +19035,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44949</v>
+        <v>46245</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19036,7 +19051,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19079,7 +19094,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 3276-2023</t>
+          <t>A 33090-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19093,10 +19108,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>44949</v>
+        <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19109,7 +19124,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19152,7 +19167,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 53786-2021</t>
+          <t>A 33177-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19166,10 +19181,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44463</v>
+        <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19181,13 +19196,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I243" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19230,7 +19240,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19244,10 +19254,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>44753</v>
+        <v>45211</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19260,7 +19270,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19303,7 +19313,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19317,10 +19327,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46027</v>
+        <v>45211</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19376,7 +19386,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19390,10 +19400,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44652</v>
+        <v>45236</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19406,7 +19416,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19449,7 +19459,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 19925-2024</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19463,10 +19473,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45035</v>
+        <v>45433</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19478,13 +19488,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I247" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19527,7 +19532,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 21397-2023</t>
+          <t>A 21396-2025</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19541,10 +19546,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45063</v>
+        <v>45782</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19600,7 +19605,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19614,10 +19619,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45258</v>
+        <v>45193</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19630,7 +19635,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19673,7 +19678,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19687,10 +19692,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46055</v>
+        <v>45202</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19703,7 +19708,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19746,7 +19751,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19760,10 +19765,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46055</v>
+        <v>45526</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19776,7 +19781,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19819,7 +19824,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19833,10 +19838,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46055</v>
+        <v>45793</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19849,7 +19854,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19892,7 +19897,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 10122-2025</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19906,10 +19911,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45719</v>
+        <v>45597</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19921,8 +19926,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19965,7 +19975,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 54785-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19979,10 +19989,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44985</v>
+        <v>44883</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19995,7 +20005,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>4.6</v>
+        <v>8.5</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20038,7 +20048,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 6522-2025</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20052,10 +20062,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45040</v>
+        <v>45699</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20067,13 +20077,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20116,7 +20121,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 15779-2024</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20130,10 +20135,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45404</v>
+        <v>45317</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20146,7 +20151,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20189,7 +20194,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 19747-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20203,10 +20208,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44980</v>
+        <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20219,7 +20224,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20262,7 +20267,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 19747-2024</t>
+          <t>A 30523-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20276,10 +20281,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45432</v>
+        <v>46210</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20292,7 +20297,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20335,7 +20340,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 54785-2022</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20349,10 +20354,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44883</v>
+        <v>44910</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20365,7 +20370,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20408,7 +20413,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 6522-2025</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20422,10 +20427,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45699</v>
+        <v>44616</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20438,7 +20443,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20481,7 +20486,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 16342-2023</t>
+          <t>A 34488-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20495,10 +20500,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45028</v>
+        <v>46255</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20511,7 +20516,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20554,7 +20559,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 34616-2026</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20568,10 +20573,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44749</v>
+        <v>46255</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20584,7 +20589,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20627,7 +20632,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20641,10 +20646,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45352</v>
+        <v>45062</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20657,7 +20662,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20700,7 +20705,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 34489-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20714,10 +20719,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45093</v>
+        <v>46255</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20730,7 +20735,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20773,7 +20778,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20787,10 +20792,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45205</v>
+        <v>45432</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20802,13 +20807,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I265" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20851,7 +20851,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 21487-2023</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20865,10 +20865,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45063</v>
+        <v>45588</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20924,7 +20924,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 6548-2022</t>
+          <t>A 30964-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20934,14 +20934,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44601</v>
+        <v>46213</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20954,7 +20954,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20997,7 +20997,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 18961-2022</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21011,10 +21011,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44690</v>
+        <v>45404</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21070,7 +21070,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21084,10 +21084,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45632</v>
+        <v>44518</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21143,7 +21143,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21157,10 +21157,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45176</v>
+        <v>44818</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21216,7 +21216,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 10122-2025</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21230,10 +21230,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45202</v>
+        <v>45719</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21289,7 +21289,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21303,10 +21303,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44965</v>
+        <v>45287</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21362,7 +21362,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 35740-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21372,14 +21372,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>44896</v>
+        <v>46265</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21435,7 +21435,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 37421-2024</t>
+          <t>A 35806-2026</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21449,10 +21449,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45540</v>
+        <v>46265</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21508,7 +21508,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 35924-2026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21522,10 +21522,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>44949</v>
+        <v>46266</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21581,7 +21581,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21595,10 +21595,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45357</v>
+        <v>45628</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21654,7 +21654,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 36555-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21668,10 +21668,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>45565</v>
+        <v>46269</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21727,7 +21727,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 47354-2023</t>
+          <t>A 38060-2026</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21741,10 +21741,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45202</v>
+        <v>46280</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 3276-2024</t>
+          <t>A 57862-2023</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -21814,10 +21814,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45317</v>
+        <v>45247</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -21873,7 +21873,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 24367-2025</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -21887,10 +21887,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45404</v>
+        <v>45797</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -21946,7 +21946,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 2336-2024</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -21960,10 +21960,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>44979</v>
+        <v>45310</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22019,7 +22019,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 57862-2023</t>
+          <t>A 59399-2021</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22033,10 +22033,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45247</v>
+        <v>44491</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22092,7 +22092,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 24367-2025</t>
+          <t>A 22974-2025</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22102,14 +22102,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45797</v>
+        <v>45790</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22165,7 +22165,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 2336-2024</t>
+          <t>A 6580-2025</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22179,10 +22179,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45310</v>
+        <v>45699</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22255,7 +22255,7 @@
         <v>44140</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>43951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44735</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45300</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45708</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46076</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>45253</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45926</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>44571</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46018</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>44573</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>44463</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45323</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>45331</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>45173</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>44994</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         <v>44952</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>45790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>44749</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44869</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>44687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44536</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>44613</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>44881</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>44531</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>44564</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>44636</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>44658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>44656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>44463</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>44629</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>44573</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44593</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44881</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>44480</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
         <v>44487</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>44728</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>44753</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45687</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45597</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>44607</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45590</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>45540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45433</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>44690</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>44970</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45148</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>44601</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>44957</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>45254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>45590</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>45020</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>45028</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45344</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>44749</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>45719</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45189</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44949</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>45176</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>45336</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44573</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45202</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>44833</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>45204</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>45183</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>45271</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45093</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44592</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>45158</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>44593</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44974</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44799</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44587</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>44749</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>45404</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>45624</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45601</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>44949</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45357</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>45035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>45258</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>44937</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44937</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44965</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44883</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45992</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>46139</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>46139</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>45176</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>45205</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>44979</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>45099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>44942</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45354</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45581</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44896</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45093</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45093</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45901</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45902</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45902</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44585</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>46139</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44903</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>44985</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45481</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45228</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>45167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>45926</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
         <v>45926</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>45929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>46141</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>45782</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44897</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11235,7 +11235,7 @@
         <v>44463</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>45170</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>45926</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45926</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45761</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11678,7 +11678,7 @@
         <v>45411</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45685</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11824,7 +11824,7 @@
         <v>45685</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11897,7 +11897,7 @@
         <v>45632</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44852</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         <v>45215</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12116,7 +12116,7 @@
         <v>46147</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>45352</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45258</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44980</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44587</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>44725</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>46154</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>45973</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>45565</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>45040</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>46154</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>46154</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>46155</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44728</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45339</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45986</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>44652</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13523,7 +13523,7 @@
         <v>45992</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13596,7 +13596,7 @@
         <v>45036</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44970</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>44922</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13815,7 +13815,7 @@
         <v>45195</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44972</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45999</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>45999</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44883</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>46006</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>46006</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>46006</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>46006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45183</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>44777</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>46020</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44899</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46020</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>45404</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14920,7 +14920,7 @@
         <v>45215</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>46019</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>46020</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>46027</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>46027</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>46027</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15358,7 +15358,7 @@
         <v>44953</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>46029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44830</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>46170</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>45257</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>46027</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>44463</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44613</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15952,7 +15952,7 @@
         <v>45569</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>45569</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45063</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16181,7 +16181,7 @@
         <v>45394</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45758</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>45133</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16400,7 +16400,7 @@
         <v>46177</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>45063</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45546</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>45546</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>46055</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>46055</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>44575</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>46055</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45173</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>44722</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>46066</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>46066</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17354,7 +17354,7 @@
         <v>46066</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>46066</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45063</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45705</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>45705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>46077</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17792,7 +17792,7 @@
         <v>45195</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>45629</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>44949</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>45218</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44918</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45719</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>46049</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>46189</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45009</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46195</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46195</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>46105</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>46105</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>46105</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18892,7 +18892,7 @@
         <v>44952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>45204</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>46245</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45211</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>45211</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19403,7 +19403,7 @@
         <v>45236</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>45433</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19549,7 +19549,7 @@
         <v>45782</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19622,7 +19622,7 @@
         <v>45193</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45202</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45526</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45793</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>45597</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44883</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45699</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45317</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45432</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>46210</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44910</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44616</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>46255</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>46255</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45062</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46255</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45432</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45588</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46213</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45404</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44518</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44818</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45719</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45287</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46265</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>46265</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>46266</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45628</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>46269</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>46280</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>45247</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45797</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45310</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>44491</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45790</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45699</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>44140</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>43951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>44735</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45300</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45708</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>46076</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>45253</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>45926</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>44571</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22311-2022</t>
+          <t>A 34616-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44712</v>
+        <v>46255</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1862,19 +1862,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1889,1112 +1889,1118 @@
         <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Lateritticka
+Talltita
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 34616-2026 artfynd.xlsx", "A 34616-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 34616-2026 karta.png", "A 34616-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 34616-2026 georefererad karta.tif", "A 34616-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 34616-2026 FSC-klagomål.docx", "A 34616-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 34616-2026 FSC-klagomål mail.docx", "A 34616-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 34616-2026 tillsynsbegäran.docx", "A 34616-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 34616-2026 tillsynsbegäran mail.docx", "A 34616-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 34616-2026 prioriterade fågelarter.docx", "A 34616-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22311-2022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44712</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="T13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>2</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Gullklöver
 Jungfrulin</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 22311-2022 artfynd.xlsx", "A 22311-2022")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 22311-2022 karta.png", "A 22311-2022")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 22311-2022 georefererad karta.tif", "A 22311-2022")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 22311-2022 FSC-klagomål.docx", "A 22311-2022")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 22311-2022 FSC-klagomål mail.docx", "A 22311-2022")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 22311-2022 tillsynsbegäran.docx", "A 22311-2022")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 22311-2022 tillsynsbegäran mail.docx", "A 22311-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 63760-2025</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
         <v>46018</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>3.3</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
         <v>2</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Grovticka
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 63760-2025 artfynd.xlsx", "A 63760-2025")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 63760-2025 karta.png", "A 63760-2025")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 63760-2025 georefererad karta.tif", "A 63760-2025")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 63760-2025 FSC-klagomål.docx", "A 63760-2025")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 63760-2025 FSC-klagomål mail.docx", "A 63760-2025")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 63760-2025 tillsynsbegäran.docx", "A 63760-2025")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 63760-2025 tillsynsbegäran mail.docx", "A 63760-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 31168-2022</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>44770</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>1.7</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>1</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>2</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Skogsalm</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 31168-2022 artfynd.xlsx", "A 31168-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 31168-2022 karta.png", "A 31168-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 31168-2022 georefererad karta.tif", "A 31168-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 31168-2022 FSC-klagomål.docx", "A 31168-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 31168-2022 FSC-klagomål mail.docx", "A 31168-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 31168-2022 tillsynsbegäran.docx", "A 31168-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 31168-2022 tillsynsbegäran mail.docx", "A 31168-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 1543-2022</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>44573</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>6.5</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Hasselsnok</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 53785-2021</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
         <v>44463</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Övriga Aktiebolag</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>6.9</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="U18" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Ekoxe</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 53785-2021 artfynd.xlsx", "A 53785-2021")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 53785-2021 karta.png", "A 53785-2021")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 53785-2021 georefererad karta.tif", "A 53785-2021")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 53785-2021 FSC-klagomål.docx", "A 53785-2021")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 53785-2021 FSC-klagomål mail.docx", "A 53785-2021")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 53785-2021 tillsynsbegäran.docx", "A 53785-2021")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 53785-2021 tillsynsbegäran mail.docx", "A 53785-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 4148-2024</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
         <v>45323</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>2.4</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Gullviva</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 5414-2024</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45331</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.8</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Tallticka</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 40874-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
         <v>45173</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 11749-2023</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>44994</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>2.4</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Adam och eva</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 18758-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45043</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>2.9</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 4051-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
@@ -3015,7 +3021,7 @@
         <v>46188</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3107,7 +3113,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 23067-2025</t>
+          <t>A 4051-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3121,10 +3127,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45790</v>
+        <v>44952</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3137,31 +3143,31 @@
         </is>
       </c>
       <c r="I25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3173,123 +3179,155 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 23067-2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>45790</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 23067-2025 artfynd.xlsx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 23067-2025 karta.png", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 23067-2025 georefererad karta.tif", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 23067-2025 FSC-klagomål.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 23067-2025 FSC-klagomål mail.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 23067-2025 tillsynsbegäran.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 23067-2025 tillsynsbegäran mail.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 23067-2025 prioriterade fågelarter.docx", "A 23067-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 8718-2022</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>44613</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr"/>
-    </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 29011-2022</t>
+          <t>A 8718-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3303,10 +3341,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44749</v>
+        <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3319,7 +3357,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3362,7 +3400,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 51436-2022</t>
+          <t>A 29011-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3376,10 +3414,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44869</v>
+        <v>44749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3392,7 +3430,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3435,7 +3473,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 47632-2022</t>
+          <t>A 51436-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3449,10 +3487,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44852</v>
+        <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3465,7 +3503,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3525,7 +3563,7 @@
         <v>44687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3581,7 +3619,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 70314-2021</t>
+          <t>A 47632-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3595,10 +3633,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44536</v>
+        <v>44852</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3611,7 +3649,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3654,7 +3692,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8717-2022</t>
+          <t>A 70314-2021</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3668,10 +3706,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44613</v>
+        <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3684,7 +3722,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3727,7 +3765,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 69457-2021</t>
+          <t>A 8717-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3741,10 +3779,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44531</v>
+        <v>44613</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3757,7 +3795,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3800,7 +3838,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 7128-2022</t>
+          <t>A 69457-2021</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3814,10 +3852,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44603</v>
+        <v>44531</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3830,7 +3868,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3873,7 +3911,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 54231-2022</t>
+          <t>A 7128-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3887,10 +3925,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44881</v>
+        <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3903,7 +3941,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3963,7 +4001,7 @@
         <v>44531</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4019,7 +4057,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8720-2022</t>
+          <t>A 54231-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4033,10 +4071,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44613</v>
+        <v>44881</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4049,7 +4087,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4092,7 +4130,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 118-2022</t>
+          <t>A 8720-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4106,10 +4144,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44564</v>
+        <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4122,7 +4160,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4165,7 +4203,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8688-2022</t>
+          <t>A 118-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4179,10 +4217,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44613</v>
+        <v>44564</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4195,7 +4233,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4238,7 +4276,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12094-2022</t>
+          <t>A 8688-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4252,10 +4290,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44636</v>
+        <v>44613</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4268,7 +4306,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.7</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4311,7 +4349,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 15115-2022</t>
+          <t>A 12094-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4325,10 +4363,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44658</v>
+        <v>44636</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4341,7 +4379,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>6.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4384,7 +4422,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1527-2022</t>
+          <t>A 15115-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4398,10 +4436,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44573</v>
+        <v>44658</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4414,7 +4452,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4457,7 +4495,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14518-2022</t>
+          <t>A 1527-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4471,10 +4509,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44656</v>
+        <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4487,7 +4525,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4530,7 +4568,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 53782-2021</t>
+          <t>A 14518-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4544,10 +4582,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44463</v>
+        <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4559,13 +4597,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4608,7 +4641,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11252-2022</t>
+          <t>A 53782-2021</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4622,10 +4655,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44629</v>
+        <v>44463</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4637,8 +4670,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4681,7 +4719,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 1424-2022</t>
+          <t>A 11252-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4695,10 +4733,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44573</v>
+        <v>44629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4711,7 +4749,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4754,7 +4792,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 4927-2022</t>
+          <t>A 1424-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4768,10 +4806,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44593</v>
+        <v>44573</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4784,7 +4822,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4827,7 +4865,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 54230-2022</t>
+          <t>A 4927-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4841,10 +4879,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44881</v>
+        <v>44593</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4900,7 +4938,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6996-2022</t>
+          <t>A 54230-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4914,10 +4952,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44603</v>
+        <v>44881</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4929,13 +4967,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4978,7 +5011,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56581-2021</t>
+          <t>A 6996-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4992,10 +5025,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44480</v>
+        <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5007,8 +5040,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5051,7 +5089,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 58100-2021</t>
+          <t>A 56581-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5065,10 +5103,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44487</v>
+        <v>44480</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5081,7 +5119,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5124,7 +5162,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7125-2022</t>
+          <t>A 58100-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5138,10 +5176,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44603</v>
+        <v>44487</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5154,7 +5192,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5197,7 +5235,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7138-2022</t>
+          <t>A 7125-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5214,7 +5252,7 @@
         <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5227,7 +5265,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5270,7 +5308,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 24971-2022</t>
+          <t>A 7138-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5284,10 +5322,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44728</v>
+        <v>44603</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5300,7 +5338,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5343,7 +5381,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 24971-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5357,10 +5395,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44753</v>
+        <v>44728</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5373,7 +5411,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5416,7 +5454,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 29424-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5430,10 +5468,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45687</v>
+        <v>44753</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5446,7 +5484,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5489,7 +5527,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5503,10 +5541,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45597</v>
+        <v>45687</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5518,13 +5556,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5584,7 +5617,7 @@
         <v>44607</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5657,7 +5690,7 @@
         <v>45590</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5730,7 +5763,7 @@
         <v>45540</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5803,7 +5836,7 @@
         <v>45433</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5876,7 +5909,7 @@
         <v>44690</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5949,7 +5982,7 @@
         <v>44970</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6022,7 +6055,7 @@
         <v>45148</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6095,7 +6128,7 @@
         <v>44601</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6168,7 +6201,7 @@
         <v>44957</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6241,7 +6274,7 @@
         <v>45254</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6297,7 +6330,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6311,10 +6344,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45590</v>
+        <v>45020</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6327,7 +6360,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6370,7 +6403,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6384,10 +6417,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45020</v>
+        <v>45590</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6400,7 +6433,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6460,7 +6493,7 @@
         <v>45028</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6516,7 +6549,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6530,10 +6563,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45344</v>
+        <v>45189</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6546,7 +6579,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6589,7 +6622,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6603,10 +6636,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44749</v>
+        <v>45344</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6619,7 +6652,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6662,7 +6695,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6676,10 +6709,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45719</v>
+        <v>45597</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6691,8 +6724,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6735,7 +6773,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 29008-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6749,10 +6787,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45189</v>
+        <v>44749</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6765,7 +6803,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6808,7 +6846,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6822,10 +6860,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44949</v>
+        <v>45719</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6838,7 +6876,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6881,7 +6919,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 3280-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6895,10 +6933,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45176</v>
+        <v>44949</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6911,7 +6949,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6954,7 +6992,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6968,10 +7006,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45336</v>
+        <v>45176</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6984,7 +7022,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7027,7 +7065,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 6022-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7041,10 +7079,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44573</v>
+        <v>45336</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7057,7 +7095,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7100,7 +7138,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7114,10 +7152,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45202</v>
+        <v>44573</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7130,7 +7168,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7173,7 +7211,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7187,10 +7225,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44833</v>
+        <v>45204</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7203,7 +7241,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7246,7 +7284,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7260,10 +7298,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45204</v>
+        <v>45183</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7276,7 +7314,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7319,7 +7357,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7336,7 +7374,7 @@
         <v>45183</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7349,7 +7387,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7392,7 +7430,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7406,10 +7444,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45183</v>
+        <v>44592</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7422,7 +7460,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>11.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7465,7 +7503,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 47205-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7479,10 +7517,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45271</v>
+        <v>45202</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7494,13 +7532,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>11.1</v>
+        <v>4.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7543,7 +7576,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7557,10 +7590,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45093</v>
+        <v>45271</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7572,8 +7605,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>11.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7616,7 +7654,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7630,10 +7668,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44592</v>
+        <v>45093</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7646,7 +7684,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>11.6</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7689,7 +7727,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7703,10 +7741,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45158</v>
+        <v>44833</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7719,7 +7757,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7762,7 +7800,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7776,10 +7814,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44593</v>
+        <v>45158</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7792,7 +7830,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7835,7 +7873,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7849,10 +7887,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44974</v>
+        <v>44593</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7865,7 +7903,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7908,7 +7946,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 8143-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7922,10 +7960,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45036</v>
+        <v>44974</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7938,7 +7976,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7998,7 +8036,7 @@
         <v>44799</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8054,7 +8092,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8068,10 +8106,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44894</v>
+        <v>45036</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8084,7 +8122,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8127,7 +8165,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 58262-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8141,10 +8179,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44587</v>
+        <v>44894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8157,7 +8195,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8200,7 +8238,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8214,10 +8252,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44749</v>
+        <v>44587</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8230,7 +8268,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8273,7 +8311,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8287,10 +8325,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45404</v>
+        <v>44749</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8303,7 +8341,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8363,7 +8401,7 @@
         <v>45624</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8419,7 +8457,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8433,10 +8471,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45601</v>
+        <v>45404</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8449,7 +8487,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8509,7 +8547,7 @@
         <v>44949</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8565,7 +8603,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8579,10 +8617,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45357</v>
+        <v>45601</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8595,7 +8633,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8638,7 +8676,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 21396-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8652,10 +8690,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45035</v>
+        <v>45782</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8667,13 +8705,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8716,7 +8749,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 8890-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8730,10 +8763,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45258</v>
+        <v>45357</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8746,7 +8779,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.5</v>
+        <v>7.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8789,7 +8822,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8803,10 +8836,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44937</v>
+        <v>45793</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8819,7 +8852,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8862,7 +8895,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 17296-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8876,10 +8909,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44937</v>
+        <v>45035</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8891,8 +8924,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8935,7 +8973,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8949,10 +8987,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44965</v>
+        <v>44937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8965,7 +9003,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9008,7 +9046,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9022,10 +9060,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44883</v>
+        <v>44937</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9038,7 +9076,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9081,7 +9119,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 60285-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9095,10 +9133,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45992</v>
+        <v>45258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9111,7 +9149,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9154,7 +9192,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20246-2026</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9168,10 +9206,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46139</v>
+        <v>45992</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9183,13 +9221,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9232,7 +9265,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20248-2026</t>
+          <t>A 20246-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9249,7 +9282,7 @@
         <v>46139</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9267,7 +9300,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9310,7 +9343,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 20248-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9324,10 +9357,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45176</v>
+        <v>46139</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9339,8 +9372,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9383,7 +9421,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 6357-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9397,10 +9435,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45205</v>
+        <v>44965</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9412,13 +9450,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9461,7 +9494,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9475,10 +9508,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44979</v>
+        <v>45901</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9491,7 +9524,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9534,7 +9567,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 41839-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9548,10 +9581,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45099</v>
+        <v>45902</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9564,7 +9597,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9607,7 +9640,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 41843-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9621,10 +9654,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44942</v>
+        <v>45902</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9637,7 +9670,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9680,7 +9713,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 46186-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9694,10 +9727,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45354</v>
+        <v>45581</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9710,7 +9743,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9753,7 +9786,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9767,10 +9800,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45581</v>
+        <v>44883</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9783,7 +9816,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9826,7 +9859,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 41889-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9836,14 +9869,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44896</v>
+        <v>45176</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9856,7 +9889,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9899,7 +9932,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 20307-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9913,10 +9946,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45093</v>
+        <v>46139</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9929,7 +9962,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9972,7 +10005,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 48158-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9986,10 +10019,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45093</v>
+        <v>45205</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10001,8 +10034,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10045,7 +10083,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10059,10 +10097,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45901</v>
+        <v>44979</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10075,7 +10113,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10118,7 +10156,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41839-2025</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10132,10 +10170,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45902</v>
+        <v>45099</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10148,7 +10186,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10191,7 +10229,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41843-2025</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10205,10 +10243,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45902</v>
+        <v>44942</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10221,7 +10259,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10264,7 +10302,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10278,10 +10316,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44585</v>
+        <v>45926</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10294,7 +10332,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10337,7 +10375,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 20307-2026</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10351,10 +10389,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46139</v>
+        <v>45926</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10367,7 +10405,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10410,7 +10448,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10424,10 +10462,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44903</v>
+        <v>45354</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10440,7 +10478,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10483,7 +10521,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10497,10 +10535,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44985</v>
+        <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10513,7 +10551,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10556,7 +10594,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10570,10 +10608,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45481</v>
+        <v>45929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10586,7 +10624,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10629,7 +10667,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10643,10 +10681,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45228</v>
+        <v>45926</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10659,7 +10697,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10702,7 +10740,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10716,10 +10754,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45167</v>
+        <v>45926</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10732,7 +10770,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10775,7 +10813,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 57513-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10785,14 +10823,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45926</v>
+        <v>44896</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10805,7 +10843,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10848,7 +10886,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 26811-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10862,10 +10900,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45926</v>
+        <v>45093</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10878,7 +10916,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10921,7 +10959,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 26821-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10935,10 +10973,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45929</v>
+        <v>45093</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10951,7 +10989,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11011,7 +11049,7 @@
         <v>46141</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11089,7 +11127,7 @@
         <v>45782</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11145,7 +11183,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11159,10 +11197,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44897</v>
+        <v>44585</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11175,7 +11213,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11218,7 +11256,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 53786-2021</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11232,10 +11270,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44463</v>
+        <v>46147</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11249,11 +11287,11 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11296,7 +11334,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11306,14 +11344,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45170</v>
+        <v>44903</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11326,7 +11364,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11369,7 +11407,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11383,10 +11421,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45929</v>
+        <v>46154</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11399,7 +11437,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11442,7 +11480,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11456,10 +11494,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45926</v>
+        <v>46154</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11472,7 +11510,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11515,7 +11553,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11529,10 +11567,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45926</v>
+        <v>46155</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11544,8 +11582,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11588,7 +11631,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 9971-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11602,10 +11645,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45761</v>
+        <v>44985</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11618,7 +11661,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11661,7 +11704,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11675,10 +11718,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45411</v>
+        <v>45481</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11691,7 +11734,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11734,7 +11777,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11748,10 +11791,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45685</v>
+        <v>45228</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11764,7 +11807,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11807,7 +11850,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11821,10 +11864,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45685</v>
+        <v>45167</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11837,7 +11880,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11880,7 +11923,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11894,10 +11937,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45632</v>
+        <v>44897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11910,7 +11953,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11953,7 +11996,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 53786-2021</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11967,10 +12010,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44852</v>
+        <v>44463</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11982,8 +12025,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12026,7 +12074,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 40728-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12036,14 +12084,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45215</v>
+        <v>45170</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12056,7 +12104,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12099,7 +12147,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12113,10 +12161,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46147</v>
+        <v>45761</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12128,13 +12176,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12177,7 +12220,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12191,10 +12234,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45352</v>
+        <v>45411</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12207,7 +12250,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12250,7 +12293,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12264,10 +12307,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45258</v>
+        <v>45685</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12280,7 +12323,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12323,7 +12366,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12337,10 +12380,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44980</v>
+        <v>45685</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12353,7 +12396,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12396,7 +12439,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 56097-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12410,10 +12453,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44587</v>
+        <v>45973</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12426,7 +12469,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12469,7 +12512,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 58247-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12483,10 +12526,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44725</v>
+        <v>45632</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12499,7 +12542,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>8.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12542,7 +12585,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12556,10 +12599,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46154</v>
+        <v>44852</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12572,7 +12615,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12615,7 +12658,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 56097-2025</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12629,10 +12672,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45973</v>
+        <v>45215</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12645,7 +12688,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12688,7 +12731,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 8328-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12702,10 +12745,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45565</v>
+        <v>45352</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12718,7 +12761,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12761,7 +12804,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12775,10 +12818,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45040</v>
+        <v>45986</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12790,13 +12833,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12839,7 +12877,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12853,10 +12891,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46154</v>
+        <v>45258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12912,7 +12950,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 22297-2026</t>
+          <t>A 58749-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12926,10 +12964,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46154</v>
+        <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12942,7 +12980,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12985,7 +13023,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12999,10 +13037,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46155</v>
+        <v>45989</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13020,7 +13058,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13063,7 +13101,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 9292-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13077,10 +13115,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45986</v>
+        <v>44980</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13093,7 +13131,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.3</v>
+        <v>6.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13136,7 +13174,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13150,10 +13188,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44728</v>
+        <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13166,7 +13204,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13209,7 +13247,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13223,10 +13261,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45339</v>
+        <v>45992</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13239,7 +13277,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13282,7 +13320,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 58749-2025</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13296,10 +13334,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45986</v>
+        <v>44587</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13355,7 +13393,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13369,10 +13407,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45989</v>
+        <v>44725</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13384,13 +13422,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13433,7 +13466,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13447,10 +13480,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44652</v>
+        <v>45999</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13462,8 +13495,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13506,7 +13544,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13520,10 +13558,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45992</v>
+        <v>45999</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13535,8 +13573,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13579,7 +13622,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 26049-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13593,10 +13636,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45036</v>
+        <v>46177</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13608,8 +13651,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13652,7 +13700,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 7266-2023</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13666,10 +13714,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44970</v>
+        <v>46006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13682,7 +13730,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13725,7 +13773,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 252-2023</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13739,10 +13787,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44922</v>
+        <v>46006</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13755,7 +13803,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13798,7 +13846,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 45783-2023</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13808,14 +13856,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45195</v>
+        <v>46006</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13828,7 +13876,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13871,7 +13919,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 7582-2023</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13885,10 +13933,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44972</v>
+        <v>46006</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13901,7 +13949,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13944,7 +13992,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 42623-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13958,10 +14006,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45999</v>
+        <v>45565</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13973,13 +14021,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14022,7 +14065,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 17937-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14036,10 +14079,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45999</v>
+        <v>45040</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14057,7 +14100,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14100,7 +14143,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 54812-2022</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14110,14 +14153,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44883</v>
+        <v>46020</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14130,7 +14173,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14173,7 +14216,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14187,10 +14230,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14203,7 +14246,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14246,7 +14289,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14260,10 +14303,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46006</v>
+        <v>46019</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14276,7 +14319,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.8</v>
+        <v>0.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14319,7 +14362,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14333,10 +14376,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14349,7 +14392,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14392,7 +14435,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 290-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14406,10 +14449,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14422,7 +14465,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14465,7 +14508,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 43151-2023</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14479,10 +14522,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45183</v>
+        <v>46027</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14495,7 +14538,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14538,7 +14581,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 31862-2022</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14552,10 +14595,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44777</v>
+        <v>46027</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14611,7 +14654,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 560-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14625,10 +14668,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46020</v>
+        <v>46029</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14640,8 +14683,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14684,7 +14732,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 57864-2022</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14698,10 +14746,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44899</v>
+        <v>44728</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14714,7 +14762,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14757,7 +14805,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14771,10 +14819,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46020</v>
+        <v>45339</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14787,7 +14835,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14830,7 +14878,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 15779-2024</t>
+          <t>A 260-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14844,10 +14892,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45404</v>
+        <v>46027</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14860,7 +14908,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14903,7 +14951,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 50041-2023</t>
+          <t>A 14429-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14917,10 +14965,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45215</v>
+        <v>44652</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14933,7 +14981,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14976,7 +15024,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 17585-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14990,10 +15038,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46019</v>
+        <v>45036</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15049,7 +15097,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 4965-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15063,10 +15111,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46020</v>
+        <v>46049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15079,7 +15127,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15122,7 +15170,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 290-2026</t>
+          <t>A 27525-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15136,10 +15184,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46027</v>
+        <v>46189</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15152,7 +15200,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15195,7 +15243,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15209,10 +15257,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46027</v>
+        <v>44970</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15225,7 +15273,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15268,7 +15316,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 6160-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15282,10 +15330,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46027</v>
+        <v>46055</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15298,7 +15346,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15341,7 +15389,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 4331-2023</t>
+          <t>A 6162-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15355,10 +15403,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44953</v>
+        <v>46055</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15371,7 +15419,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15414,7 +15462,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 6161-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15428,10 +15476,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46029</v>
+        <v>46055</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15443,13 +15491,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15492,7 +15535,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 42401-2022</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15506,10 +15549,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44830</v>
+        <v>44922</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15522,7 +15565,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15565,7 +15608,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 28119-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15579,10 +15622,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46170</v>
+        <v>46195</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15595,7 +15638,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.3</v>
+        <v>7.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15638,7 +15681,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 59741-2023</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15648,14 +15691,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45257</v>
+        <v>45195</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15668,7 +15711,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15711,7 +15754,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15725,10 +15768,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46027</v>
+        <v>44972</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15741,7 +15784,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15784,7 +15827,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 52223-2021</t>
+          <t>A 28093-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15798,10 +15841,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44463</v>
+        <v>46195</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15813,13 +15856,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>10.8</v>
+        <v>0.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15862,7 +15900,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8685-2022</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15872,14 +15910,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44613</v>
+        <v>44883</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15892,7 +15930,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15935,7 +15973,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 43516-2024</t>
+          <t>A 8845-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15949,10 +15987,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45569</v>
+        <v>46066</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15964,13 +16002,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I199" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16013,7 +16046,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 43518-2024</t>
+          <t>A 8818-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16027,10 +16060,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45569</v>
+        <v>46066</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16042,13 +16075,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16091,7 +16119,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 21399-2023</t>
+          <t>A 8823-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16105,10 +16133,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45063</v>
+        <v>46066</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16121,7 +16149,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16164,7 +16192,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 14417-2024</t>
+          <t>A 8822-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16178,10 +16206,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45394</v>
+        <v>46066</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16194,7 +16222,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16237,7 +16265,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 17717-2025</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16251,10 +16279,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45758</v>
+        <v>45183</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16267,7 +16295,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16310,7 +16338,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 34357-2023</t>
+          <t>A 10575-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16324,10 +16352,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45133</v>
+        <v>46077</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16340,7 +16368,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16383,7 +16411,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 26049-2026</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16397,10 +16425,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46177</v>
+        <v>44777</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16412,13 +16440,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16461,7 +16484,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 21483-2023</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16475,10 +16498,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45063</v>
+        <v>44899</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16491,7 +16514,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16534,7 +16557,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38431-2024</t>
+          <t>A 15779-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16548,10 +16571,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45546</v>
+        <v>45404</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16564,7 +16587,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16607,7 +16630,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 38438-2024</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16621,10 +16644,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45546</v>
+        <v>45215</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16637,7 +16660,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16680,7 +16703,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 10135-2025</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16694,10 +16717,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45719</v>
+        <v>44953</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16710,7 +16733,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>10.3</v>
+        <v>1.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16753,7 +16776,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16767,10 +16790,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46055</v>
+        <v>44830</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16783,7 +16806,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16826,7 +16849,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 33177-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16840,10 +16863,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46055</v>
+        <v>46245</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16856,7 +16879,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.9</v>
+        <v>4.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16899,7 +16922,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 1974-2022</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16913,10 +16936,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44575</v>
+        <v>45257</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16929,7 +16952,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16972,7 +16995,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 52223-2021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16986,10 +17009,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46055</v>
+        <v>44463</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17001,8 +17024,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>2.9</v>
+        <v>10.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17045,7 +17073,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 41314-2023</t>
+          <t>A 8685-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17059,10 +17087,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45173</v>
+        <v>44613</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17075,7 +17103,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17118,7 +17146,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 23827-2022</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17132,10 +17160,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44722</v>
+        <v>45569</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17147,8 +17175,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17191,7 +17224,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17205,10 +17238,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46066</v>
+        <v>45569</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17220,8 +17253,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17264,7 +17302,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 15078-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17278,10 +17316,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46066</v>
+        <v>46105</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17294,7 +17332,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17337,7 +17375,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 8823-2026</t>
+          <t>A 15138-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17351,10 +17389,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46066</v>
+        <v>46105</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17367,7 +17405,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17410,7 +17448,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 21399-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17424,10 +17462,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46066</v>
+        <v>45063</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17440,7 +17478,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17483,7 +17521,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 21487-2023</t>
+          <t>A 15096-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17497,10 +17535,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45063</v>
+        <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17513,7 +17551,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17556,7 +17594,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 7646-2025</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17570,10 +17608,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45705</v>
+        <v>45394</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17586,7 +17624,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17629,7 +17667,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 7647-2025</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17643,10 +17681,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45705</v>
+        <v>45758</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17659,7 +17697,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17702,7 +17740,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17716,10 +17754,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46077</v>
+        <v>45133</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17732,7 +17770,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17775,7 +17813,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 45873-2023</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17789,10 +17827,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45195</v>
+        <v>45063</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17805,7 +17843,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>15.8</v>
+        <v>2.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17848,7 +17886,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 57144-2024</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17862,10 +17900,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45629</v>
+        <v>45546</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17878,7 +17916,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17921,7 +17959,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 3276-2023</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17935,10 +17973,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44949</v>
+        <v>45546</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17951,7 +17989,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17994,7 +18032,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 50992-2023</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18008,10 +18046,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45218</v>
+        <v>45719</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18023,13 +18061,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>10.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18072,7 +18105,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 62048-2022</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18086,10 +18119,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44918</v>
+        <v>44575</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18102,7 +18135,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18145,7 +18178,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 10120-2025</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18159,10 +18192,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45719</v>
+        <v>45173</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18175,7 +18208,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18218,7 +18251,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18232,10 +18265,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46049</v>
+        <v>44722</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18248,7 +18281,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18291,7 +18324,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 21397-2023</t>
+          <t>A 19925-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18305,10 +18338,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45063</v>
+        <v>45433</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18321,7 +18354,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18364,7 +18397,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 21487-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18378,10 +18411,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46189</v>
+        <v>45063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18394,7 +18427,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18437,7 +18470,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 14082-2023</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18451,10 +18484,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45009</v>
+        <v>45705</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18467,7 +18500,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18510,7 +18543,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18524,10 +18557,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46195</v>
+        <v>45705</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18540,7 +18573,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>7.7</v>
+        <v>0.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18583,7 +18616,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18597,10 +18630,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46195</v>
+        <v>45195</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18613,7 +18646,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>15.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18656,7 +18689,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18670,10 +18703,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46105</v>
+        <v>45629</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18686,7 +18719,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18729,7 +18762,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 3276-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18743,10 +18776,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46105</v>
+        <v>44949</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18759,7 +18792,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18802,7 +18835,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 15096-2026</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18816,10 +18849,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46105</v>
+        <v>45218</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18831,8 +18864,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18875,7 +18913,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 4047-2023</t>
+          <t>A 30523-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18889,10 +18927,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44952</v>
+        <v>46210</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18905,7 +18943,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18948,7 +18986,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 47962-2023</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18962,10 +19000,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45204</v>
+        <v>44918</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18978,7 +19016,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.3</v>
+        <v>5.5</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19021,7 +19059,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 33076-2026</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19035,10 +19073,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46245</v>
+        <v>45719</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19051,7 +19089,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19094,7 +19132,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 33090-2026</t>
+          <t>A 21397-2023</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19108,10 +19146,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46245</v>
+        <v>45063</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19124,7 +19162,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19167,7 +19205,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 33177-2026</t>
+          <t>A 34488-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19181,10 +19219,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19197,7 +19235,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19240,7 +19278,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 49345-2023</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19254,10 +19292,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45211</v>
+        <v>45009</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19270,7 +19308,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19313,7 +19351,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 49348-2023</t>
+          <t>A 34489-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19327,10 +19365,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45211</v>
+        <v>46255</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19343,7 +19381,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19386,7 +19424,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 54849-2023</t>
+          <t>A 30964-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19396,14 +19434,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45236</v>
+        <v>46213</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19416,7 +19454,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19459,7 +19497,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19473,10 +19511,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45433</v>
+        <v>44952</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19489,7 +19527,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.4</v>
+        <v>6.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19532,7 +19570,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19546,10 +19584,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45782</v>
+        <v>45204</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19562,7 +19600,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19605,7 +19643,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 45377-2023</t>
+          <t>A 35740-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19619,10 +19657,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45193</v>
+        <v>46265</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19635,7 +19673,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19678,7 +19716,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 47354-2023</t>
+          <t>A 35806-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19692,10 +19730,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45202</v>
+        <v>46265</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19708,7 +19746,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19751,7 +19789,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 34572-2024</t>
+          <t>A 35924-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19765,10 +19803,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45526</v>
+        <v>46266</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19781,7 +19819,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19824,7 +19862,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19838,10 +19876,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45793</v>
+        <v>45211</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19854,7 +19892,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19897,7 +19935,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 49931-2024</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19911,10 +19949,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45597</v>
+        <v>45211</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19926,13 +19964,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19975,7 +20008,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 54785-2022</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19989,10 +20022,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44883</v>
+        <v>45236</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20005,7 +20038,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>8.5</v>
+        <v>1.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20048,7 +20081,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 6522-2025</t>
+          <t>A 36555-2026</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20062,10 +20095,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45699</v>
+        <v>46269</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20078,7 +20111,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20121,7 +20154,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 3276-2024</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20135,10 +20168,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45317</v>
+        <v>45193</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20151,7 +20184,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20194,7 +20227,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 19747-2024</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20208,10 +20241,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45432</v>
+        <v>45202</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20224,7 +20257,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20267,7 +20300,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 30523-2026</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20281,10 +20314,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46210</v>
+        <v>45526</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20297,7 +20330,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20340,7 +20373,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 60242-2022</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20354,10 +20387,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44910</v>
+        <v>45597</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20369,8 +20402,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I259" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20413,7 +20451,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 9337-2022</t>
+          <t>A 54785-2022</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20427,10 +20465,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44616</v>
+        <v>44883</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20443,7 +20481,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20486,7 +20524,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 34488-2026</t>
+          <t>A 6522-2025</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20500,10 +20538,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46255</v>
+        <v>45699</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20516,7 +20554,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20559,7 +20597,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 34616-2026</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20573,10 +20611,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46255</v>
+        <v>45317</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20589,7 +20627,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20632,7 +20670,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 21233-2023</t>
+          <t>A 19747-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20646,10 +20684,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45062</v>
+        <v>45432</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20662,7 +20700,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20705,7 +20743,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 34489-2026</t>
+          <t>A 38060-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20719,10 +20757,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46255</v>
+        <v>46280</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20735,7 +20773,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20778,7 +20816,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 19745-2024</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20792,10 +20830,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45432</v>
+        <v>44910</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20808,7 +20846,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20851,7 +20889,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 47679-2024</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20865,10 +20903,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45588</v>
+        <v>44616</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20881,7 +20919,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>5.5</v>
+        <v>0.6</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20924,7 +20962,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20934,14 +20972,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>46213</v>
+        <v>45062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20954,7 +20992,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20997,7 +21035,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 15660-2024</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21011,10 +21049,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45404</v>
+        <v>45432</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21027,7 +21065,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21070,7 +21108,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 66424-2021</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21084,10 +21122,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>44518</v>
+        <v>45588</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21100,7 +21138,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21143,7 +21181,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 39583-2022</t>
+          <t>A 22297-2026</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21157,10 +21195,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>44818</v>
+        <v>46154</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21173,7 +21211,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21216,7 +21254,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 10122-2025</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21230,10 +21268,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45719</v>
+        <v>45404</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21246,7 +21284,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21289,7 +21327,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 65113-2023</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21303,10 +21341,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45287</v>
+        <v>44518</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21319,7 +21357,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21362,7 +21400,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21376,10 +21414,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46265</v>
+        <v>44818</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21392,7 +21430,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21435,7 +21473,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 35806-2026</t>
+          <t>A 10122-2025</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21449,10 +21487,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>46265</v>
+        <v>45719</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21465,7 +21503,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21508,7 +21546,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 33090-2026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21522,10 +21560,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46266</v>
+        <v>46245</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21538,7 +21576,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21581,7 +21619,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 56830-2024</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21595,10 +21633,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45628</v>
+        <v>45287</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21611,7 +21649,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21654,7 +21692,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 36555-2026</t>
+          <t>A 33076-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21668,10 +21706,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>46269</v>
+        <v>46245</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21684,7 +21722,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21727,7 +21765,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 38060-2026</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21741,10 +21779,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>46280</v>
+        <v>45628</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21757,7 +21795,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -21817,7 +21855,7 @@
         <v>45247</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21890,7 +21928,7 @@
         <v>45797</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21963,7 +22001,7 @@
         <v>45310</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22036,7 +22074,7 @@
         <v>44491</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22109,7 +22147,7 @@
         <v>45790</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22182,7 +22220,7 @@
         <v>45699</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22255,7 +22293,7 @@
         <v>44140</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22328,7 +22366,7 @@
         <v>43951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22401,7 +22439,7 @@
         <v>44735</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22474,7 +22512,7 @@
         <v>45300</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22547,7 +22585,7 @@
         <v>45708</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22620,7 +22658,7 @@
         <v>46076</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 43506-2024</t>
+          <t>A 43507-2024</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -641,18 +641,133 @@
         <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>7</v>
       </c>
       <c r="T2" t="n">
+        <v>10</v>
+      </c>
+      <c r="U2" t="n">
+        <v>9</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Mindre hackspett
+Talltita
+Blåmossa
+Gullgröppa
+Spillkråka
+Myggblomster
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 43507-2024 artfynd.xlsx", "A 43507-2024")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 43507-2024 karta.png", "A 43507-2024")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 43507-2024 georefererad karta.tif", "A 43507-2024")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 43507-2024 FSC-klagomål.docx", "A 43507-2024")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 43507-2024 FSC-klagomål mail.docx", "A 43507-2024")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 43507-2024 tillsynsbegäran.docx", "A 43507-2024")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 43507-2024 tillsynsbegäran mail.docx", "A 43507-2024")</f>
+        <v/>
+      </c>
+      <c r="AE2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 43507-2024 prioriterade fågelarter.docx", "A 43507-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A 43506-2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45569</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="n">
         <v>22</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>22</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Talltita
@@ -663,158 +778,43 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 43506-2024 artfynd.xlsx", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 43506-2024 karta.png", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 43506-2024 georefererad karta.tif", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 43506-2024 karta knärot.png", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 43506-2024 FSC-klagomål.docx", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 43506-2024 FSC-klagomål mail.docx", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 43506-2024 tillsynsbegäran.docx", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 43506-2024 tillsynsbegäran mail.docx", "A 43506-2024")</f>
         <v/>
       </c>
-      <c r="AE2">
+      <c r="AE3">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 43506-2024 prioriterade fågelarter.docx", "A 43506-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 43507-2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45569</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>10</v>
-      </c>
-      <c r="U3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Mindre hackspett
-Talltita
-Blåmossa
-Gullgröppa
-Spillkråka
-Myggblomster
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 43507-2024 artfynd.xlsx", "A 43507-2024")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 43507-2024 karta.png", "A 43507-2024")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 43507-2024 georefererad karta.tif", "A 43507-2024")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 43507-2024 FSC-klagomål.docx", "A 43507-2024")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 43507-2024 FSC-klagomål mail.docx", "A 43507-2024")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 43507-2024 tillsynsbegäran.docx", "A 43507-2024")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 43507-2024 tillsynsbegäran mail.docx", "A 43507-2024")</f>
-        <v/>
-      </c>
-      <c r="AE3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 43507-2024 prioriterade fågelarter.docx", "A 43507-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59356-2023</t>
+          <t>A 46766-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45253</v>
+        <v>45926</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,16 +1186,11 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -1207,30 +1202,148 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>1</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>8</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Bronshjon
+Flagellkvastmossa
+Stubbspretmossa
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 59356-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45253</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Ask
 Bukspolsnäcka
@@ -1239,148 +1352,35 @@
 Noshornsoxe</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 59356-2023 artfynd.xlsx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 59356-2023 karta.png", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 59356-2023 georefererad karta.tif", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 59356-2023 FSC-klagomål.docx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 59356-2023 FSC-klagomål mail.docx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 59356-2023 tillsynsbegäran.docx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 59356-2023 tillsynsbegäran mail.docx", "A 59356-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 46766-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>8</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Bronshjon
-Flagellkvastmossa
-Stubbspretmossa
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>44571</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46255</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>46018</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1543-2022</t>
+          <t>A 23067-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44573</v>
+        <v>45790</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2302,7 +2302,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2314,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2330,42 +2330,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 23067-2025 artfynd.xlsx", "A 23067-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 23067-2025 karta.png", "A 23067-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 23067-2025 georefererad karta.tif", "A 23067-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 23067-2025 FSC-klagomål.docx", "A 23067-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 23067-2025 FSC-klagomål mail.docx", "A 23067-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 23067-2025 tillsynsbegäran.docx", "A 23067-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 23067-2025 tillsynsbegäran mail.docx", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 23067-2025 prioriterade fågelarter.docx", "A 23067-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53785-2021</t>
+          <t>A 4051-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2379,10 +2383,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44463</v>
+        <v>44952</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2394,37 +2398,32 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2436,39 +2435,39 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 53785-2021 artfynd.xlsx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 53785-2021 karta.png", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 53785-2021 georefererad karta.tif", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 53785-2021 FSC-klagomål.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 53785-2021 FSC-klagomål mail.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 53785-2021 tillsynsbegäran.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 53785-2021 tillsynsbegäran mail.docx", "A 53785-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
         <v/>
       </c>
     </row>
@@ -2492,7 +2491,7 @@
         <v>45323</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2597,7 +2596,7 @@
         <v>45331</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2685,7 +2684,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 40874-2023</t>
+          <t>A 11749-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2699,10 +2698,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45173</v>
+        <v>44994</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2715,7 +2714,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2724,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2739,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2755,575 +2754,576 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
+          <t>Adam och eva</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53785-2021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44463</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 53785-2021 artfynd.xlsx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 53785-2021 karta.png", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 53785-2021 georefererad karta.tif", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 53785-2021 FSC-klagomål.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 53785-2021 FSC-klagomål mail.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 53785-2021 tillsynsbegäran.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 53785-2021 tillsynsbegäran mail.docx", "A 53785-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 1543-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44573</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 18758-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Z24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 40874-2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 11749-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44994</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J22" t="n">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 27253-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R26" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 18758-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45043</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Z23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 27253-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="Z24">
+      <c r="Z26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 4051-2023</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 23067-2025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>45790</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 23067-2025 artfynd.xlsx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 23067-2025 karta.png", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 23067-2025 georefererad karta.tif", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 23067-2025 FSC-klagomål.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 23067-2025 FSC-klagomål mail.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 23067-2025 tillsynsbegäran.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 23067-2025 tillsynsbegäran mail.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 23067-2025 prioriterade fågelarter.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>44613</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>44749</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>44869</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3563,7 +3563,7 @@
         <v>44687</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>44852</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>44536</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>44613</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>44531</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 69261-2021</t>
+          <t>A 54231-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3998,10 +3998,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44531</v>
+        <v>44881</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 54231-2022</t>
+          <t>A 69261-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4071,10 +4071,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44881</v>
+        <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4147,7 +4147,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>44564</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44613</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
         <v>44636</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4439,7 +4439,7 @@
         <v>44658</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>44656</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>44463</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>44629</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44573</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>44593</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54230-2022</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4952,10 +4952,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44881</v>
+        <v>45758</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 6996-2022</t>
+          <t>A 7138-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5028,7 +5028,7 @@
         <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5040,13 +5040,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5089,7 +5084,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56581-2021</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5103,10 +5098,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44480</v>
+        <v>45158</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5119,7 +5114,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5162,7 +5157,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 58100-2021</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5176,10 +5171,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44487</v>
+        <v>45189</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5192,7 +5187,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.3</v>
+        <v>4.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5235,7 +5230,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7125-2022</t>
+          <t>A 54230-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5249,10 +5244,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44603</v>
+        <v>44881</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5265,7 +5260,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5308,7 +5303,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7138-2022</t>
+          <t>A 24971-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5322,10 +5317,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44603</v>
+        <v>44728</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5338,7 +5333,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5381,7 +5376,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 24971-2022</t>
+          <t>A 57862-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5395,10 +5390,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44728</v>
+        <v>45247</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5411,7 +5406,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5454,7 +5449,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 6996-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5468,10 +5463,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44753</v>
+        <v>44603</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5483,8 +5478,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5527,7 +5527,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 35659-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5541,10 +5541,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45687</v>
+        <v>44799</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5600,7 +5600,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7634-2022</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5614,10 +5614,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44607</v>
+        <v>45344</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 48243-2024</t>
+          <t>A 56581-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45590</v>
+        <v>44480</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5746,7 +5746,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37421-2024</t>
+          <t>A 58100-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5760,10 +5760,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45540</v>
+        <v>44487</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5819,7 +5819,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 19937-2024</t>
+          <t>A 7125-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45433</v>
+        <v>44603</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>11.9</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18961-2022</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44690</v>
+        <v>45228</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5965,7 +5965,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 7254-2023</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5979,10 +5979,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44970</v>
+        <v>45271</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5994,8 +5994,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.8</v>
+        <v>11.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6038,7 +6043,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 35908-2023</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6052,10 +6057,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45148</v>
+        <v>45687</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6068,7 +6073,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6111,7 +6116,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6548-2022</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6125,10 +6130,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44601</v>
+        <v>45761</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6141,7 +6146,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6184,7 +6189,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4856-2023</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6198,10 +6203,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44957</v>
+        <v>45063</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6214,7 +6219,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6257,7 +6262,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59516-2023</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6267,14 +6272,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45254</v>
+        <v>45719</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6287,7 +6292,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6330,7 +6335,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6344,10 +6349,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45020</v>
+        <v>45215</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6360,7 +6365,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6403,7 +6408,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6417,10 +6422,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45590</v>
+        <v>45339</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6433,7 +6438,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6476,7 +6481,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16342-2023</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6486,14 +6491,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45028</v>
+        <v>44883</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6506,7 +6511,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6549,7 +6554,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6563,10 +6568,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45189</v>
+        <v>45204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6579,7 +6584,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6622,7 +6627,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6636,10 +6641,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45344</v>
+        <v>44910</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6652,7 +6657,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6695,7 +6700,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6709,10 +6714,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45597</v>
+        <v>44585</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6724,13 +6729,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6773,7 +6773,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6787,10 +6787,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44749</v>
+        <v>45705</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45719</v>
+        <v>45705</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6919,7 +6919,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 59516-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6929,14 +6929,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44949</v>
+        <v>45254</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6992,7 +6992,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45176</v>
+        <v>44593</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7065,7 +7065,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7079,10 +7079,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45336</v>
+        <v>45411</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7152,10 +7152,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44573</v>
+        <v>45394</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7211,7 +7211,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 24367-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45204</v>
+        <v>45797</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7284,7 +7284,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45183</v>
+        <v>44883</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7357,7 +7357,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7371,10 +7371,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45183</v>
+        <v>45287</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44592</v>
+        <v>45218</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7459,8 +7459,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7503,7 +7508,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7517,10 +7522,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45202</v>
+        <v>45258</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7533,7 +7538,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7576,7 +7581,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7590,10 +7595,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45271</v>
+        <v>45093</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7605,13 +7610,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>11.1</v>
+        <v>0.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7654,7 +7654,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 2336-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7668,10 +7668,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45093</v>
+        <v>45310</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7727,7 +7727,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 7634-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44833</v>
+        <v>44607</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7757,7 +7757,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7800,7 +7800,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45158</v>
+        <v>45588</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7873,7 +7873,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44593</v>
+        <v>45354</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7946,7 +7946,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44974</v>
+        <v>44833</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8019,7 +8019,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 35659-2022</t>
+          <t>A 41843-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44799</v>
+        <v>45902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8092,7 +8092,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8106,10 +8106,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45036</v>
+        <v>45901</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8165,7 +8165,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 41839-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44894</v>
+        <v>45902</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8238,7 +8238,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8252,10 +8252,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44587</v>
+        <v>44818</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8311,7 +8311,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44749</v>
+        <v>45062</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8384,7 +8384,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 56303-2024</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8398,10 +8398,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45624</v>
+        <v>44922</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8457,7 +8457,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8471,10 +8471,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45404</v>
+        <v>45481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8530,7 +8530,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3267-2023</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8544,10 +8544,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44949</v>
+        <v>44918</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8603,7 +8603,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8617,10 +8617,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45601</v>
+        <v>44899</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8676,7 +8676,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45782</v>
+        <v>44972</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8749,7 +8749,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45357</v>
+        <v>44592</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>7.4</v>
+        <v>11.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8822,7 +8822,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45793</v>
+        <v>45099</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8909,10 +8909,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45035</v>
+        <v>44937</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8924,13 +8924,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8973,7 +8968,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8990,7 +8985,7 @@
         <v>44937</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9003,7 +8998,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9046,7 +9041,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 48243-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9060,10 +9055,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44937</v>
+        <v>45590</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9076,7 +9071,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9119,7 +9114,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9133,10 +9128,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45258</v>
+        <v>45926</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9149,7 +9144,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9192,7 +9187,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9206,10 +9201,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45992</v>
+        <v>45926</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9222,7 +9217,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9265,7 +9260,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 20246-2026</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9279,10 +9274,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46139</v>
+        <v>45176</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9294,13 +9289,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9343,7 +9333,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 20248-2026</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9357,10 +9347,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46139</v>
+        <v>45926</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9372,13 +9362,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9421,7 +9406,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9435,10 +9420,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44965</v>
+        <v>45926</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9451,7 +9436,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9494,7 +9479,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 19937-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9508,10 +9493,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45901</v>
+        <v>45433</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9524,7 +9509,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>11.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9567,7 +9552,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 41839-2025</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9581,10 +9566,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45902</v>
+        <v>45929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9597,7 +9582,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9640,7 +9625,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41843-2025</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9654,10 +9639,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45902</v>
+        <v>45929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9670,7 +9655,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9713,7 +9698,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9727,10 +9712,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45581</v>
+        <v>45404</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9743,7 +9728,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9786,7 +9771,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9800,10 +9785,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44883</v>
+        <v>44616</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9816,7 +9801,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9859,7 +9844,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9873,10 +9858,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45176</v>
+        <v>45569</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9888,8 +9873,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9932,7 +9922,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20307-2026</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9946,10 +9936,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46139</v>
+        <v>45569</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9961,8 +9951,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10005,7 +10000,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45205</v>
+        <v>45546</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10034,13 +10029,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10083,7 +10073,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10097,10 +10087,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44979</v>
+        <v>45590</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10113,7 +10103,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10156,7 +10146,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10170,10 +10160,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45099</v>
+        <v>45133</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10186,7 +10176,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10229,7 +10219,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10243,10 +10233,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44942</v>
+        <v>45629</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10259,7 +10249,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10302,7 +10292,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10316,10 +10306,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45926</v>
+        <v>45432</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10332,7 +10322,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10375,7 +10365,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10389,10 +10379,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45926</v>
+        <v>45009</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10405,7 +10395,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10448,7 +10438,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10462,10 +10452,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45354</v>
+        <v>45036</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10478,7 +10468,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10521,7 +10511,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10535,10 +10525,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45929</v>
+        <v>45719</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10551,7 +10541,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10594,7 +10584,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10608,10 +10598,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45929</v>
+        <v>44942</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10624,7 +10614,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10667,7 +10657,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10681,10 +10671,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45926</v>
+        <v>45546</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10697,7 +10687,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10740,7 +10730,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 4856-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10754,10 +10744,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45926</v>
+        <v>44957</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10770,7 +10760,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10813,7 +10803,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10827,10 +10817,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44896</v>
+        <v>45195</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10843,7 +10833,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10886,7 +10876,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10900,10 +10890,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45093</v>
+        <v>45628</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10916,7 +10906,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10959,7 +10949,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10973,10 +10963,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45093</v>
+        <v>45597</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10988,8 +10978,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11032,7 +11027,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 20773-2026</t>
+          <t>A 35908-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11046,10 +11041,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46141</v>
+        <v>45148</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11061,13 +11056,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11110,7 +11100,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21511-2025</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11120,14 +11110,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45782</v>
+        <v>45597</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11139,8 +11129,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11183,7 +11178,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11197,10 +11192,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44585</v>
+        <v>44587</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11213,7 +11208,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11256,7 +11251,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11270,10 +11265,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46147</v>
+        <v>45173</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11285,13 +11280,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11334,7 +11324,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11348,10 +11338,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44903</v>
+        <v>44575</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11364,7 +11354,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11407,7 +11397,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 7254-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11421,10 +11411,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46154</v>
+        <v>44970</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11437,7 +11427,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11480,7 +11470,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11494,10 +11484,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46154</v>
+        <v>44970</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11510,7 +11500,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11553,7 +11543,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11567,10 +11557,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46155</v>
+        <v>44587</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11582,13 +11572,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11631,7 +11616,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11645,10 +11630,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44985</v>
+        <v>45167</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11661,7 +11646,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11704,7 +11689,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11718,10 +11703,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45481</v>
+        <v>44573</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11734,7 +11719,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11777,7 +11762,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11791,10 +11776,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45228</v>
+        <v>44897</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11807,7 +11792,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11850,7 +11835,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11864,10 +11849,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45167</v>
+        <v>44777</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11880,7 +11865,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11923,7 +11908,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11937,10 +11922,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44897</v>
+        <v>45204</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11953,7 +11938,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11996,7 +11981,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 53786-2021</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12010,10 +11995,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44463</v>
+        <v>45601</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12025,13 +12010,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12074,7 +12054,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12084,14 +12064,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45170</v>
+        <v>44852</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12104,7 +12084,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12147,7 +12127,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12161,10 +12141,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45761</v>
+        <v>45211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12177,7 +12157,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12220,7 +12200,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12234,10 +12214,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45411</v>
+        <v>45211</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12250,7 +12230,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12293,7 +12273,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12307,10 +12287,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45685</v>
+        <v>45195</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12323,7 +12303,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>15.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12366,7 +12346,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12380,10 +12360,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45685</v>
+        <v>45257</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12396,7 +12376,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12456,7 +12436,7 @@
         <v>45973</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12512,7 +12492,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 56303-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12526,10 +12506,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45632</v>
+        <v>45624</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12542,7 +12522,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12585,7 +12565,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12599,10 +12579,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44852</v>
+        <v>44952</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12615,7 +12595,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12658,7 +12638,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12672,10 +12652,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45215</v>
+        <v>44728</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12688,7 +12668,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12731,7 +12711,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12745,10 +12725,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45352</v>
+        <v>44725</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12761,7 +12741,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12804,7 +12784,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12818,10 +12798,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45986</v>
+        <v>44903</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12834,7 +12814,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12877,7 +12857,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12891,10 +12871,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45258</v>
+        <v>45183</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12907,7 +12887,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12967,7 +12947,7 @@
         <v>45986</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13023,7 +13003,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13037,10 +13017,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45989</v>
+        <v>44953</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13052,13 +13032,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13101,7 +13076,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13115,10 +13090,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44980</v>
+        <v>44518</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13131,7 +13106,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13174,7 +13149,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13188,10 +13163,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46170</v>
+        <v>45193</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13204,7 +13179,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13247,7 +13222,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13261,10 +13236,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45992</v>
+        <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13277,7 +13252,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13320,7 +13295,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13334,10 +13309,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44587</v>
+        <v>45183</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13350,7 +13325,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13393,7 +13368,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13407,10 +13382,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44725</v>
+        <v>45183</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13423,7 +13398,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13466,7 +13441,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13480,10 +13455,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45999</v>
+        <v>45020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13495,13 +13470,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13544,7 +13514,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13558,10 +13528,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45999</v>
+        <v>45992</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13573,13 +13543,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13622,7 +13587,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26049-2026</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13636,10 +13601,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46177</v>
+        <v>44749</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13651,13 +13616,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13700,7 +13660,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13714,10 +13674,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46006</v>
+        <v>45526</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13730,7 +13690,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13773,7 +13733,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13787,10 +13747,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46006</v>
+        <v>44722</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13803,7 +13763,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13846,7 +13806,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13860,10 +13820,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46006</v>
+        <v>45989</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13875,8 +13835,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13919,7 +13884,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13933,10 +13898,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46006</v>
+        <v>45685</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13949,7 +13914,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13992,7 +13957,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14006,10 +13971,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45565</v>
+        <v>45685</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14022,7 +13987,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14065,7 +14030,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14079,10 +14044,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45040</v>
+        <v>45719</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14094,13 +14059,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>10.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14143,7 +14103,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14157,10 +14117,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46020</v>
+        <v>45236</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14173,7 +14133,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14216,7 +14176,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14230,10 +14190,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14246,7 +14206,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14289,7 +14249,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14303,10 +14263,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46019</v>
+        <v>46027</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14319,7 +14279,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14362,7 +14322,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 290-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14376,10 +14336,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46020</v>
+        <v>46027</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14392,7 +14352,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14435,7 +14395,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 290-2026</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14449,10 +14409,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46027</v>
+        <v>45999</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14464,8 +14424,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14508,7 +14473,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14522,10 +14487,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46027</v>
+        <v>45999</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14537,8 +14502,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14581,7 +14551,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 560-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14595,10 +14565,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14610,8 +14580,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14654,7 +14629,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14668,10 +14643,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46029</v>
+        <v>45215</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14683,13 +14658,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14732,7 +14702,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14746,10 +14716,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44728</v>
+        <v>46006</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14762,7 +14732,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14805,7 +14775,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14819,10 +14789,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45339</v>
+        <v>46006</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14835,7 +14805,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14878,7 +14848,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14892,10 +14862,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46027</v>
+        <v>46006</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14908,7 +14878,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14951,7 +14921,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14965,10 +14935,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44652</v>
+        <v>44830</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14981,7 +14951,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15024,7 +14994,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15038,10 +15008,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45036</v>
+        <v>46006</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15054,7 +15024,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15097,7 +15067,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 8143-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15111,10 +15081,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46049</v>
+        <v>44974</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15127,7 +15097,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15170,7 +15140,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 260-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15184,10 +15154,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46189</v>
+        <v>46027</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15200,7 +15170,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15243,7 +15213,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 7266-2023</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15257,10 +15227,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44970</v>
+        <v>46020</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15273,7 +15243,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15316,7 +15286,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15330,10 +15300,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46055</v>
+        <v>46019</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15346,7 +15316,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15389,7 +15359,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15403,10 +15373,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46055</v>
+        <v>46020</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15419,7 +15389,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15462,7 +15432,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15476,10 +15446,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46055</v>
+        <v>46020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15492,7 +15462,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15535,7 +15505,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 252-2023</t>
+          <t>A 40728-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15545,14 +15515,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44922</v>
+        <v>45170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15565,7 +15535,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15608,7 +15578,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 6161-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15622,10 +15592,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46195</v>
+        <v>46055</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15638,7 +15608,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7.7</v>
+        <v>2.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15681,7 +15651,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 45783-2023</t>
+          <t>A 6160-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15691,14 +15661,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45195</v>
+        <v>46055</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15711,7 +15681,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15754,7 +15724,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 7582-2023</t>
+          <t>A 6162-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15768,10 +15738,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44972</v>
+        <v>46055</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15784,7 +15754,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15827,7 +15797,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 22297-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15841,10 +15811,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46195</v>
+        <v>46154</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15857,7 +15827,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15900,7 +15870,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 54812-2022</t>
+          <t>A 8845-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15910,14 +15880,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44883</v>
+        <v>46066</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15930,7 +15900,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15973,7 +15943,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 8818-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15990,7 +15960,7 @@
         <v>46066</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16003,7 +15973,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16046,7 +16016,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 8822-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16063,7 +16033,7 @@
         <v>46066</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16076,7 +16046,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16136,7 +16106,7 @@
         <v>46066</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16192,7 +16162,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 33090-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16206,10 +16176,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46066</v>
+        <v>46245</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16222,7 +16192,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16265,7 +16235,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 43151-2023</t>
+          <t>A 33076-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16279,10 +16249,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45183</v>
+        <v>46245</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16295,7 +16265,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16338,7 +16308,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 33177-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16352,10 +16322,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46077</v>
+        <v>46245</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16368,7 +16338,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16411,7 +16381,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31862-2022</t>
+          <t>A 58262-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16425,10 +16395,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44777</v>
+        <v>44894</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16441,7 +16411,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16484,7 +16454,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 57864-2022</t>
+          <t>A 10575-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16498,10 +16468,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44899</v>
+        <v>46077</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16514,7 +16484,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16557,7 +16527,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 15779-2024</t>
+          <t>A 21399-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16571,10 +16541,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45404</v>
+        <v>45063</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16587,7 +16557,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16630,7 +16600,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 50041-2023</t>
+          <t>A 6022-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16644,10 +16614,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45215</v>
+        <v>45336</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16660,7 +16630,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16703,7 +16673,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 4331-2023</t>
+          <t>A 52223-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16717,10 +16687,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44953</v>
+        <v>44463</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16732,8 +16702,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>1.8</v>
+        <v>10.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16776,7 +16751,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 42401-2022</t>
+          <t>A 17585-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16790,10 +16765,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44830</v>
+        <v>45036</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16806,7 +16781,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16849,7 +16824,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 33177-2026</t>
+          <t>A 8685-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16863,10 +16838,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46245</v>
+        <v>44613</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16879,7 +16854,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16922,7 +16897,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 59741-2023</t>
+          <t>A 26821-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16936,10 +16911,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45257</v>
+        <v>45093</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16952,7 +16927,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16995,7 +16970,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 52223-2021</t>
+          <t>A 3267-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17009,10 +16984,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44463</v>
+        <v>44949</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17024,13 +16999,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17073,7 +17043,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 8685-2022</t>
+          <t>A 3276-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17087,10 +17057,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44613</v>
+        <v>44949</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17103,7 +17073,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17146,7 +17116,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 43516-2024</t>
+          <t>A 53786-2021</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17160,10 +17130,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45569</v>
+        <v>44463</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17177,11 +17147,11 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17224,7 +17194,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 43518-2024</t>
+          <t>A 29424-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17238,10 +17208,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45569</v>
+        <v>44753</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17253,13 +17223,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17302,7 +17267,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 59399-2021</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17316,10 +17281,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46105</v>
+        <v>44491</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17332,7 +17297,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17375,7 +17340,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 15078-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17392,7 +17357,7 @@
         <v>46105</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17405,7 +17370,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17448,7 +17413,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21399-2023</t>
+          <t>A 15138-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17462,10 +17427,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45063</v>
+        <v>46105</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17478,7 +17443,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17538,7 +17503,7 @@
         <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17594,7 +17559,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 14417-2024</t>
+          <t>A 14429-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17608,10 +17573,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45394</v>
+        <v>44652</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17624,7 +17589,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17667,7 +17632,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 17717-2025</t>
+          <t>A 17296-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17681,10 +17646,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45758</v>
+        <v>45035</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17696,8 +17661,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17740,7 +17710,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 34357-2023</t>
+          <t>A 6580-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17754,10 +17724,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45133</v>
+        <v>45699</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17770,7 +17740,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17813,7 +17783,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21483-2023</t>
+          <t>A 22974-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17823,14 +17793,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45063</v>
+        <v>45790</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17843,7 +17813,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17886,7 +17856,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 38431-2024</t>
+          <t>A 21397-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17900,10 +17870,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45546</v>
+        <v>45063</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17916,7 +17886,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17959,7 +17929,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 38438-2024</t>
+          <t>A 60285-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17973,10 +17943,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45546</v>
+        <v>45258</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17989,7 +17959,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18032,7 +18002,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 10135-2025</t>
+          <t>A 10122-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18049,7 +18019,7 @@
         <v>45719</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18062,7 +18032,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>10.3</v>
+        <v>1.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18105,7 +18075,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 1974-2022</t>
+          <t>A 9971-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18119,10 +18089,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44575</v>
+        <v>44985</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18135,7 +18105,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18178,7 +18148,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 41314-2023</t>
+          <t>A 17937-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18192,10 +18162,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45173</v>
+        <v>45040</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18205,6 +18175,11 @@
       <c r="G229" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I229" t="n">
@@ -18251,7 +18226,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 23827-2022</t>
+          <t>A 15779-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18265,10 +18240,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44722</v>
+        <v>45404</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18281,7 +18256,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18324,7 +18299,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 9292-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18338,10 +18313,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45433</v>
+        <v>44980</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18354,7 +18329,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18397,7 +18372,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 21487-2023</t>
+          <t>A 19747-2024</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18411,10 +18386,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45063</v>
+        <v>45432</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18427,7 +18402,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18470,7 +18445,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 7646-2025</t>
+          <t>A 54785-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18484,10 +18459,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45705</v>
+        <v>44883</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18500,7 +18475,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.8</v>
+        <v>8.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18543,7 +18518,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 7647-2025</t>
+          <t>A 21396-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18557,10 +18532,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45705</v>
+        <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18573,7 +18548,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18616,7 +18591,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 45873-2023</t>
+          <t>A 19925-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18630,10 +18605,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45195</v>
+        <v>45433</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18646,7 +18621,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>15.8</v>
+        <v>2.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18689,7 +18664,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 57144-2024</t>
+          <t>A 46186-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18703,10 +18678,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45629</v>
+        <v>45581</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18719,7 +18694,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18762,7 +18737,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 3276-2023</t>
+          <t>A 6522-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18776,10 +18751,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44949</v>
+        <v>45699</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18792,7 +18767,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18835,7 +18810,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 50992-2023</t>
+          <t>A 16342-2023</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18849,10 +18824,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45218</v>
+        <v>45028</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18864,13 +18839,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I238" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18913,7 +18883,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 30523-2026</t>
+          <t>A 20246-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18927,10 +18897,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46210</v>
+        <v>46139</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18942,8 +18912,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18986,7 +18961,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 62048-2022</t>
+          <t>A 20248-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19000,10 +18975,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44918</v>
+        <v>46139</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19015,8 +18990,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19059,7 +19039,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 10120-2025</t>
+          <t>A 21511-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19069,14 +19049,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45719</v>
+        <v>45782</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19089,7 +19069,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19132,7 +19112,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 21397-2023</t>
+          <t>A 29008-2022</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19146,10 +19126,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45063</v>
+        <v>44749</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19162,7 +19142,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19205,7 +19185,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 34488-2026</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19219,10 +19199,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46255</v>
+        <v>45793</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19235,7 +19215,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19278,7 +19258,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 14082-2023</t>
+          <t>A 20307-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19292,10 +19272,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45009</v>
+        <v>46139</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19308,7 +19288,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19351,7 +19331,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 34489-2026</t>
+          <t>A 8328-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19365,10 +19345,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46255</v>
+        <v>45352</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19381,7 +19361,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19424,7 +19404,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19434,14 +19414,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46213</v>
+        <v>45992</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19454,7 +19434,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19497,7 +19477,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 4047-2023</t>
+          <t>A 26811-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19511,10 +19491,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>44952</v>
+        <v>45093</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19527,7 +19507,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19570,7 +19550,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 47962-2023</t>
+          <t>A 48158-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19584,10 +19564,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45204</v>
+        <v>45205</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19599,8 +19579,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19643,7 +19628,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 21487-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19657,10 +19642,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>46265</v>
+        <v>45063</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19673,7 +19658,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19716,7 +19701,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 35806-2026</t>
+          <t>A 6548-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19730,10 +19715,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46265</v>
+        <v>44601</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19746,7 +19731,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19789,7 +19774,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 18961-2022</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19803,10 +19788,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46266</v>
+        <v>44690</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19819,7 +19804,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19862,7 +19847,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 49345-2023</t>
+          <t>A 58247-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19876,10 +19861,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45211</v>
+        <v>45632</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19892,7 +19877,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19935,7 +19920,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 49348-2023</t>
+          <t>A 41889-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19949,10 +19934,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45211</v>
+        <v>45176</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19965,7 +19950,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20008,7 +19993,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 54849-2023</t>
+          <t>A 47205-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20022,10 +20007,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45236</v>
+        <v>45202</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20038,7 +20023,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20081,7 +20066,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 36555-2026</t>
+          <t>A 6357-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20095,10 +20080,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46269</v>
+        <v>44965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20111,7 +20096,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20154,7 +20139,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 45377-2023</t>
+          <t>A 57513-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20164,14 +20149,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45193</v>
+        <v>44896</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20184,7 +20169,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.7</v>
+        <v>5.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20227,7 +20212,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 47354-2023</t>
+          <t>A 37421-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20241,10 +20226,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45202</v>
+        <v>45540</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20257,7 +20242,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20300,7 +20285,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 34572-2024</t>
+          <t>A 3280-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20314,10 +20299,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45526</v>
+        <v>44949</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20330,7 +20315,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20373,7 +20358,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 49931-2024</t>
+          <t>A 8890-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20387,10 +20372,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45597</v>
+        <v>45357</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20402,13 +20387,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>1.2</v>
+        <v>7.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20451,7 +20431,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 54785-2022</t>
+          <t>A 20773-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20465,10 +20445,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44883</v>
+        <v>46141</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20480,8 +20460,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I260" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20524,7 +20509,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 6522-2025</t>
+          <t>A 42623-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20538,10 +20523,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45699</v>
+        <v>45565</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20554,7 +20539,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20597,7 +20582,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 3276-2024</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20611,10 +20596,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45317</v>
+        <v>45202</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20627,7 +20612,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20670,7 +20655,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 19747-2024</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20684,10 +20669,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45432</v>
+        <v>45317</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20700,7 +20685,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20743,7 +20728,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 38060-2026</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20757,10 +20742,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46280</v>
+        <v>45404</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20773,7 +20758,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20816,7 +20801,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 60242-2022</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20830,10 +20815,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44910</v>
+        <v>44979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20846,7 +20831,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20889,7 +20874,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 9337-2022</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20903,10 +20888,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44616</v>
+        <v>46147</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20918,8 +20903,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I266" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20962,7 +20952,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 21233-2023</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20976,10 +20966,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45062</v>
+        <v>46154</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20992,7 +20982,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21035,7 +21025,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 19745-2024</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21049,10 +21039,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45432</v>
+        <v>46154</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21065,7 +21055,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21108,7 +21098,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 47679-2024</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21122,10 +21112,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45588</v>
+        <v>46155</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21137,8 +21127,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I269" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21181,7 +21176,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 22297-2026</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21195,10 +21190,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>46154</v>
+        <v>46170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21211,7 +21206,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21254,7 +21249,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 15660-2024</t>
+          <t>A 26049-2026</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21268,10 +21263,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45404</v>
+        <v>46177</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21283,8 +21278,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I271" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21327,7 +21327,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 66424-2021</t>
+          <t>A 27525-2026</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21341,10 +21341,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>44518</v>
+        <v>46189</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21400,7 +21400,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 39583-2022</t>
+          <t>A 4965-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21414,10 +21414,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>44818</v>
+        <v>46049</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21473,7 +21473,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 10122-2025</t>
+          <t>A 28093-2026</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21487,10 +21487,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45719</v>
+        <v>46195</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21546,7 +21546,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 33090-2026</t>
+          <t>A 28119-2026</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21560,10 +21560,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46245</v>
+        <v>46195</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21619,7 +21619,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 65113-2023</t>
+          <t>A 30523-2026</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21633,10 +21633,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>45287</v>
+        <v>46210</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21692,7 +21692,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 33076-2026</t>
+          <t>A 34488-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21706,10 +21706,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>46245</v>
+        <v>46255</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21765,7 +21765,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 56830-2024</t>
+          <t>A 34489-2026</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21779,10 +21779,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>45628</v>
+        <v>46255</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -21838,7 +21838,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 57862-2023</t>
+          <t>A 30964-2026</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -21848,14 +21848,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45247</v>
+        <v>46213</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -21911,7 +21911,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 24367-2025</t>
+          <t>A 35740-2026</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -21925,10 +21925,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>45797</v>
+        <v>46265</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -21984,7 +21984,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 2336-2024</t>
+          <t>A 35924-2026</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>45310</v>
+        <v>46266</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22057,7 +22057,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 59399-2021</t>
+          <t>A 35806-2026</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22071,10 +22071,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>44491</v>
+        <v>46265</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22130,7 +22130,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 22974-2025</t>
+          <t>A 36555-2026</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22140,14 +22140,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45790</v>
+        <v>46269</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22203,7 +22203,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 6580-2025</t>
+          <t>A 38060-2026</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22217,10 +22217,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45699</v>
+        <v>46280</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>44140</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22366,7 +22366,7 @@
         <v>43951</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22439,7 +22439,7 @@
         <v>44735</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45300</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22585,7 +22585,7 @@
         <v>45708</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>46076</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE286"/>
+  <dimension ref="A1:AE284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 59356-2023</t>
+          <t>A 1075-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45253</v>
+        <v>44571</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1186,28 +1186,23 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1219,18 +1214,366 @@
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>17</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Tallticka
+Blåmossa
+Grönpyrola
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46766-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Bronshjon
+Flagellkvastmossa
+Stubbspretmossa
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 29305-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Krusfrö
+Sädesärla
+Murgröna
+Huggorm</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 29305-2026 artfynd.xlsx", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 29305-2026 karta.png", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 29305-2026 georefererad karta.tif", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 29305-2026 karta knärot.png", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 29305-2026 FSC-klagomål.docx", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 29305-2026 FSC-klagomål mail.docx", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 29305-2026 tillsynsbegäran.docx", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 29305-2026 tillsynsbegäran mail.docx", "A 29305-2026")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 29305-2026 prioriterade fågelarter.docx", "A 29305-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 59356-2023</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45253</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Ask
 Bukspolsnäcka
@@ -1239,378 +1582,35 @@
 Noshornsoxe</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 59356-2023 artfynd.xlsx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 59356-2023 karta.png", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 59356-2023 georefererad karta.tif", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 59356-2023 FSC-klagomål.docx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 59356-2023 FSC-klagomål mail.docx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 59356-2023 tillsynsbegäran.docx", "A 59356-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 59356-2023 tillsynsbegäran mail.docx", "A 59356-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 46766-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>8</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Bronshjon
-Flagellkvastmossa
-Stubbspretmossa
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 1075-2022</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44571</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>17</v>
-      </c>
-      <c r="U9" t="n">
-        <v>17</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Tallticka
-Blåmossa
-Grönpyrola
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 29305-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46202</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>6</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Krusfrö
-Sädesärla
-Murgröna
-Huggorm</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 29305-2026 artfynd.xlsx", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 29305-2026 karta.png", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 29305-2026 georefererad karta.tif", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 29305-2026 karta knärot.png", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 29305-2026 FSC-klagomål.docx", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 29305-2026 FSC-klagomål mail.docx", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 29305-2026 tillsynsbegäran.docx", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 29305-2026 tillsynsbegäran mail.docx", "A 29305-2026")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 29305-2026 prioriterade fågelarter.docx", "A 29305-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46255</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>46018</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 1543-2022</t>
+          <t>A 4051-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44573</v>
+        <v>44952</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,19 +2290,19 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2326,39 +2326,39 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
         <v/>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
         <v>45323</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 5414-2024</t>
+          <t>A 11749-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45331</v>
+        <v>44994</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2540,35 +2540,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
         <v/>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
         <v>45173</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 11749-2023</t>
+          <t>A 27253-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44994</v>
+        <v>46188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2746,46 +2746,50 @@
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>Adam och eva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
         <v/>
       </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
+        <v/>
+      </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18758-2023</t>
+          <t>A 5414-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2799,10 +2803,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45043</v>
+        <v>45331</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2815,19 +2819,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2842,7 +2846,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2855,256 +2859,252 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 1543-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44573</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 18758-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="Z22">
+      <c r="Z24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 4051-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 27253-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44749</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47632-2022</t>
+          <t>A 18684-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44852</v>
+        <v>44687</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3436,7 +3436,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 51436-2022</t>
+          <t>A 47632-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44869</v>
+        <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3509,7 +3509,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 18684-2022</t>
+          <t>A 51436-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44687</v>
+        <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>44536</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44613</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44531</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44881</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>44564</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44636</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>44658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>44656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>44629</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>44573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>44593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44881</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44487</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 35659-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44753</v>
+        <v>44799</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5339,7 +5339,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45597</v>
+        <v>45271</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5370,11 +5370,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>11.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 7634-2022</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44607</v>
+        <v>45344</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5490,7 +5490,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48243-2024</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45590</v>
+        <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5563,7 +5563,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 37421-2024</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5577,10 +5577,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45540</v>
+        <v>45339</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5636,7 +5636,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 19937-2024</t>
+          <t>A 59516-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5646,14 +5646,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45433</v>
+        <v>45254</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11.9</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5709,7 +5709,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 18961-2022</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5723,10 +5723,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44690</v>
+        <v>45394</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5782,7 +5782,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5796,10 +5796,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45687</v>
+        <v>45287</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5855,7 +5855,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 7254-2023</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44970</v>
+        <v>44883</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35908-2023</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45148</v>
+        <v>45258</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6001,7 +6001,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6548-2022</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44601</v>
+        <v>45588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 4856-2023</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44957</v>
+        <v>46020</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6147,7 +6147,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59516-2023</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6157,14 +6157,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45254</v>
+        <v>44833</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6220,7 +6220,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45590</v>
+        <v>46019</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45020</v>
+        <v>46020</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16342-2023</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45028</v>
+        <v>46020</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6439,7 +6439,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6453,10 +6453,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45189</v>
+        <v>46027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6526,10 +6526,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44749</v>
+        <v>46027</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6585,7 +6585,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 290-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6599,10 +6599,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45344</v>
+        <v>46027</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 24367-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45719</v>
+        <v>45797</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 560-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45176</v>
+        <v>46029</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6760,8 +6760,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6804,7 +6809,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 2336-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6818,10 +6823,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44949</v>
+        <v>45310</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6834,7 +6839,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6877,7 +6882,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6891,10 +6896,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45336</v>
+        <v>44922</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6907,7 +6912,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6950,7 +6955,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 260-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6964,10 +6969,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44573</v>
+        <v>46027</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6980,7 +6985,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7023,7 +7028,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7037,10 +7042,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45202</v>
+        <v>44918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7053,7 +7058,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7096,7 +7101,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7110,10 +7115,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44833</v>
+        <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7126,7 +7131,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7169,7 +7174,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7183,10 +7188,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45204</v>
+        <v>44972</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7199,7 +7204,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7242,7 +7247,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7256,10 +7261,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45183</v>
+        <v>44592</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7272,7 +7277,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>11.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7315,7 +7320,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7329,10 +7334,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45183</v>
+        <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7345,7 +7350,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7388,7 +7393,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 48243-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7402,10 +7407,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44592</v>
+        <v>45590</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7418,7 +7423,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.6</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7461,7 +7466,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 6161-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7475,10 +7480,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45271</v>
+        <v>46055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7490,13 +7495,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>11.1</v>
+        <v>2.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7539,7 +7539,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 6160-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7553,10 +7553,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45093</v>
+        <v>46055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 6162-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7626,10 +7626,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45158</v>
+        <v>46055</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7685,7 +7685,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44593</v>
+        <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7758,7 +7758,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35659-2022</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7772,10 +7772,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44799</v>
+        <v>45546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 8845-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45036</v>
+        <v>46066</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 8818-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7918,10 +7918,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44894</v>
+        <v>46066</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7977,7 +7977,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 8822-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7991,10 +7991,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44587</v>
+        <v>46066</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8050,7 +8050,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 8823-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44749</v>
+        <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8123,7 +8123,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45404</v>
+        <v>45133</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8196,7 +8196,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22974-2025</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8206,14 +8206,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45790</v>
+        <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8269,7 +8269,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 6580-2025</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45699</v>
+        <v>45432</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8342,7 +8342,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8356,10 +8356,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44974</v>
+        <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8415,7 +8415,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56303-2024</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45624</v>
+        <v>45926</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3267-2023</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44949</v>
+        <v>45926</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8575,10 +8575,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45782</v>
+        <v>45009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 10575-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45601</v>
+        <v>46077</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8707,7 +8707,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45793</v>
+        <v>44942</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8780,7 +8780,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45357</v>
+        <v>45546</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8853,7 +8853,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45035</v>
+        <v>45929</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8882,13 +8882,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8931,7 +8926,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8945,10 +8940,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44937</v>
+        <v>45929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8961,7 +8956,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9004,7 +8999,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 4856-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9018,10 +9013,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44937</v>
+        <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9034,7 +9029,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9077,7 +9072,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9087,14 +9082,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45258</v>
+        <v>45195</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9107,7 +9102,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9150,7 +9145,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9164,10 +9159,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45901</v>
+        <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9179,8 +9174,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9223,7 +9223,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 7254-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9237,10 +9237,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44965</v>
+        <v>44970</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9296,7 +9296,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 41839-2025</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9310,10 +9310,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45902</v>
+        <v>44970</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9369,7 +9369,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 41843-2025</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9383,10 +9383,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45902</v>
+        <v>44897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9442,7 +9442,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 15078-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44883</v>
+        <v>46105</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9515,7 +9515,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 15138-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9529,10 +9529,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45176</v>
+        <v>46105</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9588,7 +9588,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9602,10 +9602,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45205</v>
+        <v>44777</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9617,13 +9617,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9666,7 +9661,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 15096-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9680,10 +9675,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44979</v>
+        <v>46105</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9696,7 +9691,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9739,7 +9734,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9753,10 +9748,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45992</v>
+        <v>45601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9769,7 +9764,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9812,7 +9807,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20246-2026</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9826,10 +9821,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46139</v>
+        <v>44852</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9841,13 +9836,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9890,7 +9880,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 20248-2026</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9904,10 +9894,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46139</v>
+        <v>45257</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9919,13 +9909,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9968,7 +9953,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 56303-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9982,10 +9967,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45099</v>
+        <v>45624</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9998,7 +9983,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10041,7 +10026,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10055,10 +10040,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44942</v>
+        <v>44952</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10071,7 +10056,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10114,7 +10099,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10128,10 +10113,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45354</v>
+        <v>44903</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10144,7 +10129,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10187,7 +10172,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10197,14 +10182,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44896</v>
+        <v>44953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10217,7 +10202,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.6</v>
+        <v>1.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10260,7 +10245,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10274,10 +10259,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45926</v>
+        <v>44518</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10290,7 +10275,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10333,7 +10318,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 56097-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10347,10 +10332,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45926</v>
+        <v>45973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10363,7 +10348,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10406,7 +10391,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10420,10 +10405,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45929</v>
+        <v>45020</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10436,7 +10421,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10479,7 +10464,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10493,10 +10478,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45929</v>
+        <v>45526</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10509,7 +10494,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10552,7 +10537,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10566,10 +10551,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45926</v>
+        <v>44722</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10582,7 +10567,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10625,7 +10610,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 58749-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10639,10 +10624,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45926</v>
+        <v>45986</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10655,7 +10640,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10698,7 +10683,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10712,10 +10697,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45093</v>
+        <v>45685</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10728,7 +10713,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10771,7 +10756,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10785,10 +10770,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45093</v>
+        <v>45685</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10801,7 +10786,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10844,7 +10829,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10858,10 +10843,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44585</v>
+        <v>45986</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10874,7 +10859,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10917,7 +10902,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10931,10 +10916,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45581</v>
+        <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10990,7 +10975,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11004,10 +10989,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44903</v>
+        <v>45158</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11020,7 +11005,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11063,7 +11048,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 21396-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11077,10 +11062,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44985</v>
+        <v>45782</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11093,7 +11078,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11136,7 +11121,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 19925-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11150,10 +11135,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45481</v>
+        <v>45433</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11166,7 +11151,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11209,7 +11194,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11223,10 +11208,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45228</v>
+        <v>45189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11239,7 +11224,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11282,7 +11267,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11296,10 +11281,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45167</v>
+        <v>45992</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11312,7 +11297,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11355,7 +11340,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20307-2026</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11369,10 +11354,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46139</v>
+        <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11384,8 +11369,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11428,7 +11418,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 46186-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11442,10 +11432,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44897</v>
+        <v>45581</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11458,7 +11448,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11501,7 +11491,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11511,14 +11501,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45170</v>
+        <v>45999</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11530,8 +11520,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11574,7 +11569,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11588,10 +11583,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45761</v>
+        <v>45999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11603,8 +11598,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11647,7 +11647,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 20246-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11661,10 +11661,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45411</v>
+        <v>46139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11676,8 +11676,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11720,7 +11725,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 20248-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11734,10 +11739,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45685</v>
+        <v>46139</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11749,8 +11754,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11793,7 +11803,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 21511-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11803,14 +11813,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45685</v>
+        <v>45782</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11823,7 +11833,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11866,7 +11876,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11880,10 +11890,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45632</v>
+        <v>45793</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11896,7 +11906,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>8.4</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11939,7 +11949,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11953,10 +11963,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44852</v>
+        <v>46006</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11969,7 +11979,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12012,7 +12022,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12026,10 +12036,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45215</v>
+        <v>46006</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12042,7 +12052,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12085,7 +12095,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56097-2025</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12099,10 +12109,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45973</v>
+        <v>46006</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12115,7 +12125,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12158,7 +12168,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 20307-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12172,10 +12182,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45352</v>
+        <v>46139</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12188,7 +12198,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12231,7 +12241,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12245,10 +12255,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45258</v>
+        <v>46006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12261,7 +12271,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12304,7 +12314,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12318,10 +12328,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44980</v>
+        <v>45992</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12334,7 +12344,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>6.4</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12377,7 +12387,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12391,10 +12401,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44587</v>
+        <v>45228</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12407,7 +12417,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12450,7 +12460,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 20773-2026</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12464,10 +12474,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46141</v>
+        <v>45687</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12479,13 +12489,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12528,7 +12533,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21511-2025</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12538,14 +12543,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45782</v>
+        <v>45761</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12558,7 +12563,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12601,7 +12606,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12615,10 +12620,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45986</v>
+        <v>45063</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12631,7 +12636,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12674,7 +12679,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12688,10 +12693,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44725</v>
+        <v>45215</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12704,7 +12709,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12747,7 +12752,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 58749-2025</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12757,14 +12762,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45986</v>
+        <v>44883</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12777,7 +12782,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12820,7 +12825,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12834,10 +12839,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45989</v>
+        <v>45204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12849,13 +12854,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12898,7 +12898,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12912,10 +12912,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46147</v>
+        <v>44910</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12927,13 +12927,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12976,7 +12971,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12990,10 +12985,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45992</v>
+        <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13006,7 +13001,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13049,7 +13044,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13063,10 +13058,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45999</v>
+        <v>45705</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13078,13 +13073,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13127,7 +13117,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13141,10 +13131,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45999</v>
+        <v>45705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13154,11 +13144,6 @@
       <c r="G161" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -13205,7 +13190,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13219,10 +13204,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46154</v>
+        <v>46147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13234,8 +13219,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13278,7 +13268,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13292,10 +13282,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46154</v>
+        <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13308,7 +13298,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13351,7 +13341,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13365,10 +13355,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13380,13 +13370,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13429,7 +13414,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13443,10 +13428,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46006</v>
+        <v>46154</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13459,7 +13444,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13502,7 +13487,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13516,10 +13501,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45565</v>
+        <v>45411</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13532,7 +13517,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13575,7 +13560,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13589,10 +13574,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46006</v>
+        <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13604,8 +13589,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13648,7 +13638,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13662,10 +13652,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46006</v>
+        <v>45218</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13677,8 +13667,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13721,7 +13716,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13735,10 +13730,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45040</v>
+        <v>45093</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13750,13 +13745,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13799,7 +13789,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 7634-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13813,10 +13803,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46006</v>
+        <v>44607</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13829,7 +13819,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13872,7 +13862,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13886,10 +13876,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46020</v>
+        <v>45354</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13902,7 +13892,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13945,7 +13935,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 59399-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13959,10 +13949,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46020</v>
+        <v>44491</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13975,7 +13965,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14018,7 +14008,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14032,10 +14022,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46019</v>
+        <v>44818</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14048,7 +14038,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14091,7 +14081,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14105,10 +14095,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46020</v>
+        <v>46170</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14121,7 +14111,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14164,7 +14154,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14178,10 +14168,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44728</v>
+        <v>45062</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14194,7 +14184,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14237,7 +14227,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 290-2026</t>
+          <t>A 6580-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14251,10 +14241,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46027</v>
+        <v>45699</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14267,7 +14257,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14310,7 +14300,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 22974-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14320,14 +14310,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45339</v>
+        <v>45790</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14340,7 +14330,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14383,7 +14373,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14397,10 +14387,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46027</v>
+        <v>45481</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14413,7 +14403,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14456,7 +14446,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 26049-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14470,10 +14460,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46027</v>
+        <v>46177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14485,8 +14475,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14529,7 +14524,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14543,10 +14538,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46029</v>
+        <v>45099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14558,13 +14553,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14607,7 +14597,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14621,10 +14611,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44652</v>
+        <v>44937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14637,7 +14627,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14680,7 +14670,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14694,10 +14684,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45036</v>
+        <v>44937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14710,7 +14700,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14753,7 +14743,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14767,10 +14757,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46027</v>
+        <v>45176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14783,7 +14773,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14826,7 +14816,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 7266-2023</t>
+          <t>A 19937-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14840,10 +14830,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44970</v>
+        <v>45433</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14856,7 +14846,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.4</v>
+        <v>11.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14899,7 +14889,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 252-2023</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14913,10 +14903,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44922</v>
+        <v>45404</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14929,7 +14919,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14972,7 +14962,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 45783-2023</t>
+          <t>A 27525-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14982,14 +14972,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45195</v>
+        <v>46189</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15002,7 +14992,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15045,7 +15035,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 7582-2023</t>
+          <t>A 4965-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15059,10 +15049,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44972</v>
+        <v>46049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15075,7 +15065,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15118,7 +15108,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15132,10 +15122,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46055</v>
+        <v>45569</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15147,8 +15137,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15191,7 +15186,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15205,10 +15200,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46055</v>
+        <v>45569</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15220,8 +15215,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15264,7 +15264,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 54812-2022</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15274,14 +15274,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44883</v>
+        <v>45590</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15337,7 +15337,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 28093-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15351,10 +15351,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46055</v>
+        <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15410,7 +15410,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 43151-2023</t>
+          <t>A 28119-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15424,10 +15424,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45183</v>
+        <v>46195</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15483,7 +15483,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 31862-2022</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15497,10 +15497,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44777</v>
+        <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15556,7 +15556,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 57864-2022</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15570,10 +15570,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44899</v>
+        <v>45036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15629,7 +15629,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 15779-2024</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15643,10 +15643,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45404</v>
+        <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15702,7 +15702,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 50041-2023</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15716,10 +15716,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45215</v>
+        <v>45628</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15775,7 +15775,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15789,10 +15789,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46066</v>
+        <v>45597</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15804,8 +15804,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15848,7 +15853,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 35908-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15862,10 +15867,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46066</v>
+        <v>45148</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15878,7 +15883,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15921,7 +15926,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 8823-2026</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15935,10 +15940,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46066</v>
+        <v>44587</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15951,7 +15956,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15994,7 +15999,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16008,10 +16013,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46066</v>
+        <v>45173</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16024,7 +16029,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16067,7 +16072,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16081,10 +16086,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46170</v>
+        <v>44575</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16097,7 +16102,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16140,7 +16145,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 4331-2023</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16154,10 +16159,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44953</v>
+        <v>44587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16170,7 +16175,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16213,7 +16218,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 42401-2022</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16227,10 +16232,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44830</v>
+        <v>45167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16243,7 +16248,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16286,7 +16291,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16300,10 +16305,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46077</v>
+        <v>44573</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16316,7 +16321,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16359,7 +16364,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 59741-2023</t>
+          <t>A 30523-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16373,10 +16378,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45257</v>
+        <v>46210</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16389,7 +16394,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16432,7 +16437,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 26049-2026</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16446,10 +16451,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46177</v>
+        <v>45204</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16461,13 +16466,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16510,7 +16510,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 8685-2022</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16524,10 +16524,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44613</v>
+        <v>45211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16583,7 +16583,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 43516-2024</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16597,10 +16597,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45569</v>
+        <v>45211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16612,13 +16612,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16661,7 +16656,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 43518-2024</t>
+          <t>A 34488-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16675,10 +16670,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45569</v>
+        <v>46255</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16688,11 +16683,6 @@
       <c r="G209" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I209" t="n">
@@ -16739,7 +16729,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 21399-2023</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16753,10 +16743,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45063</v>
+        <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16769,7 +16759,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.6</v>
+        <v>15.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16812,7 +16802,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 14417-2024</t>
+          <t>A 34489-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16826,10 +16816,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45394</v>
+        <v>46255</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16842,7 +16832,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16885,7 +16875,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 17717-2025</t>
+          <t>A 30964-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16895,14 +16885,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45758</v>
+        <v>46213</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16915,7 +16905,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16958,7 +16948,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 34357-2023</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16972,10 +16962,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45133</v>
+        <v>44728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16988,7 +16978,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17031,7 +17021,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 21483-2023</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17045,10 +17035,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45063</v>
+        <v>44725</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17061,7 +17051,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.6</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17104,7 +17094,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17118,10 +17108,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46105</v>
+        <v>45183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17134,7 +17124,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17177,7 +17167,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38431-2024</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17191,10 +17181,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45546</v>
+        <v>45193</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17207,7 +17197,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17250,7 +17240,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38438-2024</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17264,10 +17254,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45546</v>
+        <v>45183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17323,7 +17313,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17337,10 +17327,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46105</v>
+        <v>45183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17353,7 +17343,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17396,7 +17386,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 10135-2025</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17410,10 +17400,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45719</v>
+        <v>44749</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17426,7 +17416,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>10.3</v>
+        <v>6.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17469,7 +17459,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 15096-2026</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17483,10 +17473,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46105</v>
+        <v>45719</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17499,7 +17489,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>4.8</v>
+        <v>10.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17542,7 +17532,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 1974-2022</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17556,10 +17546,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44575</v>
+        <v>45236</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17615,7 +17605,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 41314-2023</t>
+          <t>A 35740-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17629,10 +17619,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45173</v>
+        <v>46265</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17645,7 +17635,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17688,7 +17678,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 35924-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17702,10 +17692,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46049</v>
+        <v>46266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17718,7 +17708,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17761,7 +17751,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 23827-2022</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17775,10 +17765,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44722</v>
+        <v>45215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17791,7 +17781,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17834,7 +17824,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17848,10 +17838,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46189</v>
+        <v>44830</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17864,7 +17854,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17907,7 +17897,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 21487-2023</t>
+          <t>A 8143-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17921,10 +17911,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45063</v>
+        <v>44974</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17937,7 +17927,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17980,7 +17970,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 7646-2025</t>
+          <t>A 36555-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17994,10 +17984,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45705</v>
+        <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18010,7 +18000,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18053,7 +18043,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 7647-2025</t>
+          <t>A 40728-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18063,14 +18053,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45705</v>
+        <v>45170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18083,7 +18073,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18126,7 +18116,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 45873-2023</t>
+          <t>A 38060-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18140,10 +18130,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45195</v>
+        <v>46280</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18156,7 +18146,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18199,7 +18189,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 57144-2024</t>
+          <t>A 22297-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18213,10 +18203,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45629</v>
+        <v>46154</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18229,7 +18219,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18272,7 +18262,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 3276-2023</t>
+          <t>A 58262-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18286,10 +18276,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44949</v>
+        <v>44894</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18302,7 +18292,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18345,7 +18335,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 21399-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18359,10 +18349,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46195</v>
+        <v>45063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18375,7 +18365,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18418,7 +18408,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 33090-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18432,10 +18422,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45433</v>
+        <v>46245</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18448,7 +18438,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18491,7 +18481,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 50992-2023</t>
+          <t>A 33076-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18505,10 +18495,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45218</v>
+        <v>46245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18520,13 +18510,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18569,7 +18554,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 6022-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18583,10 +18568,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46195</v>
+        <v>45336</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18599,7 +18584,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18642,7 +18627,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 62048-2022</t>
+          <t>A 33177-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18656,10 +18641,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44918</v>
+        <v>46245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18672,7 +18657,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18715,7 +18700,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 10120-2025</t>
+          <t>A 17585-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18729,10 +18714,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45719</v>
+        <v>45036</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18745,7 +18730,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18788,7 +18773,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 21397-2023</t>
+          <t>A 8685-2022</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18802,10 +18787,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45063</v>
+        <v>44613</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18818,7 +18803,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18861,7 +18846,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 14082-2023</t>
+          <t>A 26821-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18875,10 +18860,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45009</v>
+        <v>45093</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18891,7 +18876,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18934,7 +18919,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 4047-2023</t>
+          <t>A 20773-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18948,10 +18933,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44952</v>
+        <v>46141</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18963,8 +18948,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19007,7 +18997,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 47962-2023</t>
+          <t>A 3267-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19021,10 +19011,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45204</v>
+        <v>44949</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19037,7 +19027,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19080,7 +19070,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 30523-2026</t>
+          <t>A 35806-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19094,10 +19084,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46210</v>
+        <v>46265</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19110,7 +19100,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19153,7 +19143,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 49345-2023</t>
+          <t>A 3276-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19167,10 +19157,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45211</v>
+        <v>44949</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19183,7 +19173,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19226,7 +19216,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 49348-2023</t>
+          <t>A 29424-2022</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19240,10 +19230,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45211</v>
+        <v>44753</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19256,7 +19246,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19299,7 +19289,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 34488-2026</t>
+          <t>A 14429-2022</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19313,10 +19303,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46255</v>
+        <v>44652</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19329,7 +19319,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19372,7 +19362,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 54849-2023</t>
+          <t>A 17296-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19386,10 +19376,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45236</v>
+        <v>45035</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19401,8 +19391,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I246" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19445,7 +19440,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 34489-2026</t>
+          <t>A 21397-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19459,10 +19454,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46255</v>
+        <v>45063</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19475,7 +19470,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19518,7 +19513,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 45377-2023</t>
+          <t>A 60285-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19532,10 +19527,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45193</v>
+        <v>45258</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19548,7 +19543,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19591,7 +19586,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 47354-2023</t>
+          <t>A 10122-2025</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19605,10 +19600,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45202</v>
+        <v>45719</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19621,7 +19616,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19664,7 +19659,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 34572-2024</t>
+          <t>A 9971-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19678,10 +19673,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45526</v>
+        <v>44985</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19694,7 +19689,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19737,7 +19732,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 17937-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19747,14 +19742,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46213</v>
+        <v>45040</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19766,8 +19761,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I251" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19810,7 +19810,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 49931-2024</t>
+          <t>A 15779-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19824,10 +19824,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45597</v>
+        <v>45404</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19839,13 +19839,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19888,7 +19883,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 54785-2022</t>
+          <t>A 9292-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19902,10 +19897,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44883</v>
+        <v>44980</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19918,7 +19913,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19961,7 +19956,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 6522-2025</t>
+          <t>A 19747-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19975,10 +19970,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45699</v>
+        <v>45432</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19991,7 +19986,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20034,7 +20029,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 3276-2024</t>
+          <t>A 54785-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20048,10 +20043,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45317</v>
+        <v>44883</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20064,7 +20059,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.4</v>
+        <v>8.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20107,7 +20102,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 6522-2025</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20121,10 +20116,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46265</v>
+        <v>45699</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20137,7 +20132,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20180,7 +20175,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 16342-2023</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20194,10 +20189,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46266</v>
+        <v>45028</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20210,7 +20205,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20253,7 +20248,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 19747-2024</t>
+          <t>A 29008-2022</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20267,10 +20262,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45432</v>
+        <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20283,7 +20278,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20326,7 +20321,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 36555-2026</t>
+          <t>A 8328-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20340,10 +20335,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46269</v>
+        <v>45352</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20356,7 +20351,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20399,7 +20394,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 60242-2022</t>
+          <t>A 26811-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20413,10 +20408,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>44910</v>
+        <v>45093</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20429,7 +20424,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20472,7 +20467,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 9337-2022</t>
+          <t>A 48158-2023</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20486,10 +20481,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>44616</v>
+        <v>45205</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20501,8 +20496,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I261" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20545,7 +20545,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 21233-2023</t>
+          <t>A 21487-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20559,10 +20559,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45062</v>
+        <v>45063</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>3.3</v>
+        <v>1.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20618,7 +20618,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 19745-2024</t>
+          <t>A 6548-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20632,10 +20632,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45432</v>
+        <v>44601</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20691,7 +20691,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 47679-2024</t>
+          <t>A 18961-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20705,10 +20705,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45588</v>
+        <v>44690</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20764,7 +20764,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 15660-2024</t>
+          <t>A 58247-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20778,10 +20778,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45404</v>
+        <v>45632</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>2.9</v>
+        <v>8.4</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20837,7 +20837,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 66424-2021</t>
+          <t>A 41889-2023</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20851,10 +20851,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44518</v>
+        <v>45176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20910,7 +20910,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 39583-2022</t>
+          <t>A 47205-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20924,10 +20924,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>44818</v>
+        <v>45202</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20940,7 +20940,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20983,7 +20983,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 10122-2025</t>
+          <t>A 6357-2023</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20997,10 +20997,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45719</v>
+        <v>44965</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21056,7 +21056,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 38060-2026</t>
+          <t>A 57513-2022</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21066,14 +21066,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46280</v>
+        <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21129,7 +21129,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 65113-2023</t>
+          <t>A 37421-2024</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21143,10 +21143,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45287</v>
+        <v>45540</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21159,7 +21159,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21202,7 +21202,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 56830-2024</t>
+          <t>A 3280-2023</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21216,10 +21216,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45628</v>
+        <v>44949</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21232,7 +21232,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21275,7 +21275,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 22297-2026</t>
+          <t>A 8890-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21289,10 +21289,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>46154</v>
+        <v>45357</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21348,7 +21348,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 33090-2026</t>
+          <t>A 42623-2024</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21362,10 +21362,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46245</v>
+        <v>45565</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21421,7 +21421,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 57862-2023</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21435,10 +21435,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45247</v>
+        <v>45202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>1.2</v>
+        <v>7</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 24367-2025</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21508,10 +21508,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>45797</v>
+        <v>45317</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 35806-2026</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21581,10 +21581,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>46265</v>
+        <v>45404</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21640,7 +21640,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 33177-2026</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21654,10 +21654,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>46245</v>
+        <v>44979</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 33076-2026</t>
+          <t>A 57862-2023</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -21727,10 +21727,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>46245</v>
+        <v>45247</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -21786,24 +21786,24 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 2336-2024</t>
+          <t>S 2472-2020</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>45310</v>
+        <v>44140</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         </is>
       </c>
       <c r="I279" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -21859,24 +21859,24 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 59399-2021</t>
+          <t>S 1221-2020</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>44491</v>
+        <v>43951</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -21932,7 +21932,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>S 2472-2020</t>
+          <t>S 3578-2022</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -21942,14 +21942,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>44140</v>
+        <v>44735</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21962,7 +21962,7 @@
         </is>
       </c>
       <c r="I281" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22005,7 +22005,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>S 1221-2020</t>
+          <t>S 70-2024</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22015,14 +22015,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>43951</v>
+        <v>45300</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22035,7 +22035,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>0.6</v>
+        <v>5.9</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22078,7 +22078,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>S 3578-2022</t>
+          <t>S 536-2025</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22088,14 +22088,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>44735</v>
+        <v>45708</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22148,10 +22148,10 @@
       </c>
       <c r="V283" s="2" t="inlineStr"/>
     </row>
-    <row r="284" ht="15" customHeight="1">
+    <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>S 70-2024</t>
+          <t>S 508-2026</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22161,14 +22161,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>45300</v>
+        <v>46076</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>5.9</v>
+        <v>42.4</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22220,152 +22220,6 @@
         <v>0</v>
       </c>
       <c r="V284" s="2" t="inlineStr"/>
-    </row>
-    <row r="285" ht="15" customHeight="1">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>S 536-2025</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Åtgärd i nyckelbiotop</t>
-        </is>
-      </c>
-      <c r="D285" s="1" t="n">
-        <v>45708</v>
-      </c>
-      <c r="E285" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I285" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J285" t="n">
-        <v>0</v>
-      </c>
-      <c r="K285" t="n">
-        <v>0</v>
-      </c>
-      <c r="L285" t="n">
-        <v>0</v>
-      </c>
-      <c r="M285" t="n">
-        <v>0</v>
-      </c>
-      <c r="N285" t="n">
-        <v>0</v>
-      </c>
-      <c r="O285" t="n">
-        <v>0</v>
-      </c>
-      <c r="P285" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
-      <c r="R285" t="n">
-        <v>0</v>
-      </c>
-      <c r="S285" t="n">
-        <v>0</v>
-      </c>
-      <c r="T285" t="n">
-        <v>0</v>
-      </c>
-      <c r="U285" t="n">
-        <v>0</v>
-      </c>
-      <c r="V285" s="2" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>S 508-2026</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D286" s="1" t="n">
-        <v>46076</v>
-      </c>
-      <c r="E286" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I286" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="J286" t="n">
-        <v>0</v>
-      </c>
-      <c r="K286" t="n">
-        <v>0</v>
-      </c>
-      <c r="L286" t="n">
-        <v>0</v>
-      </c>
-      <c r="M286" t="n">
-        <v>0</v>
-      </c>
-      <c r="N286" t="n">
-        <v>0</v>
-      </c>
-      <c r="O286" t="n">
-        <v>0</v>
-      </c>
-      <c r="P286" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
-      <c r="R286" t="n">
-        <v>0</v>
-      </c>
-      <c r="S286" t="n">
-        <v>0</v>
-      </c>
-      <c r="T286" t="n">
-        <v>0</v>
-      </c>
-      <c r="U286" t="n">
-        <v>0</v>
-      </c>
-      <c r="V286" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>44571</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45926</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46255</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>46018</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>44952</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>45323</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44994</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45173</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>46188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45331</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>45043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44749</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44687</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44536</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44613</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44531</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44881</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>44564</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44636</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>44658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>44656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>44629</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>44573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>44593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44881</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44487</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44799</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45271</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45344</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45339</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45254</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45394</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45287</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44883</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45258</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>46020</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44833</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46019</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46020</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46020</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>46027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46027</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>46027</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45797</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>46029</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45310</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>44922</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>46027</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44972</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44592</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45590</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>46055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>46055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>46055</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>46066</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>46066</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>46066</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45133</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45432</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45926</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45926</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46077</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44942</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>45546</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45929</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45195</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44970</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44970</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>46105</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>46105</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44777</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>46105</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44852</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45257</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45624</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44952</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44903</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44518</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>45973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45020</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45526</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44722</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45986</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45685</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45685</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45986</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45158</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45782</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45433</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45992</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45581</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45999</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>46139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46139</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>45782</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45793</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>46006</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>46006</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>46006</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>46139</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>46006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45992</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45228</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>45687</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>45761</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>45063</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45215</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>44883</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>45204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44910</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45705</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>45705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>46147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>46154</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>46154</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45411</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45218</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45093</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44607</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45354</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>44491</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>44818</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>46170</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>45062</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45699</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>45790</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>45481</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>46177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45433</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>45404</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>46189</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>46049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45569</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45569</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45590</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>46195</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45628</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45597</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45148</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44587</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45173</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44575</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44573</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>46210</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45204</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46255</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>46255</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>46213</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44725</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45193</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44749</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45719</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45236</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46265</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>44830</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44974</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46280</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>46154</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44894</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>45063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46245</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>46245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45336</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>46245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45036</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44613</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>45093</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46141</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44949</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46265</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>44949</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44753</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44652</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45035</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45063</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45258</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45719</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>44985</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45040</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45404</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44980</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45432</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44883</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45699</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45028</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45352</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45093</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45205</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45063</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44601</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>44690</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45632</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45202</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44965</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45540</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>44949</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45357</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45565</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45317</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45404</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44979</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45247</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44140</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>43951</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44735</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45300</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45708</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46076</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>44571</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>45926</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45253</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46255</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>46018</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>44770</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>44952</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>45323</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>44994</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45173</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>46188</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45331</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44573</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>45043</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>45790</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>44613</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>44749</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44687</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44869</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>44536</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>44613</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3818,7 +3818,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>44531</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>44881</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>44564</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         <v>44613</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>44636</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>44658</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>44573</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>44656</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>44629</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>44573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>44593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>44881</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>44480</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>44487</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>44603</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>44728</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>44799</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
         <v>45271</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>45344</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>45719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
         <v>45339</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>45254</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45394</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>45287</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>44883</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45258</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>45588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>46020</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         <v>44833</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46019</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>46020</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>46020</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>46027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>46027</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>46027</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6675,7 +6675,7 @@
         <v>45797</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>46029</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>45310</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>44922</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>46027</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44918</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44899</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>44972</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44592</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>45590</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>46055</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>46055</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>46055</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
         <v>44616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>46066</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>46066</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>46066</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>46066</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45133</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45432</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45926</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45926</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45009</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46077</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44942</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>45546</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45929</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44957</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45195</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>45597</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>44970</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>44970</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         <v>46105</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         <v>46105</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>44777</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>46105</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>44852</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45257</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45624</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44952</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44903</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44953</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44518</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>45973</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>45020</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>45526</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44722</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>45986</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>45685</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>45685</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>45986</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>45758</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>45158</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>45782</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>45433</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>45189</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45992</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>45581</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>45999</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45999</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>46139</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46139</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>45782</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45793</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>46006</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>46006</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>46006</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>46139</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>46006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>45992</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12404,7 +12404,7 @@
         <v>45228</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12477,7 +12477,7 @@
         <v>45687</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>45761</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12623,7 +12623,7 @@
         <v>45063</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45215</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>44883</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>45204</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44910</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45705</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13134,7 +13134,7 @@
         <v>45705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>46147</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>44593</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>46154</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>46154</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45411</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45218</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         <v>45093</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44607</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45354</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>44491</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>44818</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>46170</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14171,7 +14171,7 @@
         <v>45062</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>45699</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>45790</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14390,7 +14390,7 @@
         <v>45481</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>46177</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45099</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44937</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14760,7 +14760,7 @@
         <v>45176</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45433</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>45404</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>46189</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>46049</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>45569</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>45569</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15281,7 +15281,7 @@
         <v>45590</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15354,7 +15354,7 @@
         <v>46195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15427,7 +15427,7 @@
         <v>46195</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15500,7 +15500,7 @@
         <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>45719</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45628</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>45597</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45148</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15943,7 +15943,7 @@
         <v>44587</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>45173</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44575</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45167</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>44573</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>46210</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45204</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45211</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45211</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46255</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45195</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>46255</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>46213</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44725</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45183</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45193</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45183</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44749</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45719</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45236</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46265</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45215</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>44830</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>44974</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>45170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46280</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>46154</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>44894</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>45063</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46245</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>46245</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45336</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>46245</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45036</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>44613</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>45093</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46141</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>44949</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46265</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>44949</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44753</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44652</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45035</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45063</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45258</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45719</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>44985</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45040</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45404</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>44980</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45432</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44883</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45699</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45028</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>44749</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45352</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45093</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>45205</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45063</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44601</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>44690</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45632</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45176</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45202</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44965</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44896</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45540</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>44949</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45357</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45565</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45202</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>45317</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>45404</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>44979</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45247</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>44140</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>43951</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>44735</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45300</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45708</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46076</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45238</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 46766-2025</t>
+          <t>A 1075-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45926</v>
+        <v>44571</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1187,16 +1187,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -1220,12 +1220,125 @@
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>17</v>
+      </c>
+      <c r="U7" t="n">
+        <v>17</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Tallticka
+Blåmossa
+Grönpyrola
+Rostfläck</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 46766-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45926</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>8</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Bronshjon
@@ -1234,152 +1347,39 @@
 Mattlummer</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 1075-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44571</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>17</v>
-      </c>
-      <c r="U8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Tallticka
-Blåmossa
-Grönpyrola
-Rostfläck</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>45253</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44712</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>44916</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>46255</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44712</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44770</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 23067-2025</t>
+          <t>A 4051-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45790</v>
+        <v>44952</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2184,31 +2184,31 @@
         </is>
       </c>
       <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2220,894 +2220,894 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 4148-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 11749-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44994</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Adam och eva</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 40874-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 5414-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 27253-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="Z21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 1543-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44573</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 18758-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Z23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 23067-2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45790</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 23067-2025 artfynd.xlsx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 23067-2025 karta.png", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 23067-2025 georefererad karta.tif", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 23067-2025 FSC-klagomål.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 23067-2025 FSC-klagomål mail.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 23067-2025 tillsynsbegäran.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 23067-2025 tillsynsbegäran mail.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 23067-2025 prioriterade fågelarter.docx", "A 23067-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 1543-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44573</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Hasselsnok</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 4148-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Gullviva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5414-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 11749-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>44994</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 18758-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45043</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 40874-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 4051-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 27253-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Z24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>44613</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>44749</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 51436-2022</t>
+          <t>A 18684-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44869</v>
+        <v>44687</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3330,7 +3330,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18684-2022</t>
+          <t>A 51436-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44687</v>
+        <v>44869</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>44852</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>44536</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>44613</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>44531</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44603</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         <v>44531</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>44881</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>44613</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44564</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>44613</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         <v>44658</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>44573</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>44656</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>44629</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44573</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>44881</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>44603</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44480</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         <v>44487</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>44603</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44728</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44753</v>
+        <v>45271</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5189,8 +5189,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5233,7 +5238,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 35659-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5247,10 +5252,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45687</v>
+        <v>44799</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5263,7 +5268,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5306,7 +5311,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5320,10 +5325,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45597</v>
+        <v>45719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5335,13 +5340,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5384,7 +5384,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18961-2022</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5398,10 +5398,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44690</v>
+        <v>45339</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5457,7 +5457,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 7634-2022</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44607</v>
+        <v>45344</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5530,7 +5530,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 7254-2023</t>
+          <t>A 59516-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5540,14 +5540,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44970</v>
+        <v>45254</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5603,7 +5603,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35908-2023</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5617,10 +5617,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45148</v>
+        <v>45394</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6548-2022</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44601</v>
+        <v>44883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5749,7 +5749,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 4856-2023</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44957</v>
+        <v>45287</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5822,7 +5822,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48243-2024</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45590</v>
+        <v>45258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5895,7 +5895,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59516-2023</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5905,14 +5905,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45254</v>
+        <v>45588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.4</v>
+        <v>5.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5968,7 +5968,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45590</v>
+        <v>46020</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6041,7 +6041,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6055,10 +6055,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45020</v>
+        <v>46019</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 16342-2023</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45028</v>
+        <v>46020</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6187,7 +6187,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 37421-2024</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45540</v>
+        <v>44833</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6260,7 +6260,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 19937-2024</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45433</v>
+        <v>46020</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6333,7 +6333,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6347,10 +6347,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45189</v>
+        <v>46027</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6406,7 +6406,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 57862-2023</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6420,10 +6420,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45247</v>
+        <v>46027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6479,7 +6479,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 290-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46006</v>
+        <v>46027</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 24367-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46006</v>
+        <v>45797</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6625,7 +6625,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 2336-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6639,10 +6639,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46006</v>
+        <v>45310</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46006</v>
+        <v>44922</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 560-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45344</v>
+        <v>46029</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6800,8 +6800,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6844,7 +6849,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 24367-2025</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6858,10 +6863,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45797</v>
+        <v>44918</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6874,7 +6879,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>5.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6917,7 +6922,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6931,10 +6936,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44749</v>
+        <v>45901</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6947,7 +6952,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6990,7 +6995,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7004,10 +7009,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45719</v>
+        <v>44899</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7020,7 +7025,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7063,7 +7068,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7077,10 +7082,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45176</v>
+        <v>44972</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7093,7 +7098,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7136,7 +7141,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2336-2024</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7150,10 +7155,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45310</v>
+        <v>44592</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7166,7 +7171,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>11.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7209,7 +7214,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 48243-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7223,10 +7228,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44949</v>
+        <v>45590</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7282,7 +7287,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 260-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7296,10 +7301,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45901</v>
+        <v>46027</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7312,7 +7317,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7355,7 +7360,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7369,10 +7374,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45336</v>
+        <v>44616</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7385,7 +7390,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7428,7 +7433,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7442,10 +7447,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44573</v>
+        <v>45546</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7458,7 +7463,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7501,7 +7506,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7515,10 +7520,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45202</v>
+        <v>45133</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7531,7 +7536,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.4</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7574,7 +7579,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7588,10 +7593,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44833</v>
+        <v>45432</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7604,7 +7609,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7647,7 +7652,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7661,10 +7666,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45204</v>
+        <v>45009</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7677,7 +7682,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7720,7 +7725,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7734,10 +7739,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45183</v>
+        <v>45926</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7750,7 +7755,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7793,7 +7798,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7807,10 +7812,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45183</v>
+        <v>45926</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7823,7 +7828,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7866,7 +7871,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7880,10 +7885,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45271</v>
+        <v>45926</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7895,13 +7900,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>11.1</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7944,7 +7944,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7958,10 +7958,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44592</v>
+        <v>45926</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8017,7 +8017,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8031,10 +8031,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45926</v>
+        <v>44942</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8090,7 +8090,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8104,10 +8104,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45926</v>
+        <v>45546</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8163,7 +8163,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 4856-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8177,10 +8177,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45929</v>
+        <v>44957</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8236,7 +8236,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8253,7 +8253,7 @@
         <v>45929</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8266,7 +8266,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8309,7 +8309,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8319,14 +8319,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45926</v>
+        <v>45195</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8382,7 +8382,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8396,10 +8396,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8455,7 +8455,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45093</v>
+        <v>45597</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8484,8 +8484,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8528,7 +8533,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 59399-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8542,10 +8547,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46020</v>
+        <v>44491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8558,7 +8563,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8601,7 +8606,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 7254-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8615,10 +8620,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46020</v>
+        <v>44970</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8631,7 +8636,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8674,7 +8679,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8688,10 +8693,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46019</v>
+        <v>44970</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8704,7 +8709,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8747,7 +8752,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 6580-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8761,10 +8766,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46020</v>
+        <v>45699</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8777,7 +8782,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8820,7 +8825,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 22974-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8830,14 +8835,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45158</v>
+        <v>45790</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8850,7 +8855,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8893,7 +8898,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8907,10 +8912,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44593</v>
+        <v>44897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8923,7 +8928,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8966,7 +8971,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 290-2026</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8980,10 +8985,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46027</v>
+        <v>44777</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8996,7 +9001,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9039,7 +9044,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 59399-2021</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9053,10 +9058,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44491</v>
+        <v>45601</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9069,7 +9074,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9112,7 +9117,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 6161-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9126,10 +9131,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46027</v>
+        <v>46055</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9142,7 +9147,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9185,7 +9190,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 6160-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9199,10 +9204,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46027</v>
+        <v>46055</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9215,7 +9220,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9258,7 +9263,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 6162-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9272,10 +9277,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46029</v>
+        <v>46055</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9287,13 +9292,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9336,7 +9336,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9350,10 +9350,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44974</v>
+        <v>44852</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9409,7 +9409,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22974-2025</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9419,14 +9419,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45790</v>
+        <v>45257</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9482,7 +9482,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 6580-2025</t>
+          <t>A 56303-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9496,10 +9496,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45699</v>
+        <v>45624</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9555,7 +9555,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9569,10 +9569,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45036</v>
+        <v>44952</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9628,7 +9628,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35659-2022</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9642,10 +9642,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44799</v>
+        <v>44903</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9701,7 +9701,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 8845-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44894</v>
+        <v>46066</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9774,7 +9774,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 8818-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9788,10 +9788,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46027</v>
+        <v>46066</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9847,7 +9847,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 56097-2025</t>
+          <t>A 8822-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45973</v>
+        <v>46066</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9920,7 +9920,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 8823-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9934,10 +9934,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44587</v>
+        <v>46066</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9993,7 +9993,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 56097-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10007,10 +10007,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44749</v>
+        <v>45973</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10023,7 +10023,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6.6</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10066,7 +10066,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10080,10 +10080,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45404</v>
+        <v>44953</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10139,7 +10139,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 56303-2024</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45624</v>
+        <v>44518</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10169,7 +10169,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10212,7 +10212,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10226,10 +10226,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45986</v>
+        <v>45020</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10285,7 +10285,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 58749-2025</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10299,10 +10299,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45986</v>
+        <v>45526</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10358,7 +10358,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 3267-2023</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10372,10 +10372,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44949</v>
+        <v>44722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10431,7 +10431,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 58749-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10445,10 +10445,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45989</v>
+        <v>45986</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10460,13 +10460,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10509,7 +10504,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10523,10 +10518,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45601</v>
+        <v>45986</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10539,7 +10534,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10582,7 +10577,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10596,10 +10591,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45357</v>
+        <v>45685</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10612,7 +10607,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.4</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10655,7 +10650,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10669,10 +10664,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45992</v>
+        <v>45685</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10685,7 +10680,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10728,7 +10723,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10742,10 +10737,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45035</v>
+        <v>45758</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10757,13 +10752,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10806,7 +10796,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 10575-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10820,10 +10810,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44937</v>
+        <v>46077</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10836,7 +10826,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.7</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10879,7 +10869,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10893,10 +10883,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44937</v>
+        <v>45158</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10909,7 +10899,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10952,7 +10942,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10966,10 +10956,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46055</v>
+        <v>45189</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10982,7 +10972,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11025,7 +11015,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11039,10 +11029,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46055</v>
+        <v>45992</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11055,7 +11045,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11098,7 +11088,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11112,10 +11102,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45258</v>
+        <v>45989</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11127,8 +11117,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11171,7 +11166,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11188,7 +11183,7 @@
         <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11206,7 +11201,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11249,7 +11244,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11266,7 +11261,7 @@
         <v>45999</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11284,7 +11279,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11327,7 +11322,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11341,10 +11336,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46055</v>
+        <v>46006</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11357,7 +11352,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11400,7 +11395,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11414,10 +11409,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44965</v>
+        <v>46006</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11430,7 +11425,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11473,7 +11468,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11487,10 +11482,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44883</v>
+        <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11503,7 +11498,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11546,7 +11541,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11560,10 +11555,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45176</v>
+        <v>46006</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11576,7 +11571,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11619,7 +11614,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11633,10 +11628,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45205</v>
+        <v>45228</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11648,13 +11643,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11697,7 +11687,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11711,10 +11701,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44979</v>
+        <v>45687</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11727,7 +11717,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11770,7 +11760,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11784,10 +11774,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46066</v>
+        <v>45761</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11800,7 +11790,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11843,7 +11833,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 15078-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11857,10 +11847,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46066</v>
+        <v>46105</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11873,7 +11863,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11916,7 +11906,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8823-2026</t>
+          <t>A 15138-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11930,10 +11920,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46066</v>
+        <v>46105</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11946,7 +11936,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11989,7 +11979,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 15096-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12003,10 +11993,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46066</v>
+        <v>46105</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12019,7 +12009,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12062,7 +12052,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12076,10 +12066,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45099</v>
+        <v>45063</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12092,7 +12082,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12135,7 +12125,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12149,10 +12139,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44942</v>
+        <v>45215</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12165,7 +12155,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12208,7 +12198,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12218,14 +12208,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45354</v>
+        <v>44883</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12238,7 +12228,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12281,7 +12271,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12295,10 +12285,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46077</v>
+        <v>45204</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12311,7 +12301,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12354,7 +12344,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12364,14 +12354,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44896</v>
+        <v>44910</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12384,7 +12374,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12427,7 +12417,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12441,10 +12431,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45093</v>
+        <v>44585</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12457,7 +12447,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12500,7 +12490,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12514,10 +12504,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45093</v>
+        <v>45705</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12530,7 +12520,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12573,7 +12563,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12587,10 +12577,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44585</v>
+        <v>45705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12603,7 +12593,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12646,7 +12636,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12660,10 +12650,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44903</v>
+        <v>44593</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12676,7 +12666,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12719,7 +12709,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12733,10 +12723,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44985</v>
+        <v>45411</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12749,7 +12739,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12792,7 +12782,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12806,10 +12796,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45481</v>
+        <v>45218</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12821,8 +12811,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12865,7 +12860,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12879,10 +12874,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45228</v>
+        <v>45093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12895,7 +12890,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12938,7 +12933,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 7634-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12952,10 +12947,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45167</v>
+        <v>44607</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12968,7 +12963,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13011,7 +13006,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13025,10 +13020,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46105</v>
+        <v>45354</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13041,7 +13036,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13084,7 +13079,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 21396-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13098,10 +13093,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46105</v>
+        <v>45782</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13114,7 +13109,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13157,7 +13152,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 15096-2026</t>
+          <t>A 19925-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13171,10 +13166,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46105</v>
+        <v>45433</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13187,7 +13182,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13230,7 +13225,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 46186-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13244,10 +13239,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44897</v>
+        <v>45581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13260,7 +13255,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13303,7 +13298,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13313,14 +13308,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45170</v>
+        <v>44818</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13333,7 +13328,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13376,7 +13371,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13390,10 +13385,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45761</v>
+        <v>45062</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13406,7 +13401,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13449,7 +13444,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 20248-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13463,10 +13458,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45411</v>
+        <v>46139</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13478,8 +13473,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13522,7 +13522,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 21511-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13532,14 +13532,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45685</v>
+        <v>45782</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13595,7 +13595,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13609,10 +13609,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45685</v>
+        <v>45793</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13668,7 +13668,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 20307-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13682,10 +13682,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45632</v>
+        <v>46139</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8.4</v>
+        <v>2.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13755,10 +13755,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44852</v>
+        <v>45481</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13828,10 +13828,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45215</v>
+        <v>45992</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13887,7 +13887,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13901,10 +13901,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45352</v>
+        <v>45099</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13960,7 +13960,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13974,10 +13974,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45258</v>
+        <v>44937</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14033,7 +14033,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14047,10 +14047,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44980</v>
+        <v>44937</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>6.4</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14106,7 +14106,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14120,10 +14120,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44587</v>
+        <v>45176</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14179,7 +14179,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 19937-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14196,7 +14196,7 @@
         <v>45433</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.4</v>
+        <v>11.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14252,7 +14252,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14266,10 +14266,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44725</v>
+        <v>45404</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14325,7 +14325,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45782</v>
+        <v>45569</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14352,6 +14352,11 @@
       <c r="G178" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -14398,7 +14403,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14412,10 +14417,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45793</v>
+        <v>45569</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14427,8 +14432,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14471,7 +14481,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14485,10 +14495,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45992</v>
+        <v>45590</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14501,7 +14511,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14544,7 +14554,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20248-2026</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14558,10 +14568,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46139</v>
+        <v>45629</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14573,13 +14583,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14622,7 +14627,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14636,10 +14641,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45565</v>
+        <v>45036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14652,7 +14657,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14695,7 +14700,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14709,10 +14714,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45040</v>
+        <v>45719</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14724,13 +14729,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14773,7 +14773,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14787,10 +14787,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45581</v>
+        <v>46147</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14802,8 +14802,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14846,7 +14851,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 20307-2026</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14860,10 +14865,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46139</v>
+        <v>45628</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14876,7 +14881,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>2.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14919,7 +14924,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14933,10 +14938,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44728</v>
+        <v>45597</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14946,6 +14951,11 @@
       <c r="G186" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -14992,7 +15002,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 35908-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15006,10 +15016,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45339</v>
+        <v>45148</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15022,7 +15032,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15065,7 +15075,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15079,10 +15089,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44652</v>
+        <v>46154</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15095,7 +15105,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15138,7 +15148,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15152,10 +15162,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45036</v>
+        <v>44587</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15168,7 +15178,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15211,7 +15221,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 7266-2023</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15225,10 +15235,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44970</v>
+        <v>45173</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15241,7 +15251,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15284,7 +15294,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 21511-2025</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15294,14 +15304,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45782</v>
+        <v>44575</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15314,7 +15324,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15357,7 +15367,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 252-2023</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15371,10 +15381,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44922</v>
+        <v>46154</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15387,7 +15397,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15430,7 +15440,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 45783-2023</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15440,14 +15450,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45195</v>
+        <v>44587</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15460,7 +15470,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15503,7 +15513,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 7582-2023</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15517,10 +15527,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44972</v>
+        <v>46155</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15532,8 +15542,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15576,7 +15591,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15590,10 +15605,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46147</v>
+        <v>45167</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15605,13 +15620,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15654,7 +15664,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 54812-2022</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15664,14 +15674,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44883</v>
+        <v>44573</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15684,7 +15694,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15727,7 +15737,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 43151-2023</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15741,10 +15751,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45183</v>
+        <v>45204</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15757,7 +15767,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15800,7 +15810,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15814,10 +15824,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46154</v>
+        <v>45211</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15830,7 +15840,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15873,7 +15883,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31862-2022</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15887,10 +15897,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44777</v>
+        <v>45211</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15903,7 +15913,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15946,7 +15956,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15960,10 +15970,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46154</v>
+        <v>45195</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15976,7 +15986,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.1</v>
+        <v>15.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16019,7 +16029,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16033,10 +16043,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46155</v>
+        <v>44728</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16048,13 +16058,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16097,7 +16102,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 57864-2022</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16111,10 +16116,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44899</v>
+        <v>44725</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16127,7 +16132,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16170,7 +16175,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 15779-2024</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16184,10 +16189,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45404</v>
+        <v>45183</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16200,7 +16205,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16243,7 +16248,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 50041-2023</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16257,10 +16262,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45215</v>
+        <v>46170</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16273,7 +16278,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16316,7 +16321,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 4331-2023</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16330,10 +16335,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44953</v>
+        <v>45193</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16346,7 +16351,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16389,7 +16394,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 42401-2022</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16403,10 +16408,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44830</v>
+        <v>45183</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16462,7 +16467,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 59741-2023</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16476,10 +16481,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45257</v>
+        <v>45183</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16492,7 +16497,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16535,7 +16540,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 8685-2022</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16549,10 +16554,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44613</v>
+        <v>44749</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16565,7 +16570,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16608,7 +16613,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 43516-2024</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16622,10 +16627,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45569</v>
+        <v>45719</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16637,13 +16642,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>10.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16686,7 +16686,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 43518-2024</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16700,10 +16700,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45569</v>
+        <v>45236</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16715,13 +16715,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16764,7 +16759,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 21399-2023</t>
+          <t>A 26049-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16778,10 +16773,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45063</v>
+        <v>46177</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16793,8 +16788,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16837,7 +16837,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 14417-2024</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16851,10 +16851,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45394</v>
+        <v>45215</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16910,7 +16910,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 17717-2025</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16924,10 +16924,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45758</v>
+        <v>44830</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16983,7 +16983,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 8143-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16997,10 +16997,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46170</v>
+        <v>44974</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17056,7 +17056,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 34357-2023</t>
+          <t>A 27525-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17070,10 +17070,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45133</v>
+        <v>46189</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17129,7 +17129,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 21483-2023</t>
+          <t>A 4965-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17143,10 +17143,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45063</v>
+        <v>46049</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17202,7 +17202,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38431-2024</t>
+          <t>A 28093-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17216,10 +17216,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45546</v>
+        <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17275,7 +17275,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38438-2024</t>
+          <t>A 28119-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17289,10 +17289,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45546</v>
+        <v>46195</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17348,7 +17348,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 10135-2025</t>
+          <t>A 40728-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17358,14 +17358,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45719</v>
+        <v>45170</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>10.3</v>
+        <v>0.5</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17421,7 +17421,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 1974-2022</t>
+          <t>A 58262-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17435,10 +17435,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44575</v>
+        <v>44894</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17494,7 +17494,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 41314-2023</t>
+          <t>A 21399-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17508,10 +17508,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45173</v>
+        <v>45063</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17567,7 +17567,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 26049-2026</t>
+          <t>A 6022-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17581,10 +17581,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46177</v>
+        <v>45336</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17596,13 +17596,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17645,7 +17640,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 23827-2022</t>
+          <t>A 17585-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17659,10 +17654,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44722</v>
+        <v>45036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17675,7 +17670,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17718,7 +17713,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 21487-2023</t>
+          <t>A 8685-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17732,10 +17727,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45063</v>
+        <v>44613</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17748,7 +17743,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.6</v>
+        <v>4.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17791,7 +17786,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 7646-2025</t>
+          <t>A 30523-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17805,10 +17800,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45705</v>
+        <v>46210</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17821,7 +17816,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -17864,7 +17859,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 7647-2025</t>
+          <t>A 26821-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17878,10 +17873,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45705</v>
+        <v>45093</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17894,7 +17889,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17937,7 +17932,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 45873-2023</t>
+          <t>A 3267-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17951,10 +17946,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45195</v>
+        <v>44949</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17967,7 +17962,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>15.8</v>
+        <v>0.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18010,7 +18005,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 57144-2024</t>
+          <t>A 3276-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18024,10 +18019,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45629</v>
+        <v>44949</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18040,7 +18035,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18083,7 +18078,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 3276-2023</t>
+          <t>A 29424-2022</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18097,10 +18092,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44949</v>
+        <v>44753</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18113,7 +18108,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18156,7 +18151,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 50992-2023</t>
+          <t>A 34488-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18170,10 +18165,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45218</v>
+        <v>46255</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18185,13 +18180,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18234,7 +18224,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 62048-2022</t>
+          <t>A 34489-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18248,10 +18238,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44918</v>
+        <v>46255</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18264,7 +18254,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18307,7 +18297,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 10120-2025</t>
+          <t>A 30964-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18317,14 +18307,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45719</v>
+        <v>46213</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18380,7 +18370,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 14429-2022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18394,10 +18384,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46049</v>
+        <v>44652</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18410,7 +18400,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18453,7 +18443,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 17296-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18467,10 +18457,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46189</v>
+        <v>45035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18482,8 +18472,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18543,7 +18538,7 @@
         <v>45063</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18599,7 +18594,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 60285-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18613,10 +18608,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46195</v>
+        <v>45258</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18629,7 +18624,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>7.7</v>
+        <v>2.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18672,7 +18667,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 14082-2023</t>
+          <t>A 35740-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18686,10 +18681,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45009</v>
+        <v>46265</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18702,7 +18697,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18745,7 +18740,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 35924-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18759,10 +18754,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46195</v>
+        <v>46266</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18775,7 +18770,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18818,7 +18813,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 4047-2023</t>
+          <t>A 10122-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18832,10 +18827,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44952</v>
+        <v>45719</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18848,7 +18843,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18891,7 +18886,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 47962-2023</t>
+          <t>A 9971-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18905,10 +18900,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45204</v>
+        <v>44985</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18921,7 +18916,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18964,7 +18959,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 49345-2023</t>
+          <t>A 17937-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18978,10 +18973,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45211</v>
+        <v>45040</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18993,8 +18988,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19037,7 +19037,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 49348-2023</t>
+          <t>A 15779-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19051,10 +19051,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45211</v>
+        <v>45404</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19110,7 +19110,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 54849-2023</t>
+          <t>A 9292-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45236</v>
+        <v>44980</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.2</v>
+        <v>6.4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19183,7 +19183,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 30523-2026</t>
+          <t>A 19747-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19197,10 +19197,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46210</v>
+        <v>45432</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19256,7 +19256,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 45377-2023</t>
+          <t>A 36555-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19270,10 +19270,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45193</v>
+        <v>46269</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19329,7 +19329,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 47354-2023</t>
+          <t>A 54785-2022</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19343,10 +19343,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45202</v>
+        <v>44883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19402,7 +19402,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 34572-2024</t>
+          <t>A 6522-2025</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19416,10 +19416,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45526</v>
+        <v>45699</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19475,7 +19475,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 34488-2026</t>
+          <t>A 16342-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19489,10 +19489,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46255</v>
+        <v>45028</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19548,7 +19548,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 49931-2024</t>
+          <t>A 29008-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19562,10 +19562,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45597</v>
+        <v>44749</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19577,13 +19577,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I249" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19626,7 +19621,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 54785-2022</t>
+          <t>A 38060-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19640,10 +19635,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44883</v>
+        <v>46280</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19656,7 +19651,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19699,7 +19694,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 34489-2026</t>
+          <t>A 8328-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19713,10 +19708,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46255</v>
+        <v>45352</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19729,7 +19724,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19772,7 +19767,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 26811-2023</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19782,14 +19777,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>46213</v>
+        <v>45093</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19802,7 +19797,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19845,7 +19840,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 6522-2025</t>
+          <t>A 48158-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19859,10 +19854,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45699</v>
+        <v>45205</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19874,8 +19869,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19918,7 +19918,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 3276-2024</t>
+          <t>A 21487-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19932,10 +19932,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45317</v>
+        <v>45063</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19948,7 +19948,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19991,7 +19991,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 19747-2024</t>
+          <t>A 6548-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20005,10 +20005,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>45432</v>
+        <v>44601</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20064,7 +20064,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 18961-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20078,10 +20078,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>46265</v>
+        <v>44690</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20137,7 +20137,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 60242-2022</t>
+          <t>A 58247-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20151,10 +20151,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44910</v>
+        <v>45632</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20210,7 +20210,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 41889-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20224,10 +20224,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46266</v>
+        <v>45176</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20283,7 +20283,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 9337-2022</t>
+          <t>A 47205-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20297,10 +20297,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>44616</v>
+        <v>45202</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20356,7 +20356,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 21233-2023</t>
+          <t>A 6357-2023</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20370,10 +20370,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45062</v>
+        <v>44965</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20386,7 +20386,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20429,7 +20429,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 36555-2026</t>
+          <t>A 57513-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20439,14 +20439,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46269</v>
+        <v>44896</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="I261" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20502,7 +20502,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 19745-2024</t>
+          <t>A 37421-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20516,10 +20516,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45432</v>
+        <v>45540</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20575,7 +20575,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 47679-2024</t>
+          <t>A 3280-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20589,10 +20589,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45588</v>
+        <v>44949</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20648,7 +20648,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 15660-2024</t>
+          <t>A 22297-2026</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20662,10 +20662,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45404</v>
+        <v>46154</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20721,7 +20721,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 66424-2021</t>
+          <t>A 8890-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20735,10 +20735,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44518</v>
+        <v>45357</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20794,7 +20794,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 39583-2022</t>
+          <t>A 33090-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20808,10 +20808,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44818</v>
+        <v>46245</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20867,7 +20867,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 10122-2025</t>
+          <t>A 33076-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20881,10 +20881,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45719</v>
+        <v>46245</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20940,7 +20940,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 65113-2023</t>
+          <t>A 33177-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20954,10 +20954,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45287</v>
+        <v>46245</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21013,7 +21013,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 56830-2024</t>
+          <t>A 42623-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21027,10 +21027,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45628</v>
+        <v>45565</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21086,7 +21086,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 38060-2026</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21100,10 +21100,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>46280</v>
+        <v>45202</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21159,7 +21159,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 22297-2026</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21173,10 +21173,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>46154</v>
+        <v>45317</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21232,7 +21232,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 33090-2026</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21246,10 +21246,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>46245</v>
+        <v>45404</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>0.9</v>
+        <v>6.2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21305,7 +21305,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 33177-2026</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21319,10 +21319,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46245</v>
+        <v>44979</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21378,7 +21378,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 33076-2026</t>
+          <t>A 20773-2026</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21392,10 +21392,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>46245</v>
+        <v>46141</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21407,8 +21407,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I274" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21468,7 +21473,7 @@
         <v>46265</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21524,7 +21529,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 20246-2026</t>
+          <t>A 57862-2023</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -21538,10 +21543,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>46139</v>
+        <v>45247</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21553,13 +21558,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I276" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -21602,7 +21602,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 20773-2026</t>
+          <t>A 20246-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -21616,10 +21616,10 @@
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>46141</v>
+        <v>46139</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21633,11 +21633,11 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I277" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
         <v>44140</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>43951</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44735</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45300</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>45708</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>46076</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>44571</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45926</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44770</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>44573</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>45323</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45331</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44994</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45043</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45173</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>46188</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>44952</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>44613</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44869</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44687</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44536</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44603</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44881</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44613</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44564</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44658</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44573</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44656</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44881</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44487</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44728</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45687</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45597</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45540</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45433</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44970</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>44601</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44957</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45148</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45020</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45028</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45254</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45590</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45247</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46006</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45344</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>46006</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>46006</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>46006</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44749</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45719</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45176</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>46020</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>46020</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46019</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>44949</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>46020</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46027</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46027</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45336</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>46029</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45901</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44573</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45202</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45797</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45183</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45183</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45271</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44592</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45310</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>46055</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>46055</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>46055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45926</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>45926</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45929</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45929</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45926</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46066</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46066</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46066</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>46066</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45158</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44593</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>46077</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44974</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45036</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44799</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>44894</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44587</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>44749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>45404</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45624</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46105</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45601</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>46105</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45357</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45986</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45258</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45986</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>44965</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44883</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45176</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45205</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44979</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>45433</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>45099</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44942</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45354</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45782</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44896</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45793</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45093</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45093</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44585</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44903</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44491</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44985</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45481</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45228</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45167</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44897</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45761</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45411</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45685</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45685</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45632</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>44852</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45215</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45790</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45699</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45352</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45782</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44980</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>46147</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44725</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>46154</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>46155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45565</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45040</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44728</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45339</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>46170</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>44652</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45036</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44970</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44922</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45195</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44883</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>46195</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46195</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44777</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44899</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45404</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45215</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44953</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44830</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45257</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44613</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45569</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45569</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45063</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45394</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45758</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45133</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46213</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45063</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45546</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45546</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45719</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44575</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45173</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46265</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44722</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>46266</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45063</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45705</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45705</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45195</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45629</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44949</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46280</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44918</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45719</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45063</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45009</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44952</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46245</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45204</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46265</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>46139</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>46141</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45211</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45211</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45236</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45193</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45202</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45526</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45597</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>44883</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>46255</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45973</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>46255</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45699</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>46177</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45317</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46245</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45432</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>44910</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44616</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45062</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45432</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45588</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45404</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44518</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44818</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45719</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45287</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45628</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>44140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>43951</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44735</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45708</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>46076</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>44571</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45926</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44770</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>44573</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>45323</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45331</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44994</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>45043</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45173</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>46188</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>44952</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>44613</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44852</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44869</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44687</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44536</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44603</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44881</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44613</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44564</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44658</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44573</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44656</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44881</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44487</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44728</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>45687</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>45597</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45540</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>45433</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         <v>44970</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5729,7 +5729,7 @@
         <v>44601</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44957</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         <v>45148</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>45020</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>45028</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45254</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>45590</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>45189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45247</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46006</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>45344</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>46006</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>46006</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>46006</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44749</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45719</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45176</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>46020</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>46020</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>46019</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>44949</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>46020</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46027</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>46027</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45336</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>46027</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>46029</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>45901</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44573</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>46027</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45202</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>44833</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45204</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45797</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45183</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45183</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45271</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44592</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45310</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>46055</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>46055</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>46055</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45926</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>45926</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45929</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>45093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45929</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>45926</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45926</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>46066</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46066</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46066</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>46066</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45158</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>44593</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>46077</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9827,7 +9827,7 @@
         <v>44974</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>45036</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44799</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>44894</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44587</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>44749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10265,7 +10265,7 @@
         <v>45404</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45624</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>44949</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>46105</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>45601</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>46105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>46105</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45357</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45035</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10927,7 +10927,7 @@
         <v>45986</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44937</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
         <v>44937</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>45258</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>45986</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11292,7 +11292,7 @@
         <v>45989</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>44965</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11443,7 +11443,7 @@
         <v>45992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
         <v>44883</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>45999</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11667,7 +11667,7 @@
         <v>45999</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>45176</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>45205</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44979</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>45433</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>45099</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44942</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>45354</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>45782</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44896</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45793</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>45093</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45093</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44585</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44903</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45992</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44491</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>44985</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>45481</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45228</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45167</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44897</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45761</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45411</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45685</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45685</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45632</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>44852</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45215</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45790</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45699</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45352</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45782</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>45258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44980</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>46147</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>44587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>44725</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>46154</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>46154</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>46155</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45565</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45040</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44728</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45339</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>46170</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>44652</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45036</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>44970</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44922</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45195</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44972</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>44883</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46189</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>46195</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>46195</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>44777</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>44899</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45404</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45215</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44953</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44830</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45257</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>44613</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45569</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45569</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45063</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45394</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45758</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>45133</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>46213</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45063</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45546</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45546</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45719</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44575</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45173</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>46265</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44722</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>46266</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45063</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45705</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45705</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45195</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45629</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44949</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>46280</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44918</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45719</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45063</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45009</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44952</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>46245</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45204</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>46265</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>46139</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>46141</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45211</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45211</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45236</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19601,7 +19601,7 @@
         <v>45193</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45202</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19747,7 +19747,7 @@
         <v>45526</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45597</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19898,7 +19898,7 @@
         <v>44883</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>46255</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45973</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>46255</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45699</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>46177</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45317</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46245</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45432</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>44910</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44616</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>45062</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45432</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45588</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45404</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>44518</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>44818</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45719</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45287</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45628</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>44140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>43951</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44735</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45708</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>46076</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 1075-2022</t>
+          <t>A 46766-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1061,10 +1061,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44571</v>
+        <v>45926</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1110,12 +1110,125 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>8</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Bronshjon
+Flagellkvastmossa
+Stubbspretmossa
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 1075-2022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>17</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>17</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tallticka
@@ -1124,152 +1237,39 @@
 Rostfläck</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 46766-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45926</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Bronshjon
-Flagellkvastmossa
-Stubbspretmossa
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 46766-2025 artfynd.xlsx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 46766-2025 karta.png", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 46766-2025 georefererad karta.tif", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 46766-2025 karta knärot.png", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 46766-2025 FSC-klagomål.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 46766-2025 FSC-klagomål mail.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 46766-2025 tillsynsbegäran.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 46766-2025 tillsynsbegäran mail.docx", "A 46766-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>45253</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44770</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 23067-2025</t>
+          <t>A 4051-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45790</v>
+        <v>44952</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,31 +2074,31 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2110,894 +2110,894 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 4148-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 11749-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44994</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Adam och eva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 40874-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45173</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 5414-2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 27253-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 1543-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44573</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Hasselsnok</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18758-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Z22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 23067-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45790</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 23067-2025 artfynd.xlsx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 23067-2025 karta.png", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 23067-2025 georefererad karta.tif", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 23067-2025 FSC-klagomål.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 23067-2025 FSC-klagomål mail.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 23067-2025 tillsynsbegäran.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 23067-2025 tillsynsbegäran mail.docx", "A 23067-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 23067-2025 prioriterade fågelarter.docx", "A 23067-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 1543-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44573</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Hasselsnok</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 4148-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Gullviva</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 5414-2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 11749-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44994</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 18758-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45043</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 40874-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45173</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 27253-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 4051-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>44613</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 47632-2022</t>
+          <t>A 51436-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44852</v>
+        <v>44869</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 51436-2022</t>
+          <t>A 18684-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44869</v>
+        <v>44687</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 18684-2022</t>
+          <t>A 47632-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44687</v>
+        <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>44536</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44603</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44881</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44613</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44564</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44613</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44658</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44573</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44656</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44881</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>44487</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>44603</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44728</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 35659-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44753</v>
+        <v>44799</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45687</v>
+        <v>45344</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>0.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45597</v>
+        <v>45271</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5227,11 +5227,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>11.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7634-2022</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44607</v>
+        <v>45719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48243-2024</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45590</v>
+        <v>45339</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37421-2024</t>
+          <t>A 59516-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5430,14 +5430,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45540</v>
+        <v>45254</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5493,7 +5493,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19937-2024</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45433</v>
+        <v>45287</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.9</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5566,7 +5566,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18961-2022</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44690</v>
+        <v>44883</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5639,7 +5639,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7254-2023</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44970</v>
+        <v>45258</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6548-2022</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44601</v>
+        <v>45588</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5785,7 +5785,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 4856-2023</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44957</v>
+        <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5858,7 +5858,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 35908-2023</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45148</v>
+        <v>45394</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5931,7 +5931,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45020</v>
+        <v>44922</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 16342-2023</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45028</v>
+        <v>44972</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6077,7 +6077,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 59516-2023</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6087,14 +6087,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45254</v>
+        <v>44592</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>11.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45590</v>
+        <v>44899</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45189</v>
+        <v>44918</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 57862-2023</t>
+          <t>A 48243-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45247</v>
+        <v>45590</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46006</v>
+        <v>44616</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45344</v>
+        <v>45546</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46006</v>
+        <v>45133</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46006</v>
+        <v>45432</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46006</v>
+        <v>45009</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44749</v>
+        <v>44942</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45719</v>
+        <v>45546</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 6161-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45176</v>
+        <v>46055</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 4856-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46020</v>
+        <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46020</v>
+        <v>45195</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46019</v>
+        <v>45901</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 6160-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44949</v>
+        <v>46055</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7245,7 +7245,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 6162-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46020</v>
+        <v>46055</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 290-2026</t>
+          <t>A 59399-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7332,10 +7332,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46027</v>
+        <v>44491</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7391,7 +7391,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7405,10 +7405,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46027</v>
+        <v>45597</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7420,8 +7420,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7464,7 +7469,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 7254-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7478,10 +7483,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45336</v>
+        <v>44970</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7494,7 +7499,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7537,7 +7542,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7551,10 +7556,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46027</v>
+        <v>44970</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7567,7 +7572,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7610,7 +7615,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 6580-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7624,10 +7629,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46029</v>
+        <v>45699</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7639,13 +7644,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7688,7 +7688,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 22974-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7698,14 +7698,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45901</v>
+        <v>45790</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7761,7 +7761,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44573</v>
+        <v>44897</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7834,7 +7834,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7848,10 +7848,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46027</v>
+        <v>44777</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7907,7 +7907,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45202</v>
+        <v>45601</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7980,7 +7980,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7994,10 +7994,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44833</v>
+        <v>45926</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8053,7 +8053,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8067,10 +8067,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45204</v>
+        <v>44852</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8126,7 +8126,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24367-2025</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45797</v>
+        <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8213,10 +8213,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45183</v>
+        <v>45926</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8272,7 +8272,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8286,10 +8286,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45183</v>
+        <v>45926</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8345,7 +8345,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8359,10 +8359,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45271</v>
+        <v>45257</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8374,13 +8374,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>11.1</v>
+        <v>0.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8423,7 +8418,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8437,10 +8432,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44592</v>
+        <v>45929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8453,7 +8448,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8496,7 +8491,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2336-2024</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8510,10 +8505,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45310</v>
+        <v>45929</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8526,7 +8521,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8569,7 +8564,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 56303-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8583,10 +8578,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46055</v>
+        <v>45624</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8599,7 +8594,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8642,7 +8637,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8656,10 +8651,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46055</v>
+        <v>44952</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8672,7 +8667,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8715,7 +8710,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8729,10 +8724,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46055</v>
+        <v>44903</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8745,7 +8740,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8788,7 +8783,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 8845-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8802,10 +8797,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45926</v>
+        <v>46066</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8818,7 +8813,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8861,7 +8856,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 8818-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8875,10 +8870,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45926</v>
+        <v>46066</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8891,7 +8886,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8934,7 +8929,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 8822-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45929</v>
+        <v>46066</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8964,7 +8959,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9007,7 +9002,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 8823-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9021,10 +9016,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45093</v>
+        <v>46066</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9037,7 +9032,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9080,7 +9075,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9094,10 +9089,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45929</v>
+        <v>44953</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9110,7 +9105,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9153,7 +9148,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9167,10 +9162,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45926</v>
+        <v>44518</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9183,7 +9178,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9226,7 +9221,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9240,10 +9235,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45926</v>
+        <v>45020</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9299,7 +9294,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9313,10 +9308,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46066</v>
+        <v>45526</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9329,7 +9324,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9372,7 +9367,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9386,10 +9381,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46066</v>
+        <v>44722</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9402,7 +9397,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9445,7 +9440,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8823-2026</t>
+          <t>A 10575-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9459,10 +9454,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46066</v>
+        <v>46077</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9475,7 +9470,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9518,7 +9513,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9532,10 +9527,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46066</v>
+        <v>45685</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9591,7 +9586,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9605,10 +9600,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45158</v>
+        <v>45685</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9621,7 +9616,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9664,7 +9659,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9678,10 +9673,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44593</v>
+        <v>45758</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9694,7 +9689,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9737,7 +9732,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9751,10 +9746,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46077</v>
+        <v>45158</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9767,7 +9762,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9810,7 +9805,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9824,10 +9819,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44974</v>
+        <v>45189</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9840,7 +9835,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9883,7 +9878,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9897,10 +9892,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45036</v>
+        <v>45228</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9913,7 +9908,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9956,7 +9951,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35659-2022</t>
+          <t>A 15078-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9970,10 +9965,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44799</v>
+        <v>46105</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9986,7 +9981,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10029,7 +10024,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 15138-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10043,10 +10038,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44894</v>
+        <v>46105</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10059,7 +10054,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10102,7 +10097,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 15096-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10116,10 +10111,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44587</v>
+        <v>46105</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10132,7 +10127,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6.3</v>
+        <v>4.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10175,7 +10170,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10189,10 +10184,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44749</v>
+        <v>45687</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10205,7 +10200,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10248,7 +10243,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10262,10 +10257,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45404</v>
+        <v>45761</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10278,7 +10273,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.2</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10321,7 +10316,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 56303-2024</t>
+          <t>A 58749-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10335,10 +10330,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45624</v>
+        <v>45986</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10351,7 +10346,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10394,7 +10389,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 3267-2023</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10408,10 +10403,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44949</v>
+        <v>45063</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10424,7 +10419,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10467,7 +10462,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10481,10 +10476,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46105</v>
+        <v>45215</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10497,7 +10492,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10540,7 +10535,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10550,14 +10545,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45601</v>
+        <v>44883</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10570,7 +10565,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10613,7 +10608,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10627,10 +10622,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46105</v>
+        <v>45986</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10643,7 +10638,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10686,7 +10681,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 15096-2026</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10700,10 +10695,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46105</v>
+        <v>45204</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10716,7 +10711,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10759,7 +10754,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10773,10 +10768,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45357</v>
+        <v>45992</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10789,7 +10784,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>7.4</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10832,7 +10827,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10846,10 +10841,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45035</v>
+        <v>44910</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10861,13 +10856,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10910,7 +10900,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10924,10 +10914,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10939,8 +10929,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10983,7 +10978,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10997,10 +10992,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44937</v>
+        <v>45999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11012,8 +11007,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11056,7 +11056,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44937</v>
+        <v>44585</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11129,7 +11129,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11143,10 +11143,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45258</v>
+        <v>45999</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11158,8 +11158,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11202,7 +11207,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 58749-2025</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11216,10 +11221,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45986</v>
+        <v>45705</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11232,7 +11237,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11275,7 +11280,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11289,10 +11294,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45989</v>
+        <v>45705</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11304,13 +11309,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11367,10 +11367,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44965</v>
+        <v>46006</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11426,7 +11426,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11499,7 +11499,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44883</v>
+        <v>46006</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45999</v>
+        <v>44593</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11601,13 +11601,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11650,7 +11645,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11664,10 +11659,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45999</v>
+        <v>46006</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11679,13 +11674,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11728,7 +11718,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11742,10 +11732,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45176</v>
+        <v>45411</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11758,7 +11748,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11801,7 +11791,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 21396-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11815,10 +11805,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45205</v>
+        <v>45782</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11830,13 +11820,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11879,7 +11864,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 19925-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11893,10 +11878,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44979</v>
+        <v>45433</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11952,7 +11937,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11966,10 +11951,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45433</v>
+        <v>45218</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11981,8 +11966,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12025,7 +12015,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12039,10 +12029,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45099</v>
+        <v>45093</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12055,7 +12045,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12098,7 +12088,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 46186-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12112,10 +12102,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44942</v>
+        <v>45581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12128,7 +12118,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12171,7 +12161,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12185,10 +12175,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45354</v>
+        <v>46020</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12201,7 +12191,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12244,7 +12234,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12258,10 +12248,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45782</v>
+        <v>46019</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12274,7 +12264,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12317,7 +12307,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12327,14 +12317,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44896</v>
+        <v>46020</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12347,7 +12337,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.6</v>
+        <v>2.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12390,7 +12380,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12404,10 +12394,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45793</v>
+        <v>46020</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12420,7 +12410,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12463,7 +12453,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 7634-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12477,10 +12467,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45093</v>
+        <v>44607</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12493,7 +12483,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12536,7 +12526,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12550,10 +12540,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45093</v>
+        <v>46027</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12566,7 +12556,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12609,7 +12599,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12623,10 +12613,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44585</v>
+        <v>46027</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12639,7 +12629,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12682,7 +12672,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 290-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12696,10 +12686,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44903</v>
+        <v>46027</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12712,7 +12702,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12755,7 +12745,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12769,10 +12759,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45992</v>
+        <v>45354</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12785,7 +12775,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12828,7 +12818,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 59399-2021</t>
+          <t>A 21511-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12838,14 +12828,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44491</v>
+        <v>45782</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12858,7 +12848,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12901,7 +12891,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 560-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12915,10 +12905,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44985</v>
+        <v>46029</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12930,8 +12920,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>4.6</v>
+        <v>0.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12974,7 +12969,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12988,10 +12983,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45481</v>
+        <v>45793</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13004,7 +12999,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13047,7 +13042,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13061,10 +13056,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45581</v>
+        <v>44818</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13077,7 +13072,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13120,7 +13115,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 260-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13134,10 +13129,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45228</v>
+        <v>46027</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13150,7 +13145,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13193,7 +13188,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13207,10 +13202,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45167</v>
+        <v>45062</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13223,7 +13218,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13266,7 +13261,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13280,10 +13275,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44897</v>
+        <v>45992</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13296,7 +13291,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13339,7 +13334,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13349,14 +13344,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45170</v>
+        <v>45481</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13369,7 +13364,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13412,7 +13407,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13426,10 +13421,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45761</v>
+        <v>45099</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13442,7 +13437,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13485,7 +13480,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13499,10 +13494,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45411</v>
+        <v>44937</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13515,7 +13510,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13558,7 +13553,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13572,10 +13567,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45685</v>
+        <v>44937</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13588,7 +13583,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13631,7 +13626,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13645,10 +13640,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45685</v>
+        <v>45176</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13661,7 +13656,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13704,7 +13699,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 19937-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13718,10 +13713,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45632</v>
+        <v>45433</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13734,7 +13729,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>8.4</v>
+        <v>11.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13777,7 +13772,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13791,10 +13786,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44852</v>
+        <v>45404</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13807,7 +13802,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13850,7 +13845,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13864,10 +13859,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45215</v>
+        <v>45569</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13879,8 +13874,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13923,7 +13923,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 22974-2025</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13933,14 +13933,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45790</v>
+        <v>45569</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13952,8 +13952,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13996,7 +14001,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 6580-2025</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14010,10 +14015,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45699</v>
+        <v>46147</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14025,8 +14030,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14069,7 +14079,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14083,10 +14093,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45352</v>
+        <v>45590</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14099,7 +14109,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14142,7 +14152,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 21511-2025</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14152,14 +14162,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45782</v>
+        <v>46154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14172,7 +14182,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14215,7 +14225,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14229,10 +14239,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45258</v>
+        <v>46154</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14245,7 +14255,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14288,7 +14298,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14302,10 +14312,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44980</v>
+        <v>46155</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14317,8 +14327,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>6.4</v>
+        <v>3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14361,7 +14376,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14375,10 +14390,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46147</v>
+        <v>45629</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14390,13 +14405,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14439,7 +14449,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14453,10 +14463,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44587</v>
+        <v>45036</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14469,7 +14479,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14512,7 +14522,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14526,10 +14536,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44725</v>
+        <v>45719</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14542,7 +14552,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14585,7 +14595,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14599,10 +14609,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46154</v>
+        <v>45628</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14615,7 +14625,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14658,7 +14668,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14672,10 +14682,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46154</v>
+        <v>45597</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14687,8 +14697,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14731,7 +14746,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 35908-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14745,10 +14760,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46155</v>
+        <v>45148</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14760,13 +14775,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14809,7 +14819,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14823,10 +14833,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45565</v>
+        <v>44587</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14839,7 +14849,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14882,7 +14892,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14896,10 +14906,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45040</v>
+        <v>45173</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14909,11 +14919,6 @@
       <c r="G186" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -14960,7 +14965,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14974,10 +14979,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44728</v>
+        <v>44575</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14990,7 +14995,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15033,7 +15038,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15047,10 +15052,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45339</v>
+        <v>44587</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15063,7 +15068,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15106,7 +15111,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15120,10 +15125,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46170</v>
+        <v>45167</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15136,7 +15141,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15179,7 +15184,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15193,10 +15198,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44652</v>
+        <v>44573</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15209,7 +15214,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15252,7 +15257,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15266,10 +15271,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45036</v>
+        <v>46170</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15282,7 +15287,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.4</v>
+        <v>2.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15325,7 +15330,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 7266-2023</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15339,10 +15344,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44970</v>
+        <v>45204</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15355,7 +15360,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15398,7 +15403,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 252-2023</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15412,10 +15417,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44922</v>
+        <v>45211</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15428,7 +15433,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15471,7 +15476,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 45783-2023</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15481,14 +15486,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45195</v>
+        <v>45211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15501,7 +15506,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15544,7 +15549,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 7582-2023</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15558,10 +15563,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44972</v>
+        <v>45195</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15574,7 +15579,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.4</v>
+        <v>15.8</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15617,7 +15622,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15631,10 +15636,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46049</v>
+        <v>44728</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15647,7 +15652,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15690,7 +15695,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 54812-2022</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15700,14 +15705,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44883</v>
+        <v>44725</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15720,7 +15725,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15763,7 +15768,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15777,10 +15782,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46189</v>
+        <v>45183</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15793,7 +15798,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15836,7 +15841,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15850,10 +15855,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46195</v>
+        <v>45193</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15866,7 +15871,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15909,7 +15914,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15923,10 +15928,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46195</v>
+        <v>45183</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15939,7 +15944,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15982,7 +15987,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 43151-2023</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -15999,7 +16004,7 @@
         <v>45183</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16012,7 +16017,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16055,7 +16060,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31862-2022</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16069,10 +16074,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44777</v>
+        <v>44749</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16085,7 +16090,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.1</v>
+        <v>6.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16128,7 +16133,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 57864-2022</t>
+          <t>A 27525-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16142,10 +16147,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44899</v>
+        <v>46189</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16158,7 +16163,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16201,7 +16206,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 15779-2024</t>
+          <t>A 4965-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16215,10 +16220,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45404</v>
+        <v>46049</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16231,7 +16236,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16274,7 +16279,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 50041-2023</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16288,10 +16293,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45215</v>
+        <v>45719</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16304,7 +16309,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>10.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16347,7 +16352,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 4331-2023</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16361,10 +16366,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44953</v>
+        <v>45236</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16377,7 +16382,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16420,7 +16425,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 42401-2022</t>
+          <t>A 28093-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16434,10 +16439,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44830</v>
+        <v>46195</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16450,7 +16455,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16493,7 +16498,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 59741-2023</t>
+          <t>A 28119-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16507,10 +16512,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45257</v>
+        <v>46195</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16523,7 +16528,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16566,7 +16571,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 8685-2022</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16580,10 +16585,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44613</v>
+        <v>45215</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16596,7 +16601,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16639,7 +16644,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 43516-2024</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16653,10 +16658,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45569</v>
+        <v>44830</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16668,13 +16673,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16717,7 +16717,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 43518-2024</t>
+          <t>A 8143-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16731,10 +16731,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45569</v>
+        <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16746,13 +16746,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16795,7 +16790,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 21399-2023</t>
+          <t>A 40728-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16805,14 +16800,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45063</v>
+        <v>45170</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16825,7 +16820,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16868,7 +16863,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 14417-2024</t>
+          <t>A 30964-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16878,14 +16873,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45394</v>
+        <v>46213</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16898,7 +16893,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16941,7 +16936,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 17717-2025</t>
+          <t>A 58262-2022</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16955,10 +16950,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45758</v>
+        <v>44894</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16971,7 +16966,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17014,7 +17009,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 34357-2023</t>
+          <t>A 21399-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17028,10 +17023,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45133</v>
+        <v>45063</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17044,7 +17039,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17087,7 +17082,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 6022-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17097,14 +17092,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46213</v>
+        <v>45336</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17117,7 +17112,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17160,7 +17155,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 21483-2023</t>
+          <t>A 17585-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17174,10 +17169,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45063</v>
+        <v>45036</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17190,7 +17185,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17233,7 +17228,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38431-2024</t>
+          <t>A 8685-2022</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17247,10 +17242,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45546</v>
+        <v>44613</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17263,7 +17258,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17306,7 +17301,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 38438-2024</t>
+          <t>A 26821-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17320,10 +17315,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45546</v>
+        <v>45093</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17336,7 +17331,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17379,7 +17374,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 10135-2025</t>
+          <t>A 35740-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17393,10 +17388,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45719</v>
+        <v>46265</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17409,7 +17404,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>10.3</v>
+        <v>1.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17452,7 +17447,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 1974-2022</t>
+          <t>A 3267-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17466,10 +17461,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44575</v>
+        <v>44949</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17482,7 +17477,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17525,7 +17520,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 41314-2023</t>
+          <t>A 3276-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17539,10 +17534,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45173</v>
+        <v>44949</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17555,7 +17550,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17598,7 +17593,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 35924-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17612,10 +17607,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17628,7 +17623,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17671,7 +17666,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 23827-2022</t>
+          <t>A 29424-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17685,10 +17680,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44722</v>
+        <v>44753</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17701,7 +17696,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17744,7 +17739,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 14429-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17758,10 +17753,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46266</v>
+        <v>44652</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17817,7 +17812,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 21487-2023</t>
+          <t>A 17296-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17831,10 +17826,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45063</v>
+        <v>45035</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17846,8 +17841,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17907,7 +17907,7 @@
         <v>46269</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 7646-2025</t>
+          <t>A 21397-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45705</v>
+        <v>45063</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18036,7 +18036,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 7647-2025</t>
+          <t>A 60285-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18050,10 +18050,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45705</v>
+        <v>45258</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18109,7 +18109,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 45873-2023</t>
+          <t>A 38060-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18123,10 +18123,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45195</v>
+        <v>46280</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>15.8</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18182,7 +18182,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 57144-2024</t>
+          <t>A 10122-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18196,10 +18196,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45629</v>
+        <v>45719</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18255,7 +18255,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 3276-2023</t>
+          <t>A 9971-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18269,10 +18269,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44949</v>
+        <v>44985</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18328,7 +18328,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 50992-2023</t>
+          <t>A 17937-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18342,10 +18342,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45218</v>
+        <v>45040</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18406,7 +18406,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 38060-2026</t>
+          <t>A 15779-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18420,10 +18420,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46280</v>
+        <v>45404</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18479,7 +18479,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 62048-2022</t>
+          <t>A 9292-2023</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18493,10 +18493,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44918</v>
+        <v>44980</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18552,7 +18552,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 10120-2025</t>
+          <t>A 19747-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45719</v>
+        <v>45432</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18625,7 +18625,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 21397-2023</t>
+          <t>A 54785-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18639,10 +18639,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45063</v>
+        <v>44883</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.4</v>
+        <v>8.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18698,7 +18698,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 14082-2023</t>
+          <t>A 6522-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18712,10 +18712,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45009</v>
+        <v>45699</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18788,7 +18788,7 @@
         <v>46154</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 4047-2023</t>
+          <t>A 16342-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18858,10 +18858,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>44952</v>
+        <v>45028</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18917,7 +18917,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 33177-2026</t>
+          <t>A 29008-2022</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18931,10 +18931,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46245</v>
+        <v>44749</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19007,7 +19007,7 @@
         <v>46245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 47962-2023</t>
+          <t>A 33177-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19077,10 +19077,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45204</v>
+        <v>46245</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19136,7 +19136,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 35806-2026</t>
+          <t>A 8328-2024</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19150,10 +19150,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46265</v>
+        <v>45352</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19209,7 +19209,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 20246-2026</t>
+          <t>A 26811-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19223,10 +19223,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46139</v>
+        <v>45093</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19238,13 +19238,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I245" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19287,7 +19282,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 20773-2026</t>
+          <t>A 48158-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19301,10 +19296,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>46141</v>
+        <v>45205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19318,11 +19313,11 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I246" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19365,7 +19360,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 49345-2023</t>
+          <t>A 21487-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19379,10 +19374,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45211</v>
+        <v>45063</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19395,7 +19390,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19438,7 +19433,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 49348-2023</t>
+          <t>A 20773-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19452,10 +19447,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45211</v>
+        <v>46141</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19467,8 +19462,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I248" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19511,7 +19511,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 54849-2023</t>
+          <t>A 6548-2022</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19525,10 +19525,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45236</v>
+        <v>44601</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19584,7 +19584,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 45377-2023</t>
+          <t>A 18961-2022</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19598,10 +19598,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>45193</v>
+        <v>44690</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19657,7 +19657,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 47354-2023</t>
+          <t>A 35806-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19671,10 +19671,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>45202</v>
+        <v>46265</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19730,7 +19730,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 34572-2024</t>
+          <t>A 58247-2024</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19744,10 +19744,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45526</v>
+        <v>45632</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19803,7 +19803,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 49931-2024</t>
+          <t>A 41889-2023</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19817,10 +19817,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45597</v>
+        <v>45176</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19832,13 +19832,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I253" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19881,7 +19876,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 54785-2022</t>
+          <t>A 47205-2023</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19895,10 +19890,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>44883</v>
+        <v>45202</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19911,7 +19906,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>8.5</v>
+        <v>4.4</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19954,7 +19949,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 34488-2026</t>
+          <t>A 6357-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19968,10 +19963,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46255</v>
+        <v>44965</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19984,7 +19979,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20027,7 +20022,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 56097-2025</t>
+          <t>A 57513-2022</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20037,14 +20032,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45973</v>
+        <v>44896</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20057,7 +20052,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>1.9</v>
+        <v>5.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20100,7 +20095,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 34489-2026</t>
+          <t>A 37421-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20114,10 +20109,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46255</v>
+        <v>45540</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20130,7 +20125,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20173,7 +20168,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 6522-2025</t>
+          <t>A 3280-2023</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20187,10 +20182,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45699</v>
+        <v>44949</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20203,7 +20198,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20246,7 +20241,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 26049-2026</t>
+          <t>A 8890-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20260,10 +20255,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46177</v>
+        <v>45357</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20275,13 +20270,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>1.4</v>
+        <v>7.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20324,7 +20314,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 3276-2024</t>
+          <t>A 42623-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20338,10 +20328,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45317</v>
+        <v>45565</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20354,7 +20344,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20397,7 +20387,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 33090-2026</t>
+          <t>A 20246-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20411,10 +20401,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46245</v>
+        <v>46139</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20426,8 +20416,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I261" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20470,7 +20465,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 19747-2024</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20484,10 +20479,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45432</v>
+        <v>45202</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20500,7 +20495,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20543,7 +20538,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 60242-2022</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20557,10 +20552,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44910</v>
+        <v>45317</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20573,7 +20568,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20616,7 +20611,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 9337-2022</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20630,10 +20625,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>44616</v>
+        <v>45404</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20646,7 +20641,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20689,7 +20684,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 21233-2023</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20703,10 +20698,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>45062</v>
+        <v>44979</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20719,7 +20714,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20762,7 +20757,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 19745-2024</t>
+          <t>A 26049-2026</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20776,10 +20771,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>45432</v>
+        <v>46177</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20791,8 +20786,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I266" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20835,7 +20835,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 47679-2024</t>
+          <t>A 57862-2023</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20849,10 +20849,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45588</v>
+        <v>45247</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>5.5</v>
+        <v>1.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20908,7 +20908,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 15660-2024</t>
+          <t>A 34489-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20922,10 +20922,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>45404</v>
+        <v>46255</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20981,7 +20981,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 66424-2021</t>
+          <t>A 34488-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20995,10 +20995,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>44518</v>
+        <v>46255</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21054,7 +21054,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 39583-2022</t>
+          <t>A 24367-2025</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>44818</v>
+        <v>45797</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21127,7 +21127,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 10122-2025</t>
+          <t>A 2336-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21141,10 +21141,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45719</v>
+        <v>45310</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 65113-2023</t>
+          <t>A 56097-2025</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21214,10 +21214,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45287</v>
+        <v>45973</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 56830-2024</t>
+          <t>A 33090-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21287,10 +21287,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>45628</v>
+        <v>46245</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21363,7 +21363,7 @@
         <v>44140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>43951</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44735</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45708</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>46076</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45926</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 1075-2022</t>
+          <t>A 59356-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44571</v>
+        <v>45253</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1189,23 +1189,28 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1217,18 +1222,127 @@
         <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Bukspolsnäcka
+Aspvedgnagare
+Myskbock
+Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 59356-2023 artfynd.xlsx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 59356-2023 karta.png", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 59356-2023 georefererad karta.tif", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 59356-2023 FSC-klagomål.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 59356-2023 FSC-klagomål mail.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 59356-2023 tillsynsbegäran.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 59356-2023 tillsynsbegäran mail.docx", "A 59356-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 1075-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44571</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>17</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>17</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tallticka
@@ -1237,153 +1351,39 @@
 Rostfläck</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1075-2022 artfynd.xlsx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1075-2022 karta.png", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1075-2022 georefererad karta.tif", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 1075-2022 karta knärot.png", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1075-2022 FSC-klagomål.docx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1075-2022 FSC-klagomål mail.docx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1075-2022 tillsynsbegäran.docx", "A 1075-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1075-2022 tillsynsbegäran mail.docx", "A 1075-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 59356-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45253</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Bukspolsnäcka
-Aspvedgnagare
-Myskbock
-Noshornsoxe</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 59356-2023 artfynd.xlsx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 59356-2023 karta.png", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 59356-2023 georefererad karta.tif", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 59356-2023 FSC-klagomål.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 59356-2023 FSC-klagomål mail.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 59356-2023 tillsynsbegäran.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 59356-2023 tillsynsbegäran mail.docx", "A 59356-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44770</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 4051-2023</t>
+          <t>A 1543-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44952</v>
+        <v>44573</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,19 +2074,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2110,39 +2110,39 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
         <v>45323</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11749-2023</t>
+          <t>A 5414-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44994</v>
+        <v>45331</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2324,466 +2324,470 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 11749-2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44994</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>Adam och eva</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 18758-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="Z19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 40874-2023</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
         <v>45173</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>1.5</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>1</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U20" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 5414-2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 27253-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
+      <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 27253-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="Z20">
+      <c r="Z21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 1543-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44573</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Hasselsnok</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 18758-2023</t>
+          <t>A 4051-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2797,10 +2801,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45043</v>
+        <v>44952</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2813,19 +2817,19 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2840,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2849,43 +2853,39 @@
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
         <v/>
       </c>
-      <c r="Z22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
-        <v/>
-      </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
         <v>45790</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>44613</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>44869</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>44687</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>44852</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44536</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44603</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44881</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44613</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 118-2022</t>
+          <t>A 8688-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44564</v>
+        <v>44613</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3950,7 +3950,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8688-2022</t>
+          <t>A 118-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3964,10 +3964,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44613</v>
+        <v>44564</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4040,7 +4040,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44658</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44573</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44656</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>44573</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44593</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44881</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44603</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 58100-2021</t>
+          <t>A 7125-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44487</v>
+        <v>44603</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 7125-2022</t>
+          <t>A 58100-2021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44603</v>
+        <v>44487</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4921,7 +4921,7 @@
         <v>44603</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>44728</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35659-2022</t>
+          <t>A 29424-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44799</v>
+        <v>44753</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45344</v>
+        <v>45687</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45271</v>
+        <v>45597</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5227,11 +5227,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>11.1</v>
+        <v>1.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10120-2025</t>
+          <t>A 7634-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5288,10 +5288,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45719</v>
+        <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 48243-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45339</v>
+        <v>45590</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5420,7 +5420,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59516-2023</t>
+          <t>A 37421-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5430,14 +5430,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45254</v>
+        <v>45540</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5493,7 +5493,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 65113-2023</t>
+          <t>A 19937-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45287</v>
+        <v>45433</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>11.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5566,7 +5566,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 18961-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44883</v>
+        <v>44690</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5639,7 +5639,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 35908-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5653,10 +5653,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45258</v>
+        <v>45148</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 47679-2024</t>
+          <t>A 7254-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45588</v>
+        <v>44970</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.5</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5785,7 +5785,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 6548-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44833</v>
+        <v>44601</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5858,7 +5858,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 14417-2024</t>
+          <t>A 4856-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45394</v>
+        <v>44957</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5931,7 +5931,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 252-2023</t>
+          <t>A 59516-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5941,14 +5941,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44922</v>
+        <v>45254</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7582-2023</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44972</v>
+        <v>45020</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.4</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6077,7 +6077,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44592</v>
+        <v>45590</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.6</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57864-2022</t>
+          <t>A 16342-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44899</v>
+        <v>45028</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62048-2022</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44918</v>
+        <v>45189</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48243-2024</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45590</v>
+        <v>45344</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9337-2022</t>
+          <t>A 29008-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44616</v>
+        <v>44749</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 38438-2024</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45546</v>
+        <v>45719</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 34357-2023</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45133</v>
+        <v>45176</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 19745-2024</t>
+          <t>A 3280-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45432</v>
+        <v>44949</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 14082-2023</t>
+          <t>A 6022-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6675,10 +6675,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45009</v>
+        <v>45336</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44942</v>
+        <v>44573</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38431-2024</t>
+          <t>A 47205-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45546</v>
+        <v>45202</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46055</v>
+        <v>44833</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 4856-2023</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6967,10 +6967,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44957</v>
+        <v>45204</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7026,7 +7026,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 45783-2023</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7036,14 +7036,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45195</v>
+        <v>45183</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7099,7 +7099,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7113,10 +7113,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45901</v>
+        <v>45183</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7172,7 +7172,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46055</v>
+        <v>45271</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7201,8 +7201,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.2</v>
+        <v>11.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7245,7 +7250,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7259,10 +7264,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46055</v>
+        <v>46027</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7275,7 +7280,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7318,7 +7323,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 59399-2021</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7332,10 +7337,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44491</v>
+        <v>44592</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7348,7 +7353,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7391,7 +7396,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49931-2024</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7405,10 +7410,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45597</v>
+        <v>46027</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7420,13 +7425,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7254-2023</t>
+          <t>A 560-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44970</v>
+        <v>46029</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7498,8 +7498,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7542,7 +7547,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 7266-2023</t>
+          <t>A 2336-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7556,10 +7561,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44970</v>
+        <v>45310</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7572,7 +7577,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7615,7 +7620,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6580-2025</t>
+          <t>A 260-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7629,10 +7634,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45699</v>
+        <v>46027</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7645,7 +7650,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7688,7 +7693,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22974-2025</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7698,14 +7703,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45790</v>
+        <v>45093</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7718,7 +7723,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.6</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7761,7 +7766,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7775,10 +7780,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44897</v>
+        <v>45158</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7791,7 +7796,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7834,7 +7839,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 31862-2022</t>
+          <t>A 6160-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7848,10 +7853,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44777</v>
+        <v>46055</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7864,7 +7869,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7907,7 +7912,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 6162-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7921,10 +7926,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45601</v>
+        <v>46055</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7937,7 +7942,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7980,7 +7985,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7994,10 +7999,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45926</v>
+        <v>44593</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8010,7 +8015,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8053,7 +8058,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 6161-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8067,10 +8072,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44852</v>
+        <v>46055</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8083,7 +8088,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8126,7 +8131,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8140,10 +8145,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45926</v>
+        <v>45901</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8156,7 +8161,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8199,7 +8204,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 8143-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8213,10 +8218,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45926</v>
+        <v>44974</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8229,7 +8234,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8272,7 +8277,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8286,10 +8291,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45926</v>
+        <v>45036</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8302,7 +8307,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8345,7 +8350,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59741-2023</t>
+          <t>A 8845-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8359,10 +8364,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45257</v>
+        <v>46066</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8375,7 +8380,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8418,7 +8423,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 8818-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8432,10 +8437,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45929</v>
+        <v>46066</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8448,7 +8453,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8491,7 +8496,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 8823-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8505,10 +8510,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45929</v>
+        <v>46066</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8521,7 +8526,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8564,7 +8569,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 56303-2024</t>
+          <t>A 8822-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8578,10 +8583,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45624</v>
+        <v>46066</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8594,7 +8599,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8637,7 +8642,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4047-2023</t>
+          <t>A 35659-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8651,10 +8656,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44952</v>
+        <v>44799</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8667,7 +8672,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6.5</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8710,7 +8715,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 10575-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8724,10 +8729,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44903</v>
+        <v>46077</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8740,7 +8745,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8783,7 +8788,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 58262-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8797,10 +8802,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46066</v>
+        <v>44894</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8813,7 +8818,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8856,7 +8861,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8870,10 +8875,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46066</v>
+        <v>44587</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8886,7 +8891,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8929,7 +8934,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46066</v>
+        <v>45926</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8959,7 +8964,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9002,7 +9007,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8823-2026</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9016,10 +9021,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46066</v>
+        <v>45926</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9032,7 +9037,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9075,7 +9080,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 4331-2023</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9089,10 +9094,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44953</v>
+        <v>45929</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9105,7 +9110,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9148,7 +9153,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 66424-2021</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9162,10 +9167,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44518</v>
+        <v>44749</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9178,7 +9183,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9221,7 +9226,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9235,10 +9240,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45020</v>
+        <v>45929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9251,7 +9256,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9294,7 +9299,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 34572-2024</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9308,10 +9313,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45526</v>
+        <v>45926</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9324,7 +9329,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9367,7 +9372,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23827-2022</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9381,10 +9386,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44722</v>
+        <v>45926</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9397,7 +9402,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9440,7 +9445,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9454,10 +9459,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46077</v>
+        <v>45404</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9470,7 +9475,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>6.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9513,7 +9518,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 56303-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9527,10 +9532,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45685</v>
+        <v>45624</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9543,7 +9548,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9586,7 +9591,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 3267-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9600,10 +9605,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45685</v>
+        <v>44949</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9616,7 +9621,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9659,7 +9664,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 17717-2025</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9673,10 +9678,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45758</v>
+        <v>45601</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9689,7 +9694,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9732,7 +9737,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 8890-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9746,10 +9751,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45158</v>
+        <v>45357</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9762,7 +9767,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>7.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9805,7 +9810,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 15078-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9819,10 +9824,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45189</v>
+        <v>46105</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9835,7 +9840,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9878,7 +9883,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 17296-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9892,10 +9897,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45228</v>
+        <v>45035</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9907,8 +9912,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9951,7 +9961,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 15138-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9968,7 +9978,7 @@
         <v>46105</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9981,7 +9991,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10024,7 +10034,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 15096-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10041,7 +10051,7 @@
         <v>46105</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10054,7 +10064,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10097,7 +10107,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 15096-2026</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10111,10 +10121,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46105</v>
+        <v>44937</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10127,7 +10137,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10170,7 +10180,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10184,10 +10194,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45687</v>
+        <v>44937</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10200,7 +10210,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10243,7 +10253,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 60285-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10257,10 +10267,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45761</v>
+        <v>45258</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10273,7 +10283,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10316,7 +10326,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 58749-2025</t>
+          <t>A 59399-2021</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10330,10 +10340,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45986</v>
+        <v>44491</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10346,7 +10356,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10389,7 +10399,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21483-2023</t>
+          <t>A 6357-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10403,10 +10413,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45063</v>
+        <v>44965</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10419,7 +10429,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10462,7 +10472,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 22974-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10472,14 +10482,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45215</v>
+        <v>45790</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10492,7 +10502,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10535,7 +10545,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 54812-2022</t>
+          <t>A 6580-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10545,14 +10555,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44883</v>
+        <v>45699</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10565,7 +10575,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10608,7 +10618,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10622,10 +10632,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45986</v>
+        <v>44883</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10638,7 +10648,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10681,7 +10691,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 47962-2023</t>
+          <t>A 19925-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10695,10 +10705,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45204</v>
+        <v>45433</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10711,7 +10721,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10754,7 +10764,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 41889-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10768,10 +10778,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45992</v>
+        <v>45176</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10784,7 +10794,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10827,7 +10837,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60242-2022</t>
+          <t>A 48158-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10841,10 +10851,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44910</v>
+        <v>45205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10856,8 +10866,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10900,7 +10915,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10914,10 +10929,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45989</v>
+        <v>44979</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10929,13 +10944,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10978,7 +10988,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 21396-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10992,10 +11002,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45999</v>
+        <v>45782</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11007,13 +11017,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11056,7 +11061,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11070,10 +11075,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44585</v>
+        <v>45099</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11086,7 +11091,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11129,7 +11134,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11143,10 +11148,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45999</v>
+        <v>44942</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11158,13 +11163,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11207,7 +11207,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7646-2025</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45705</v>
+        <v>45793</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 7647-2025</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11294,10 +11294,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45705</v>
+        <v>45354</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 57513-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11363,14 +11363,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46006</v>
+        <v>44896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11426,7 +11426,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11440,10 +11440,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46006</v>
+        <v>45992</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11499,7 +11499,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11513,10 +11513,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46006</v>
+        <v>45986</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11572,7 +11572,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 58749-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11586,10 +11586,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44593</v>
+        <v>45986</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11645,7 +11645,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46006</v>
+        <v>45989</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11674,8 +11674,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11718,7 +11723,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11732,10 +11737,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45411</v>
+        <v>45992</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11748,7 +11753,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11791,7 +11796,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 46186-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11805,10 +11810,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45782</v>
+        <v>45581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11821,7 +11826,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11864,7 +11869,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11878,10 +11883,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45433</v>
+        <v>45999</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11893,8 +11898,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11937,7 +11947,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 50992-2023</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11951,10 +11961,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45218</v>
+        <v>45999</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11972,7 +11982,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12015,7 +12025,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 26811-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12032,7 +12042,7 @@
         <v>45093</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12045,7 +12055,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12088,7 +12098,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12102,10 +12112,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45581</v>
+        <v>46006</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12118,7 +12128,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12161,7 +12171,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12175,10 +12185,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46020</v>
+        <v>46006</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12191,7 +12201,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12234,7 +12244,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12248,10 +12258,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46019</v>
+        <v>46006</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12264,7 +12274,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12307,7 +12317,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12321,10 +12331,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46020</v>
+        <v>46006</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12337,7 +12347,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12380,7 +12390,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12397,7 +12407,7 @@
         <v>46020</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12410,7 +12420,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12453,7 +12463,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7634-2022</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12467,10 +12477,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44607</v>
+        <v>46020</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12483,7 +12493,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12526,7 +12536,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12540,10 +12550,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46027</v>
+        <v>46019</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12556,7 +12566,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12599,7 +12609,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12613,10 +12623,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46027</v>
+        <v>46020</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12629,7 +12639,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12689,7 +12699,7 @@
         <v>46027</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12745,7 +12755,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 21511-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12755,14 +12765,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45354</v>
+        <v>45782</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12775,7 +12785,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12818,7 +12828,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 21511-2025</t>
+          <t>A 26821-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12828,14 +12838,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45782</v>
+        <v>45093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12848,7 +12858,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12891,7 +12901,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12905,10 +12915,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46029</v>
+        <v>46147</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12926,7 +12936,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12969,7 +12979,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12983,10 +12993,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45793</v>
+        <v>46154</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12999,7 +13009,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13042,7 +13052,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 39583-2022</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13056,10 +13066,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44818</v>
+        <v>46154</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13072,7 +13082,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13115,7 +13125,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13129,10 +13139,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46027</v>
+        <v>46155</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13144,8 +13154,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13188,7 +13203,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 21233-2023</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13202,10 +13217,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45062</v>
+        <v>44585</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13218,7 +13233,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13261,7 +13276,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13275,10 +13290,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45992</v>
+        <v>46170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13291,7 +13306,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13334,7 +13349,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13348,10 +13363,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45481</v>
+        <v>44903</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13364,7 +13379,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13407,7 +13422,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 9971-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13421,10 +13436,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45099</v>
+        <v>44985</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13437,7 +13452,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13480,7 +13495,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 4965-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13494,10 +13509,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44937</v>
+        <v>46049</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13510,7 +13525,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13553,7 +13568,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13567,10 +13582,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44937</v>
+        <v>45481</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13583,7 +13598,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13626,7 +13641,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13640,10 +13655,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45176</v>
+        <v>45228</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13656,7 +13671,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13699,7 +13714,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 19937-2024</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13713,10 +13728,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45433</v>
+        <v>45167</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13729,7 +13744,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>11.9</v>
+        <v>2.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13772,7 +13787,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 15660-2024</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13786,10 +13801,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45404</v>
+        <v>44897</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13802,7 +13817,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13845,7 +13860,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 43516-2024</t>
+          <t>A 40728-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13855,14 +13870,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45569</v>
+        <v>45170</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13874,13 +13889,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13923,7 +13933,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 43518-2024</t>
+          <t>A 27525-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13937,10 +13947,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45569</v>
+        <v>46189</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13952,13 +13962,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14001,7 +14006,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14015,10 +14020,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46147</v>
+        <v>45761</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14030,13 +14035,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14079,7 +14079,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14093,10 +14093,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45590</v>
+        <v>45411</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14152,7 +14152,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14166,10 +14166,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46154</v>
+        <v>45685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14225,7 +14225,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14239,10 +14239,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46154</v>
+        <v>45685</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14298,7 +14298,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 58247-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14312,10 +14312,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46155</v>
+        <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14327,13 +14327,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14376,7 +14371,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 57144-2024</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14390,10 +14385,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45629</v>
+        <v>44852</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14406,7 +14401,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14449,7 +14444,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14463,10 +14458,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45036</v>
+        <v>45215</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14479,7 +14474,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14522,7 +14517,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 28119-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14536,10 +14531,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45719</v>
+        <v>46195</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14552,7 +14547,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14595,7 +14590,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 56830-2024</t>
+          <t>A 28093-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14609,10 +14604,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45628</v>
+        <v>46195</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14625,7 +14620,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14668,7 +14663,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 8328-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14682,10 +14677,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45597</v>
+        <v>45352</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14697,13 +14692,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14746,7 +14736,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 35908-2023</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14760,10 +14750,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45148</v>
+        <v>45258</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14776,7 +14766,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14819,7 +14809,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 9292-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14833,10 +14823,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44587</v>
+        <v>44980</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14849,7 +14839,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14892,7 +14882,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 41314-2023</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14906,10 +14896,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45173</v>
+        <v>44587</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14922,7 +14912,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14965,7 +14955,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 1974-2022</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14979,10 +14969,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44575</v>
+        <v>44725</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14995,7 +14985,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15038,7 +15028,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 42623-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15052,10 +15042,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44587</v>
+        <v>45565</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15068,7 +15058,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15111,7 +15101,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 17937-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15125,10 +15115,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45167</v>
+        <v>45040</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15140,8 +15130,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15184,7 +15179,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 30964-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15194,14 +15189,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44573</v>
+        <v>46213</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15214,7 +15209,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15257,7 +15252,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15271,10 +15266,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46170</v>
+        <v>44728</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15287,7 +15282,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15330,7 +15325,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15344,10 +15339,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45204</v>
+        <v>45339</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15360,7 +15355,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15403,7 +15398,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 49345-2023</t>
+          <t>A 14429-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15417,10 +15412,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45211</v>
+        <v>44652</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15433,7 +15428,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15476,7 +15471,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 49348-2023</t>
+          <t>A 17585-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15490,10 +15485,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45211</v>
+        <v>45036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15506,7 +15501,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15549,7 +15544,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 45873-2023</t>
+          <t>A 35740-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15563,10 +15558,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45195</v>
+        <v>46265</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15579,7 +15574,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>15.8</v>
+        <v>1.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15622,7 +15617,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 35924-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15636,10 +15631,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44728</v>
+        <v>46266</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15652,7 +15647,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -15695,7 +15690,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -15709,10 +15704,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44725</v>
+        <v>44970</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -15725,7 +15720,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -15768,7 +15763,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 43151-2023</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -15782,10 +15777,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45183</v>
+        <v>44922</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -15798,7 +15793,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -15841,7 +15836,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 45377-2023</t>
+          <t>A 36555-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -15855,10 +15850,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45193</v>
+        <v>46269</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -15871,7 +15866,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -15914,7 +15909,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -15924,14 +15919,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45183</v>
+        <v>45195</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -15944,7 +15939,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15987,7 +15982,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16001,10 +15996,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45183</v>
+        <v>44972</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16017,7 +16012,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16060,7 +16055,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16070,14 +16065,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44749</v>
+        <v>44883</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16090,7 +16085,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16133,7 +16128,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16147,10 +16142,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46189</v>
+        <v>45183</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16163,7 +16158,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16206,7 +16201,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16220,10 +16215,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46049</v>
+        <v>44777</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16236,7 +16231,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16279,7 +16274,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 10135-2025</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16293,10 +16288,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45719</v>
+        <v>44899</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16309,7 +16304,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>10.3</v>
+        <v>0.7</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16352,7 +16347,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 54849-2023</t>
+          <t>A 15779-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16366,10 +16361,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45236</v>
+        <v>45404</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16382,7 +16377,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16425,7 +16420,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16439,10 +16434,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46195</v>
+        <v>45215</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16455,7 +16450,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16498,7 +16493,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16512,10 +16507,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46195</v>
+        <v>44953</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16528,7 +16523,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -16571,7 +16566,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 50041-2023</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -16585,10 +16580,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45215</v>
+        <v>44830</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -16601,7 +16596,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -16644,7 +16639,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 42401-2022</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -16658,10 +16653,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44830</v>
+        <v>45257</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -16674,7 +16669,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -16717,7 +16712,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 8685-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -16731,10 +16726,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44974</v>
+        <v>44613</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -16747,7 +16742,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -16790,7 +16785,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -16800,14 +16795,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45170</v>
+        <v>45569</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -16819,8 +16814,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -16863,7 +16863,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -16873,14 +16873,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46213</v>
+        <v>45569</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -16892,8 +16892,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -16936,7 +16941,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 21399-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -16950,10 +16955,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44894</v>
+        <v>45063</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -16966,7 +16971,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17009,7 +17014,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 21399-2023</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17023,10 +17028,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45063</v>
+        <v>45394</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17039,7 +17044,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17082,7 +17087,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17096,10 +17101,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45336</v>
+        <v>45758</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17112,7 +17117,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17155,7 +17160,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17169,10 +17174,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45036</v>
+        <v>45133</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17185,7 +17190,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17228,7 +17233,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 8685-2022</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17242,10 +17247,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44613</v>
+        <v>45063</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17258,7 +17263,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17301,7 +17306,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17315,10 +17320,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45093</v>
+        <v>45546</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17331,7 +17336,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17374,7 +17379,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17388,10 +17393,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46265</v>
+        <v>45546</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17404,7 +17409,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17447,7 +17452,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 3267-2023</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17461,10 +17466,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44949</v>
+        <v>45719</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17477,7 +17482,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>10.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17520,7 +17525,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 3276-2023</t>
+          <t>A 22297-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -17534,10 +17539,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44949</v>
+        <v>46154</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17550,7 +17555,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -17593,7 +17598,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -17607,10 +17612,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46266</v>
+        <v>44575</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -17623,7 +17628,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -17666,7 +17671,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -17680,10 +17685,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44753</v>
+        <v>45173</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -17696,7 +17701,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -17739,7 +17744,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -17753,10 +17758,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44652</v>
+        <v>44722</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -17812,7 +17817,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 21487-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -17826,10 +17831,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45035</v>
+        <v>45063</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -17841,13 +17846,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -17890,7 +17890,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 36555-2026</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -17904,10 +17904,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46269</v>
+        <v>45705</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21397-2023</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -17977,10 +17977,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45063</v>
+        <v>45705</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18036,7 +18036,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18050,10 +18050,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45258</v>
+        <v>45195</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.5</v>
+        <v>15.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18109,7 +18109,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 38060-2026</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18123,10 +18123,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46280</v>
+        <v>45629</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18182,7 +18182,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 10122-2025</t>
+          <t>A 33177-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18196,10 +18196,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45719</v>
+        <v>46245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18255,7 +18255,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 33076-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18269,10 +18269,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44985</v>
+        <v>46245</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18328,7 +18328,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 3276-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18342,10 +18342,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45040</v>
+        <v>44949</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18357,13 +18357,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18406,7 +18401,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 15779-2024</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18420,10 +18415,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45404</v>
+        <v>45218</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18435,8 +18430,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18479,7 +18479,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 20246-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18493,10 +18493,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44980</v>
+        <v>46139</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18508,8 +18508,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -18552,7 +18557,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 19747-2024</t>
+          <t>A 20773-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -18566,10 +18571,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45432</v>
+        <v>46141</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18581,8 +18586,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -18625,7 +18635,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 54785-2022</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -18639,10 +18649,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>44883</v>
+        <v>44918</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -18655,7 +18665,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -18698,7 +18708,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 6522-2025</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -18712,10 +18722,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45699</v>
+        <v>45719</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -18728,7 +18738,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -18771,7 +18781,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 22297-2026</t>
+          <t>A 21397-2023</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -18785,10 +18795,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46154</v>
+        <v>45063</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -18801,7 +18811,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -18844,7 +18854,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 16342-2023</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -18858,10 +18868,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45028</v>
+        <v>45009</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -18874,7 +18884,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -18917,7 +18927,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -18931,10 +18941,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>44749</v>
+        <v>44952</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -18947,7 +18957,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>1.7</v>
+        <v>6.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -18990,7 +19000,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 33076-2026</t>
+          <t>A 56097-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19004,10 +19014,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>46245</v>
+        <v>45973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19020,7 +19030,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19063,7 +19073,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 33177-2026</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19077,10 +19087,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>46245</v>
+        <v>45204</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19093,7 +19103,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19136,7 +19146,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 26049-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19150,10 +19160,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45352</v>
+        <v>46177</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19165,8 +19175,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19209,7 +19224,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19223,10 +19238,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45093</v>
+        <v>45211</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19239,7 +19254,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19282,7 +19297,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19296,10 +19311,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45205</v>
+        <v>45211</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19311,13 +19326,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19360,7 +19370,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 21487-2023</t>
+          <t>A 33090-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19374,10 +19384,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45063</v>
+        <v>46245</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19390,7 +19400,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19433,7 +19443,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 20773-2026</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19447,10 +19457,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46141</v>
+        <v>45236</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19462,13 +19472,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I248" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19511,7 +19516,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 6548-2022</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -19525,10 +19530,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>44601</v>
+        <v>45193</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19541,7 +19546,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -19584,7 +19589,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 18961-2022</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -19598,10 +19603,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44690</v>
+        <v>45202</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -19614,7 +19619,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -19657,7 +19662,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 35806-2026</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -19671,10 +19676,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46265</v>
+        <v>45526</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -19687,7 +19692,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -19730,7 +19735,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 34488-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -19744,10 +19749,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>45632</v>
+        <v>46255</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -19760,7 +19765,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -19803,7 +19808,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 35806-2026</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -19817,10 +19822,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45176</v>
+        <v>46265</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -19833,7 +19838,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -19876,7 +19881,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -19890,10 +19895,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45202</v>
+        <v>45597</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -19905,8 +19910,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -19949,7 +19959,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 54785-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -19963,10 +19973,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>44965</v>
+        <v>44883</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -19979,7 +19989,7 @@
         </is>
       </c>
       <c r="I255" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20022,7 +20032,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 38060-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20032,14 +20042,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44896</v>
+        <v>46280</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20052,7 +20062,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>5.6</v>
+        <v>1.5</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20095,7 +20105,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 37421-2024</t>
+          <t>A 34489-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20109,10 +20119,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>45540</v>
+        <v>46255</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20125,7 +20135,7 @@
         </is>
       </c>
       <c r="I257" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20168,7 +20178,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 6522-2025</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20182,10 +20192,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>44949</v>
+        <v>45699</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20198,7 +20208,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20241,7 +20251,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20255,10 +20265,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>45357</v>
+        <v>45317</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20271,7 +20281,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20314,7 +20324,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 19747-2024</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20328,10 +20338,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45565</v>
+        <v>45432</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20344,7 +20354,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20387,7 +20397,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 20246-2026</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20401,10 +20411,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>46139</v>
+        <v>44910</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20416,13 +20426,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I261" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20465,7 +20470,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 47354-2023</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20479,10 +20484,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>45202</v>
+        <v>44616</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20495,7 +20500,7 @@
         </is>
       </c>
       <c r="I262" t="n">
-        <v>7</v>
+        <v>0.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -20538,7 +20543,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 3276-2024</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -20552,10 +20557,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45317</v>
+        <v>45062</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -20568,7 +20573,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -20611,7 +20616,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -20625,10 +20630,10 @@
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45404</v>
+        <v>45432</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -20641,7 +20646,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>6.2</v>
+        <v>1.6</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -20684,7 +20689,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -20698,10 +20703,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44979</v>
+        <v>45588</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -20714,7 +20719,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -20757,7 +20762,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 26049-2026</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -20771,10 +20776,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>46177</v>
+        <v>45404</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -20786,13 +20791,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I266" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -20835,7 +20835,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 57862-2023</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -20849,10 +20849,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>45247</v>
+        <v>44518</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -20908,7 +20908,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 34489-2026</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -20922,10 +20922,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>46255</v>
+        <v>44818</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -20981,7 +20981,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 34488-2026</t>
+          <t>A 10122-2025</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -20995,10 +20995,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46255</v>
+        <v>45719</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21011,7 +21011,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21054,7 +21054,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 24367-2025</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21068,10 +21068,10 @@
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>45797</v>
+        <v>45287</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="I270" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21127,7 +21127,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 2336-2024</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21141,10 +21141,10 @@
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45310</v>
+        <v>45628</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21200,7 +21200,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 56097-2025</t>
+          <t>A 57862-2023</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21214,10 +21214,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45973</v>
+        <v>45247</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         </is>
       </c>
       <c r="I272" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 33090-2026</t>
+          <t>A 24367-2025</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21287,10 +21287,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>46245</v>
+        <v>45797</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21363,7 +21363,7 @@
         <v>44140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>43951</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44735</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45300</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45708</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>46076</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>

--- a/Översikt VALDEMARSVIK.xlsx
+++ b/Översikt VALDEMARSVIK.xlsx
@@ -601,7 +601,7 @@
         <v>45569</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         <v>45569</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>45961</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>44573</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>45926</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>45253</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>44571</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46202</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44712</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>44916</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>46255</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>44712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>44770</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1543-2022</t>
+          <t>A 23067-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44573</v>
+        <v>45790</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2098,10 +2098,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2114,890 +2114,890 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 23067-2025 artfynd.xlsx", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 23067-2025 karta.png", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 23067-2025 georefererad karta.tif", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 23067-2025 FSC-klagomål.docx", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 23067-2025 FSC-klagomål mail.docx", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 23067-2025 tillsynsbegäran.docx", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 23067-2025 tillsynsbegäran mail.docx", "A 23067-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 23067-2025 prioriterade fågelarter.docx", "A 23067-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 4051-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44952</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 4148-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 5414-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45331</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 11749-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44994</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Adam och eva</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 27253-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="Z20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 1543-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44573</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
           <t>Hasselsnok</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 1543-2022 artfynd.xlsx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 1543-2022 karta.png", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 1543-2022 georefererad karta.tif", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 1543-2022 FSC-klagomål.docx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 1543-2022 FSC-klagomål mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 1543-2022 tillsynsbegäran.docx", "A 1543-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 1543-2022 tillsynsbegäran mail.docx", "A 1543-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 4148-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J16" t="n">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 18758-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45043</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="n">
+      <c r="R22" t="n">
         <v>1</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Gullviva</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4148-2024 artfynd.xlsx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4148-2024 karta.png", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4148-2024 georefererad karta.tif", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4148-2024 FSC-klagomål.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4148-2024 FSC-klagomål mail.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4148-2024 tillsynsbegäran.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4148-2024 tillsynsbegäran mail.docx", "A 4148-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 5414-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45331</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="U22" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 5414-2024 artfynd.xlsx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 5414-2024 karta.png", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 5414-2024 georefererad karta.tif", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 5414-2024 FSC-klagomål.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 5414-2024 FSC-klagomål mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 5414-2024 tillsynsbegäran.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 5414-2024 tillsynsbegäran mail.docx", "A 5414-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 11749-2023</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>44994</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Adam och eva</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 11749-2023 artfynd.xlsx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 11749-2023 karta.png", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 11749-2023 georefererad karta.tif", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 11749-2023 FSC-klagomål.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 11749-2023 FSC-klagomål mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 11749-2023 tillsynsbegäran.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 11749-2023 tillsynsbegäran mail.docx", "A 11749-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 18758-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45043</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Knärot</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 18758-2023 artfynd.xlsx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 18758-2023 karta.png", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 18758-2023 georefererad karta.tif", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="Z19">
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 18758-2023 karta knärot.png", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 18758-2023 FSC-klagomål.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 18758-2023 FSC-klagomål mail.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 18758-2023 tillsynsbegäran.docx", "A 18758-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 18758-2023 tillsynsbegäran mail.docx", "A 18758-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 40874-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45173</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ÖSTERGÖTLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>1.5</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>1</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U23" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 40874-2023 artfynd.xlsx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 40874-2023 karta.png", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 40874-2023 georefererad karta.tif", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 40874-2023 FSC-klagomål.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 40874-2023 FSC-klagomål mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 40874-2023 tillsynsbegäran.docx", "A 40874-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 40874-2023 tillsynsbegäran mail.docx", "A 40874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 27253-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>46188</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 27253-2026 artfynd.xlsx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 27253-2026 karta.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 27253-2026 georefererad karta.tif", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="Z21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/knärot/A 27253-2026 karta knärot.png", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 27253-2026 FSC-klagomål.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 27253-2026 FSC-klagomål mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 27253-2026 tillsynsbegäran.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 27253-2026 tillsynsbegäran mail.docx", "A 27253-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 4051-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44952</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 4051-2023 artfynd.xlsx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 4051-2023 karta.png", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 4051-2023 georefererad karta.tif", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 4051-2023 FSC-klagomål.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 4051-2023 FSC-klagomål mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 4051-2023 tillsynsbegäran.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 4051-2023 tillsynsbegäran mail.docx", "A 4051-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 23067-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45790</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>ÖSTERGÖTLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/artfynd/A 23067-2025 artfynd.xlsx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor/A 23067-2025 karta.png", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/kartor_geotiff/A 23067-2025 georefererad karta.tif", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomål/A 23067-2025 FSC-klagomål.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/klagomålsmail/A 23067-2025 FSC-klagomål mail.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsyn/A 23067-2025 tillsynsbegäran.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/tillsynsmail/A 23067-2025 tillsynsbegäran mail.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0563/fåglar/A 23067-2025 prioriterade fågelarter.docx", "A 23067-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>44613</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44749</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 51436-2022</t>
+          <t>A 18684-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44869</v>
+        <v>44687</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 18684-2022</t>
+          <t>A 47632-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44687</v>
+        <v>44852</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3293,7 +3293,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 47632-2022</t>
+          <t>A 51436-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44852</v>
+        <v>44869</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>44536</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>44613</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>44531</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>44603</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         <v>44531</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         <v>44881</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44613</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>44613</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44564</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>44658</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>44573</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44656</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44629</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 1424-2022</t>
+          <t>A 24971-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4402,10 +4402,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44573</v>
+        <v>44728</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4461,7 +4461,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 4927-2022</t>
+          <t>A 6996-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44593</v>
+        <v>44603</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4490,8 +4490,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4534,7 +4539,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 54230-2022</t>
+          <t>A 1424-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4548,10 +4553,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44881</v>
+        <v>44573</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4564,7 +4569,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4607,7 +4612,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6996-2022</t>
+          <t>A 53111-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4621,10 +4626,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44603</v>
+        <v>45228</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4636,13 +4641,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7125-2022</t>
+          <t>A 35659-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44603</v>
+        <v>44799</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4831,7 +4831,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 58100-2021</t>
+          <t>A 7237-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44487</v>
+        <v>45344</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4904,7 +4904,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 7138-2022</t>
+          <t>A 58100-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44603</v>
+        <v>44487</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4977,7 +4977,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 24971-2022</t>
+          <t>A 4927-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4991,10 +4991,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44728</v>
+        <v>44593</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 29424-2022</t>
+          <t>A 4627-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44753</v>
+        <v>45687</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5123,7 +5123,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 4627-2025</t>
+          <t>A 7125-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45687</v>
+        <v>44603</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5196,7 +5196,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 49934-2024</t>
+          <t>A 7138-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5210,10 +5210,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45597</v>
+        <v>44603</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5223,11 +5223,6 @@
       <c r="G54" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -5274,7 +5269,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 7634-2022</t>
+          <t>A 62914-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5288,10 +5283,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44607</v>
+        <v>45271</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5303,8 +5298,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>11.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5347,7 +5347,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 48243-2024</t>
+          <t>A 18200-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45590</v>
+        <v>45761</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 37421-2024</t>
+          <t>A 21483-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5434,10 +5434,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45540</v>
+        <v>45063</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5493,7 +5493,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 19937-2024</t>
+          <t>A 54230-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45433</v>
+        <v>44881</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>11.9</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5566,7 +5566,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18961-2022</t>
+          <t>A 50148-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5580,10 +5580,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44690</v>
+        <v>45215</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5639,7 +5639,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35908-2023</t>
+          <t>A 54812-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5649,14 +5649,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45148</v>
+        <v>44883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 7254-2023</t>
+          <t>A 47354-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5726,10 +5726,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44970</v>
+        <v>45202</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5785,7 +5785,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6548-2022</t>
+          <t>A 3276-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44601</v>
+        <v>45317</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5858,7 +5858,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 4856-2023</t>
+          <t>A 15648-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44957</v>
+        <v>45404</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5931,7 +5931,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59516-2023</t>
+          <t>A 8965-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5941,14 +5941,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45254</v>
+        <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15541-2023</t>
+          <t>A 47962-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45020</v>
+        <v>45204</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6077,7 +6077,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48247-2024</t>
+          <t>A 10120-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6091,10 +6091,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45590</v>
+        <v>45719</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16342-2023</t>
+          <t>A 6502-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6164,10 +6164,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45028</v>
+        <v>45339</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 44640-2023</t>
+          <t>A 60242-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6237,10 +6237,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45189</v>
+        <v>44910</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7237-2024</t>
+          <t>A 3533-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6310,10 +6310,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45344</v>
+        <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6369,7 +6369,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29008-2022</t>
+          <t>A 7646-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44749</v>
+        <v>45705</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6442,7 +6442,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 10184-2025</t>
+          <t>A 7647-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45719</v>
+        <v>45705</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6515,7 +6515,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 41881-2023</t>
+          <t>A 57862-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6529,10 +6529,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45176</v>
+        <v>45247</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3280-2023</t>
+          <t>A 4946-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6602,10 +6602,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44949</v>
+        <v>44593</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6661,7 +6661,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 6022-2024</t>
+          <t>A 59516-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45336</v>
+        <v>45254</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6734,7 +6734,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 1423-2022</t>
+          <t>A 16771-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6748,10 +6748,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44573</v>
+        <v>45411</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47205-2023</t>
+          <t>A 14417-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45202</v>
+        <v>45394</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6880,7 +6880,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43225-2022</t>
+          <t>A 50992-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44833</v>
+        <v>45218</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6909,8 +6909,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6953,7 +6958,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 47959-2023</t>
+          <t>A 54765-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6967,10 +6972,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45204</v>
+        <v>44883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6983,7 +6988,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7026,7 +7031,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44559-2023</t>
+          <t>A 26939-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7040,10 +7045,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45183</v>
+        <v>45093</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7056,7 +7061,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7099,7 +7104,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44565-2023</t>
+          <t>A 65113-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7113,10 +7118,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45183</v>
+        <v>45287</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7129,7 +7134,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7172,7 +7177,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62914-2023</t>
+          <t>A 60288-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7186,10 +7191,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45271</v>
+        <v>45258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7201,13 +7206,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7250,7 +7250,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 286-2026</t>
+          <t>A 41536-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46027</v>
+        <v>45901</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 4742-2022</t>
+          <t>A 24367-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7337,10 +7337,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44592</v>
+        <v>45797</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.6</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7396,7 +7396,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 275-2026</t>
+          <t>A 7634-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46027</v>
+        <v>44607</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7469,7 +7469,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 560-2026</t>
+          <t>A 2336-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7483,10 +7483,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46029</v>
+        <v>45310</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7498,13 +7498,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7547,7 +7542,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 2336-2024</t>
+          <t>A 8678-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7561,10 +7556,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45310</v>
+        <v>45354</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7577,7 +7572,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7620,7 +7615,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 260-2026</t>
+          <t>A 47679-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7634,10 +7629,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46027</v>
+        <v>45588</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7650,7 +7645,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>5.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7693,7 +7688,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 26939-2023</t>
+          <t>A 43225-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7707,10 +7702,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45093</v>
+        <v>44833</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7723,7 +7718,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7766,7 +7761,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37524-2023</t>
+          <t>A 39583-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7780,10 +7775,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45158</v>
+        <v>44818</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7796,7 +7791,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7839,7 +7834,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6160-2026</t>
+          <t>A 21233-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7853,10 +7848,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46055</v>
+        <v>45062</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7869,7 +7864,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7912,7 +7907,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6162-2026</t>
+          <t>A 46759-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7926,10 +7921,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46055</v>
+        <v>45926</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7942,7 +7937,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7985,7 +7980,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4946-2022</t>
+          <t>A 46762-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7999,10 +7994,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44593</v>
+        <v>45926</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8015,7 +8010,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8058,7 +8053,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 6161-2026</t>
+          <t>A 252-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8072,10 +8067,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46055</v>
+        <v>44922</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8088,7 +8083,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8131,7 +8126,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41536-2025</t>
+          <t>A 46774-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8145,10 +8140,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45901</v>
+        <v>45926</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8161,7 +8156,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8204,7 +8199,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8143-2023</t>
+          <t>A 46763-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8218,10 +8213,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44974</v>
+        <v>45926</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8234,7 +8229,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8277,7 +8272,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17590-2023</t>
+          <t>A 29041-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8291,10 +8286,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45036</v>
+        <v>45481</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8307,7 +8302,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8350,7 +8345,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8845-2026</t>
+          <t>A 46951-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8364,10 +8359,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46066</v>
+        <v>45929</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8380,7 +8375,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8423,7 +8418,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 8818-2026</t>
+          <t>A 46948-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8437,10 +8432,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46066</v>
+        <v>45929</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8453,7 +8448,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8496,7 +8491,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 8823-2026</t>
+          <t>A 28259-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8510,10 +8505,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46066</v>
+        <v>45099</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8526,7 +8521,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8569,7 +8564,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8822-2026</t>
+          <t>A 62048-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8583,10 +8578,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46066</v>
+        <v>44918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8599,7 +8594,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>5.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8642,7 +8637,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 35659-2022</t>
+          <t>A 1620-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8656,10 +8651,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44799</v>
+        <v>44937</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8672,7 +8667,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8715,7 +8710,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10575-2026</t>
+          <t>A 1621-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8729,10 +8724,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46077</v>
+        <v>44937</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8745,7 +8740,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8788,7 +8783,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58262-2022</t>
+          <t>A 57864-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8802,10 +8797,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44894</v>
+        <v>44899</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8818,7 +8813,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8861,7 +8856,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4027-2022</t>
+          <t>A 7582-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8875,10 +8870,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44587</v>
+        <v>44972</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8891,7 +8886,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8934,7 +8929,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 46774-2025</t>
+          <t>A 41881-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45926</v>
+        <v>45176</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8964,7 +8959,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9007,7 +9002,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 46759-2025</t>
+          <t>A 4742-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9021,10 +9016,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45926</v>
+        <v>44592</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9037,7 +9032,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.9</v>
+        <v>11.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9080,7 +9075,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 46951-2025</t>
+          <t>A 19937-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9094,10 +9089,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45929</v>
+        <v>45433</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9110,7 +9105,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>11.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9153,7 +9148,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28997-2022</t>
+          <t>A 48243-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9167,10 +9162,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44749</v>
+        <v>45590</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9183,7 +9178,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.6</v>
+        <v>0.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9226,7 +9221,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 46948-2025</t>
+          <t>A 15660-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9240,10 +9235,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45929</v>
+        <v>45404</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9256,7 +9251,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9299,7 +9294,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 46762-2025</t>
+          <t>A 43516-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9313,10 +9308,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45926</v>
+        <v>45569</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9328,8 +9323,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9372,7 +9372,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46763-2025</t>
+          <t>A 43518-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45926</v>
+        <v>45569</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9401,8 +9401,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9445,7 +9450,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 15648-2024</t>
+          <t>A 48247-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9459,10 +9464,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45404</v>
+        <v>45590</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9475,7 +9480,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.2</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9518,7 +9523,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56303-2024</t>
+          <t>A 9337-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9532,10 +9537,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45624</v>
+        <v>44616</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9548,7 +9553,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9591,7 +9596,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 3267-2023</t>
+          <t>A 38438-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9605,10 +9610,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44949</v>
+        <v>45546</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9621,7 +9626,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9664,7 +9669,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50606-2024</t>
+          <t>A 57144-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9678,10 +9683,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45601</v>
+        <v>45629</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9694,7 +9699,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9737,7 +9742,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 8890-2024</t>
+          <t>A 34357-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9751,10 +9756,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45357</v>
+        <v>45133</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9767,7 +9772,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7.4</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9810,7 +9815,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 15078-2026</t>
+          <t>A 17590-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9824,10 +9829,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46105</v>
+        <v>45036</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9840,7 +9845,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9883,7 +9888,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 17296-2023</t>
+          <t>A 10184-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9897,10 +9902,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45035</v>
+        <v>45719</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9912,13 +9917,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9961,7 +9961,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15138-2026</t>
+          <t>A 19745-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9975,10 +9975,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46105</v>
+        <v>45432</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10034,7 +10034,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 15096-2026</t>
+          <t>A 59399-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46105</v>
+        <v>44491</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 1620-2023</t>
+          <t>A 56830-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44937</v>
+        <v>45628</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10180,7 +10180,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 1621-2023</t>
+          <t>A 49934-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44937</v>
+        <v>45597</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10209,8 +10209,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10253,7 +10258,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60285-2023</t>
+          <t>A 14082-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10267,10 +10272,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45258</v>
+        <v>45009</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10283,7 +10288,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10326,7 +10331,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59399-2021</t>
+          <t>A 35908-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10340,10 +10345,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44491</v>
+        <v>45148</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10356,7 +10361,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10399,7 +10404,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 6357-2023</t>
+          <t>A 6580-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10413,10 +10418,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44965</v>
+        <v>45699</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10429,7 +10434,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10489,7 +10494,7 @@
         <v>45790</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10545,7 +10550,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6580-2025</t>
+          <t>A 2355-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10559,10 +10564,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45699</v>
+        <v>44942</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10575,7 +10580,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10618,7 +10623,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 54765-2022</t>
+          <t>A 38431-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10632,10 +10637,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44883</v>
+        <v>45546</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10648,7 +10653,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10691,7 +10696,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19925-2024</t>
+          <t>A 4856-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10705,10 +10710,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45433</v>
+        <v>44957</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10721,7 +10726,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10764,7 +10769,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 41889-2023</t>
+          <t>A 45783-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10774,14 +10779,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45176</v>
+        <v>45195</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10794,7 +10799,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10837,7 +10842,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 48158-2023</t>
+          <t>A 4027-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10851,10 +10856,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45205</v>
+        <v>44587</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10866,13 +10871,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10915,7 +10915,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8965-2023</t>
+          <t>A 41314-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44979</v>
+        <v>45173</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10988,7 +10988,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 21396-2025</t>
+          <t>A 1974-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11002,10 +11002,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45782</v>
+        <v>44575</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11061,7 +11061,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 28259-2023</t>
+          <t>A 3894-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11075,10 +11075,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45099</v>
+        <v>44587</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11134,7 +11134,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 2355-2023</t>
+          <t>A 23672-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11148,10 +11148,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44942</v>
+        <v>45793</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11207,7 +11207,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23672-2025</t>
+          <t>A 39517-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11221,10 +11221,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45793</v>
+        <v>45167</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11280,7 +11280,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 8678-2024</t>
+          <t>A 49931-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11294,10 +11294,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45354</v>
+        <v>45597</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11309,8 +11309,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11353,7 +11358,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57513-2022</t>
+          <t>A 1423-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11363,14 +11368,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44896</v>
+        <v>44573</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11383,7 +11388,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11426,7 +11431,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 59838-2025</t>
+          <t>A 7254-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11440,10 +11445,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45992</v>
+        <v>44970</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11456,7 +11461,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11499,7 +11504,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 58740-2025</t>
+          <t>A 7266-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11513,10 +11518,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45986</v>
+        <v>44970</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11529,7 +11534,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11572,7 +11577,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 58749-2025</t>
+          <t>A 59838-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11586,10 +11591,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45986</v>
+        <v>45992</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11602,7 +11607,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11645,7 +11650,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 59479-2025</t>
+          <t>A 47959-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11659,10 +11664,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45989</v>
+        <v>45204</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11674,13 +11679,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11723,7 +11723,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 59839-2025</t>
+          <t>A 57680-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11737,10 +11737,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45992</v>
+        <v>44897</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11796,7 +11796,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 46186-2024</t>
+          <t>A 31862-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11810,10 +11810,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45581</v>
+        <v>44777</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60903-2025</t>
+          <t>A 58749-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11883,10 +11883,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45999</v>
+        <v>45986</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11898,13 +11898,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11947,7 +11942,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 60911-2025</t>
+          <t>A 49345-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11961,10 +11956,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45999</v>
+        <v>45211</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11976,13 +11971,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12025,7 +12015,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26811-2023</t>
+          <t>A 49348-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12039,10 +12029,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45093</v>
+        <v>45211</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12055,7 +12045,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12098,7 +12088,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 62239-2025</t>
+          <t>A 50606-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12112,10 +12102,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46006</v>
+        <v>45601</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12128,7 +12118,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12171,7 +12161,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 62220-2025</t>
+          <t>A 58740-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12185,10 +12175,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46006</v>
+        <v>45986</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12201,7 +12191,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12244,7 +12234,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 62228-2025</t>
+          <t>A 45873-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12258,10 +12248,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46006</v>
+        <v>45195</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12274,7 +12264,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>15.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12317,7 +12307,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 62238-2025</t>
+          <t>A 47219-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12331,10 +12321,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46006</v>
+        <v>44852</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12347,7 +12337,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12390,7 +12380,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 63826-2025</t>
+          <t>A 21370-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12404,10 +12394,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46020</v>
+        <v>46147</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12419,8 +12409,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12463,7 +12458,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 63954-2025</t>
+          <t>A 22292-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12477,10 +12472,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46020</v>
+        <v>46154</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12493,7 +12488,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12536,7 +12531,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 63779-2025</t>
+          <t>A 59839-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12550,10 +12545,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46019</v>
+        <v>45992</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12566,7 +12561,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12609,7 +12604,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 63957-2025</t>
+          <t>A 59741-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12623,10 +12618,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46020</v>
+        <v>45257</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12639,7 +12634,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12682,7 +12677,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 290-2026</t>
+          <t>A 59479-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12696,10 +12691,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46027</v>
+        <v>45989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12709,6 +12704,11 @@
       <c r="G156" t="inlineStr">
         <is>
           <t>VALDEMARSVIK</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -12755,7 +12755,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 21511-2025</t>
+          <t>A 22296-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12765,14 +12765,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45782</v>
+        <v>46154</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12828,7 +12828,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26821-2023</t>
+          <t>A 24972-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12842,10 +12842,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45093</v>
+        <v>44728</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 21370-2026</t>
+          <t>A 22468-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12915,10 +12915,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46147</v>
+        <v>46155</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12979,7 +12979,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 22296-2026</t>
+          <t>A 56303-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12993,10 +12993,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46154</v>
+        <v>45624</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13052,7 +13052,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 22292-2026</t>
+          <t>A 24234-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13066,10 +13066,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46154</v>
+        <v>44725</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13125,7 +13125,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 22468-2026</t>
+          <t>A 43151-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13139,10 +13139,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46155</v>
+        <v>45183</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13154,13 +13154,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13203,7 +13198,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 3533-2022</t>
+          <t>A 4047-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13217,10 +13212,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44585</v>
+        <v>44952</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13233,7 +13228,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13276,7 +13271,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24532-2026</t>
+          <t>A 58979-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13290,10 +13285,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46170</v>
+        <v>44903</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13306,7 +13301,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13349,7 +13344,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 58979-2022</t>
+          <t>A 45377-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13363,10 +13358,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44903</v>
+        <v>45193</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13379,7 +13374,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13422,7 +13417,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 9971-2023</t>
+          <t>A 60911-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13436,10 +13431,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44985</v>
+        <v>45999</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13451,8 +13446,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13495,7 +13495,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 4965-2026</t>
+          <t>A 60903-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13509,10 +13509,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46049</v>
+        <v>45999</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13524,8 +13524,13 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13568,7 +13573,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 29041-2024</t>
+          <t>A 4331-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13582,10 +13587,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45481</v>
+        <v>44953</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13598,7 +13603,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13641,7 +13646,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 53111-2023</t>
+          <t>A 66424-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13655,10 +13660,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45228</v>
+        <v>44518</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13671,7 +13676,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13714,7 +13719,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 39517-2023</t>
+          <t>A 44559-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13728,10 +13733,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45167</v>
+        <v>45183</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13744,7 +13749,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13787,7 +13792,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 57680-2022</t>
+          <t>A 44565-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13801,10 +13806,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44897</v>
+        <v>45183</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13817,7 +13822,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13860,7 +13865,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 40728-2023</t>
+          <t>A 62228-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13870,14 +13875,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45170</v>
+        <v>46006</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13890,7 +13895,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13933,7 +13938,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 27525-2026</t>
+          <t>A 62238-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13947,10 +13952,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46189</v>
+        <v>46006</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14006,7 +14011,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 18200-2025</t>
+          <t>A 62220-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14020,10 +14025,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45761</v>
+        <v>46006</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14036,7 +14041,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14079,7 +14084,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 16771-2024</t>
+          <t>A 28997-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14093,10 +14098,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45411</v>
+        <v>44749</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14109,7 +14114,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14152,7 +14157,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 4125-2025</t>
+          <t>A 62239-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14166,10 +14171,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45685</v>
+        <v>46006</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14182,7 +14187,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14225,7 +14230,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 4126-2025</t>
+          <t>A 15541-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14239,10 +14244,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45685</v>
+        <v>45020</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14255,7 +14260,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14298,7 +14303,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58247-2024</t>
+          <t>A 10135-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14312,10 +14317,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45632</v>
+        <v>45719</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14328,7 +14333,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>8.4</v>
+        <v>10.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14371,7 +14376,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 47219-2022</t>
+          <t>A 54849-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14385,10 +14390,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44852</v>
+        <v>45236</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14401,7 +14406,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14444,7 +14449,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 50148-2023</t>
+          <t>A 34572-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14458,10 +14463,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45215</v>
+        <v>45526</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14474,7 +14479,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14517,7 +14522,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28119-2026</t>
+          <t>A 23827-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14531,10 +14536,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46195</v>
+        <v>44722</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14547,7 +14552,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14590,7 +14595,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 28093-2026</t>
+          <t>A 4125-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14604,10 +14609,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46195</v>
+        <v>45685</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14663,7 +14668,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 8328-2024</t>
+          <t>A 4126-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14677,10 +14682,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45352</v>
+        <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14693,7 +14698,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14736,7 +14741,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 60288-2023</t>
+          <t>A 17717-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14750,10 +14755,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45258</v>
+        <v>45758</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14766,7 +14771,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14809,7 +14814,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 9292-2023</t>
+          <t>A 50041-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14823,10 +14828,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44980</v>
+        <v>45215</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14839,7 +14844,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14882,7 +14887,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 3894-2022</t>
+          <t>A 37524-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14896,10 +14901,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44587</v>
+        <v>45158</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14912,7 +14917,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14955,7 +14960,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 24234-2022</t>
+          <t>A 44640-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14969,10 +14974,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44725</v>
+        <v>45189</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14985,7 +14990,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15028,7 +15033,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 42623-2024</t>
+          <t>A 63826-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15042,10 +15047,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45565</v>
+        <v>46020</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15058,7 +15063,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15101,7 +15106,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 17937-2023</t>
+          <t>A 42401-2022</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15115,10 +15120,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45040</v>
+        <v>44830</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15130,13 +15135,8 @@
           <t>VALDEMARSVIK</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15179,7 +15179,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 30964-2026</t>
+          <t>A 63779-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15189,14 +15189,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46213</v>
+        <v>46019</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15252,7 +15252,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 24972-2022</t>
+          <t>A 63954-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15266,10 +15266,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44728</v>
+        <v>46020</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 6502-2024</t>
+          <t>A 63957-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15339,10 +15339,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45339</v>
+        <v>46020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15398,7 +15398,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14429-2022</t>
+          <t>A 24532-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15412,10 +15412,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44652</v>
+        <v>46170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15471,7 +15471,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 17585-2023</t>
+          <t>A 286-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15485,10 +15485,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45036</v>
+        <v>46027</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15544,7 +15544,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 35740-2026</t>
+          <t>A 275-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46265</v>
+        <v>46027</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 35924-2026</t>
+          <t>A 290-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46266</v>
+        <v>46027</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@